--- a/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Лаб1.xlsx
+++ b/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Лаб1.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Codespace\Файлы\1 курс\2 семестр\Экология\Лабы\18.02.25 - 1-ая лаба\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codespace\Файлы\1 курс\2 семестр\Экология\Лабы\18.02.25 - 1-ая лаба\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32554071-56B9-4BAA-AB0D-BC1F49420787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_Hlk153478266" localSheetId="1">Лист2!$K$19</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="233">
   <si>
     <t>V(ов) л</t>
   </si>
@@ -581,9 +583,6 @@
     <t>CnHn</t>
   </si>
   <si>
-    <t>Вредное</t>
-  </si>
-  <si>
     <r>
       <t>Масса вредного вещества при сгорании топлива (m вв</t>
     </r>
@@ -1033,144 +1032,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>ВВ. </t>
-    </r>
-  </si>
-  <si>
-    <t>вещество</t>
-  </si>
-  <si>
-    <t>Концентрация вредных</t>
-  </si>
-  <si>
-    <r>
-      <t>веществ на учетной территории, мг/м</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>, (С</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>ВВ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Объем воздуха,</t>
-  </si>
-  <si>
-    <r>
-      <t>необходимый для разбавления, м</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> (Vв</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>р</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Класс</t>
-  </si>
-  <si>
-    <t>опасности</t>
-  </si>
-  <si>
-    <t>Предельно допустимые</t>
-  </si>
-  <si>
-    <r>
-      <t>концентрации, мг/м</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t> (ПДК)</t>
     </r>
   </si>
   <si>
@@ -1759,17 +1620,237 @@
   </si>
   <si>
     <t>Тип автомобиля</t>
+  </si>
+  <si>
+    <t>Вещество</t>
+  </si>
+  <si>
+    <t>ПДКсс</t>
+  </si>
+  <si>
+    <t>А = 1 / ПДК</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>fM</t>
+  </si>
+  <si>
+    <t>Класс опаности</t>
+  </si>
+  <si>
+    <t>Предельно допустимые концентрации, мг/м3 (ПДК)</t>
+  </si>
+  <si>
+    <t>Объем воздуха, необходимый для разбавления, м3 (Vвр)</t>
+  </si>
+  <si>
+    <t>Концентрация вредных веществ на учетной территории, мг/м3, (СВВ)</t>
+  </si>
+  <si>
+    <r>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (т)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>mf</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>NO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>С</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Н</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>У</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>атм</t>
+    </r>
+  </si>
+  <si>
+    <t>руб/год</t>
+  </si>
+  <si>
+    <t>γ</t>
+  </si>
+  <si>
+    <t>руб/усл.т.</t>
+  </si>
+  <si>
+    <t>σ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1913,14 +1994,6 @@
     </font>
     <font>
       <vertAlign val="superscript"/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1945,6 +2018,34 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1960,7 +2061,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -2238,12 +2339,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2262,9 +2389,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2275,18 +2399,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2326,12 +2441,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2339,39 +2448,68 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2403,60 +2541,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2495,7 +2662,7 @@
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CE44EA3F-B28A-BD79-1AB5-04F7F8379C00}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2544,7 +2711,7 @@
         <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8754555E-3D36-4C82-ACE2-B462D285F125}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2585,7 +2752,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2623,7 +2796,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Рисунок 3"/>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2911,7 +3090,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3390,7 +3569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3412,13 +3591,13 @@
       <c r="A1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>73</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -3669,17 +3848,17 @@
       <c r="C10" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="55" t="s">
+      <c r="G10" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="57" t="s">
+      <c r="H10" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="59"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="62"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
@@ -3691,23 +3870,23 @@
       <c r="C11" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="56"/>
-      <c r="H11" s="13" t="s">
+      <c r="G11" s="59"/>
+      <c r="H11" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="12" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3716,22 +3895,22 @@
       <c r="G12" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="12">
         <v>395</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <v>1.6</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="12">
         <v>20</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="12">
         <v>0.7</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="12">
         <v>34</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="12">
         <v>2</v>
       </c>
     </row>
@@ -3749,22 +3928,22 @@
       <c r="G13" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <v>9</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>6</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="12">
         <v>33</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="12">
         <v>20</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="12">
         <v>16</v>
       </c>
     </row>
@@ -3781,17 +3960,17 @@
       </c>
     </row>
     <row r="15" spans="1:17" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G15" s="28" t="s">
+      <c r="G15" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="I15" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="J15" s="14" t="s">
         <v>152</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -3808,15 +3987,15 @@
       <c r="G16" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="12">
         <f>B4</f>
         <v>5</v>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="25">
         <f>H16*3</f>
         <v>15</v>
       </c>
-      <c r="J16" s="29">
+      <c r="J16" s="25">
         <f>B21*I16*2</f>
         <v>6</v>
       </c>
@@ -3835,17 +4014,17 @@
       <c r="G17" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G18" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:16" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
@@ -3856,114 +4035,114 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B20">
         <f>B4</f>
         <v>5</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-    </row>
-    <row r="21" spans="1:16" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H20" s="12"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+    </row>
+    <row r="21" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B21">
         <f>0.2</f>
         <v>0.2</v>
       </c>
       <c r="C21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="16" t="s">
-        <v>162</v>
+      <c r="A23" s="15" t="s">
+        <v>161</v>
       </c>
       <c r="B23">
         <f>H34</f>
         <v>0</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="H23" s="63" t="s">
         <v>134</v>
       </c>
-      <c r="H23" s="60" t="s">
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="65"/>
+    </row>
+    <row r="24" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G24" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="I23" s="61"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="61"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="61"/>
-      <c r="O23" s="61"/>
-      <c r="P23" s="62"/>
-    </row>
-    <row r="24" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G24" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="24" t="s">
+      <c r="I24" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="I24" s="24" t="s">
+      <c r="J24" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="J24" s="24" t="s">
+      <c r="K24" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="K24" s="24" t="s">
+      <c r="L24" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="L24" s="24" t="s">
+      <c r="M24" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="N24" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="M24" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="N24" s="25" t="s">
+      <c r="O24" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="O24" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="P24" s="23" t="s">
-        <v>131</v>
+      <c r="P24" s="19" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="21" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B25">
         <f>B26*B27*B28</f>
         <v>3.4999999999999999E-6</v>
       </c>
       <c r="C25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D25">
         <f>D26*D27*D28</f>
@@ -3972,39 +4151,39 @@
       <c r="E25" t="s">
         <v>101</v>
       </c>
-      <c r="G25" s="23" t="s">
+      <c r="G25" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="20">
         <v>19.8</v>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="20">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J25" s="24">
+      <c r="J25" s="20">
         <v>0.28000000000000003</v>
       </c>
-      <c r="K25" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="L25" s="24">
+      <c r="K25" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="L25" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M25" s="24">
+      <c r="M25" s="20">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="N25" s="25"/>
-      <c r="O25" s="26">
+      <c r="N25" s="21"/>
+      <c r="O25" s="22">
         <f>0.18*10^-6</f>
         <v>1.8E-7</v>
       </c>
-      <c r="P25" s="23">
+      <c r="P25" s="19">
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B26">
         <f>B21</f>
@@ -4015,207 +4194,207 @@
         <v>200</v>
       </c>
       <c r="E26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="H26" s="63">
+        <v>165</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="H26" s="66">
         <v>37.299999999999997</v>
       </c>
-      <c r="I26" s="63">
+      <c r="I26" s="66">
         <v>6.9</v>
       </c>
-      <c r="J26" s="63">
+      <c r="J26" s="66">
         <v>0.8</v>
       </c>
-      <c r="K26" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="L26" s="63">
+      <c r="K26" s="66" t="s">
+        <v>142</v>
+      </c>
+      <c r="L26" s="66">
         <v>0.19</v>
       </c>
-      <c r="M26" s="63">
+      <c r="M26" s="66">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="N26" s="63">
+      <c r="N26" s="66">
         <v>0.85</v>
       </c>
-      <c r="O26" s="63" t="s">
-        <v>146</v>
-      </c>
-      <c r="P26" s="63">
+      <c r="O26" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="P26" s="66">
         <v>0.23400000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B27">
         <f>10/1000</f>
         <v>0.01</v>
       </c>
       <c r="C27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>166</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="H27" s="64"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="64"/>
-      <c r="L27" s="64"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="64"/>
-      <c r="P27" s="64"/>
+        <v>165</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="H27" s="67"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="67"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="67"/>
+      <c r="P27" s="67"/>
     </row>
     <row r="28" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B28">
         <f>1.75/1000</f>
         <v>1.75E-3</v>
       </c>
       <c r="C28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D28">
         <f>B28*1000</f>
         <v>1.75</v>
       </c>
       <c r="E28" t="s">
-        <v>166</v>
-      </c>
-      <c r="G28" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="20">
+        <v>28.5</v>
+      </c>
+      <c r="I28" s="20">
+        <v>3.5</v>
+      </c>
+      <c r="J28" s="20">
+        <v>0.6</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="L28" s="20">
+        <v>0.11</v>
+      </c>
+      <c r="M28" s="20">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="N28" s="21">
+        <v>0.88</v>
+      </c>
+      <c r="O28" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="H28" s="24">
-        <v>28.5</v>
-      </c>
-      <c r="I28" s="24">
+      <c r="P28" s="19">
+        <v>0.83199999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G29" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H29" s="20">
+        <v>6.2</v>
+      </c>
+      <c r="I29" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J29" s="20">
         <v>3.5</v>
       </c>
-      <c r="J28" s="24">
-        <v>0.6</v>
-      </c>
-      <c r="K28" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="L28" s="24">
-        <v>0.11</v>
-      </c>
-      <c r="M28" s="24">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="N28" s="25">
-        <v>0.88</v>
-      </c>
-      <c r="O28" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="P28" s="23">
-        <v>0.83199999999999996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G29" s="23" t="s">
+      <c r="K29" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="L29" s="20">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="N29" s="21"/>
+      <c r="O29" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="H29" s="24">
-        <v>6.2</v>
-      </c>
-      <c r="I29" s="24">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J29" s="24">
-        <v>3.5</v>
-      </c>
-      <c r="K29" s="24">
-        <v>0.3</v>
-      </c>
-      <c r="L29" s="24">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M29" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="N29" s="25"/>
-      <c r="O29" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="P29" s="23">
+      <c r="P29" s="19">
         <v>4.72</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F31" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65" t="s">
+      <c r="F31" s="56" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="I31" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="I31" s="65" t="s">
+      <c r="J31" s="57" t="s">
         <v>124</v>
       </c>
-      <c r="J31" s="66" t="s">
-        <v>125</v>
-      </c>
-      <c r="K31" s="66"/>
+      <c r="K31" s="57"/>
     </row>
     <row r="32" spans="1:16" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B32">
         <v>16.7</v>
       </c>
       <c r="C32" t="s">
-        <v>199</v>
-      </c>
-      <c r="F32" s="65"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65"/>
+        <v>189</v>
+      </c>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
       <c r="J32" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B33">
         <f>B17/B32</f>
         <v>0.49574101796407183</v>
       </c>
       <c r="C33" t="s">
-        <v>203</v>
-      </c>
-      <c r="F33" s="67" t="s">
-        <v>136</v>
-      </c>
-      <c r="G33" s="30" t="s">
-        <v>126</v>
+        <v>193</v>
+      </c>
+      <c r="F33" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="H33" s="1">
         <f>B13*H12</f>
@@ -4225,51 +4404,51 @@
         <f>B19*H25*24*365</f>
         <v>173448.00000000003</v>
       </c>
-      <c r="J33" s="67">
+      <c r="J33" s="55">
         <f>SUM(H33:I33)</f>
         <v>2617510.5</v>
       </c>
-      <c r="K33" s="67">
+      <c r="K33" s="55">
         <f>J33/365</f>
         <v>7171.2616438356163</v>
       </c>
-      <c r="N33" s="54"/>
+      <c r="N33" s="45"/>
     </row>
     <row r="34" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B34">
         <f>Лист1!B46/10000</f>
         <v>3.8970873005464479E-2</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
-      </c>
-      <c r="F34" s="67"/>
-      <c r="G34" s="30" t="s">
-        <v>127</v>
+        <v>193</v>
+      </c>
+      <c r="F34" s="55"/>
+      <c r="G34" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="H34" s="1"/>
-      <c r="J34" s="67"/>
-      <c r="K34" s="67"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="55"/>
     </row>
     <row r="35" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B35" s="53">
+        <v>191</v>
+      </c>
+      <c r="B35" s="44">
         <f>B34+B33</f>
         <v>0.53471189096953631</v>
       </c>
       <c r="C35" t="s">
-        <v>203</v>
-      </c>
-      <c r="F35" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="F35" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="G35" s="30" t="s">
-        <v>126</v>
+      <c r="G35" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="H35" s="1">
         <f>B13*I12</f>
@@ -4279,42 +4458,42 @@
         <f>B19*L25*24*365</f>
         <v>613.20000000000005</v>
       </c>
-      <c r="J35" s="67">
+      <c r="J35" s="55">
         <f t="shared" ref="J35" si="1">SUM(H35:I35)</f>
         <v>10513.2</v>
       </c>
-      <c r="K35" s="67">
+      <c r="K35" s="55">
         <f>J35/365</f>
         <v>28.80328767123288</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="30" t="s">
-        <v>127</v>
+      <c r="F36" s="55"/>
+      <c r="G36" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="67"/>
-      <c r="K36" s="67"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
     </row>
     <row r="37" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B37">
         <f>B35*1.25</f>
         <v>0.66838986371192033</v>
       </c>
       <c r="C37" t="s">
-        <v>203</v>
-      </c>
-      <c r="F37" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="30" t="s">
-        <v>126</v>
+      <c r="G37" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="H37" s="1">
         <f>B13*J12</f>
@@ -4324,37 +4503,37 @@
         <f>B19*J25*24*365</f>
         <v>2452.8000000000002</v>
       </c>
-      <c r="J37" s="67">
+      <c r="J37" s="55">
         <f t="shared" ref="J37" si="2">SUM(H37:I37)</f>
         <v>126202.8</v>
       </c>
-      <c r="K37" s="67">
+      <c r="K37" s="55">
         <f>J37/365</f>
         <v>345.76109589041096</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F38" s="67"/>
-      <c r="G38" s="30" t="s">
-        <v>127</v>
+      <c r="F38" s="55"/>
+      <c r="G38" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="67"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="55"/>
     </row>
     <row r="39" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B39">
         <v>12</v>
       </c>
-      <c r="F39" s="67" t="s">
+      <c r="F39" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="G39" s="30" t="s">
-        <v>126</v>
+      <c r="G39" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="H39" s="1">
         <f>B13*K12</f>
@@ -4364,44 +4543,44 @@
         <f>B19*M25*24*365</f>
         <v>306.60000000000002</v>
       </c>
-      <c r="J39" s="67">
+      <c r="J39" s="55">
         <f t="shared" ref="J39" si="3">SUM(H39:I39)</f>
         <v>4637.8500000000004</v>
       </c>
-      <c r="K39" s="67">
+      <c r="K39" s="55">
         <f>J39/365</f>
         <v>12.706438356164385</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B40">
         <v>16</v>
       </c>
-      <c r="F40" s="67"/>
-      <c r="G40" s="30" t="s">
-        <v>127</v>
+      <c r="F40" s="55"/>
+      <c r="G40" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="67"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="55"/>
     </row>
     <row r="41" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B41">
         <f>B39+B40</f>
         <v>28</v>
       </c>
-      <c r="F41" s="67" t="s">
-        <v>133</v>
-      </c>
-      <c r="G41" s="30" t="s">
-        <v>126</v>
+      <c r="F41" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="H41" s="1">
         <f>B13*N25</f>
@@ -4411,38 +4590,38 @@
         <f>B19*N25</f>
         <v>0</v>
       </c>
-      <c r="J41" s="67">
+      <c r="J41" s="55">
         <f t="shared" ref="J41" si="4">SUM(H41:I41)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="67">
+      <c r="K41" s="55">
         <f>J41/365</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B42">
         <f>B39+2*B40</f>
         <v>44</v>
       </c>
-      <c r="F42" s="67"/>
-      <c r="G42" s="30" t="s">
-        <v>127</v>
+      <c r="F42" s="55"/>
+      <c r="G42" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="67"/>
-      <c r="K42" s="67"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="55"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F43" s="67" t="s">
+      <c r="F43" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="G43" s="30" t="s">
-        <v>126</v>
+      <c r="G43" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="H43" s="1">
         <f>B13*L12</f>
@@ -4452,35 +4631,35 @@
         <f>B19*I25*24*365</f>
         <v>20148</v>
       </c>
-      <c r="J43" s="67">
+      <c r="J43" s="55">
         <f t="shared" ref="J43" si="5">SUM(H43:I43)</f>
         <v>230523</v>
       </c>
-      <c r="K43" s="67">
+      <c r="K43" s="55">
         <f>J43/365</f>
         <v>631.56986301369864</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B44">
         <f>B42/B41</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="F44" s="67"/>
-      <c r="G44" s="30" t="s">
-        <v>127</v>
+      <c r="F44" s="55"/>
+      <c r="G44" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="67"/>
-      <c r="K44" s="67"/>
+      <c r="J44" s="55"/>
+      <c r="K44" s="55"/>
     </row>
     <row r="45" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B45">
         <f>J33/1000</f>
@@ -4489,29 +4668,29 @@
       <c r="C45" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="67" t="s">
-        <v>130</v>
-      </c>
-      <c r="G45" s="30" t="s">
-        <v>126</v>
+      <c r="F45" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="G45" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="H45" s="1">
         <f>B13*M12</f>
         <v>12375</v>
       </c>
       <c r="I45" s="1"/>
-      <c r="J45" s="67">
+      <c r="J45" s="55">
         <f t="shared" ref="J45" si="6">SUM(H45:I45)</f>
         <v>12375</v>
       </c>
-      <c r="K45" s="67">
+      <c r="K45" s="55">
         <f>J45/365</f>
         <v>33.904109589041099</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B46">
         <f>(B44*B45)+(Лист1!B27*1000)</f>
@@ -4520,18 +4699,18 @@
       <c r="C46" t="s">
         <v>104</v>
       </c>
-      <c r="F46" s="67"/>
-      <c r="G46" s="30" t="s">
-        <v>127</v>
+      <c r="F46" s="55"/>
+      <c r="G46" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-      <c r="J46" s="67"/>
-      <c r="K46" s="67"/>
+      <c r="J46" s="55"/>
+      <c r="K46" s="55"/>
     </row>
     <row r="47" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B47">
         <f>B46/1000</f>
@@ -4540,138 +4719,132 @@
       <c r="C47" t="s">
         <v>107</v>
       </c>
-      <c r="F47" s="67" t="s">
-        <v>157</v>
-      </c>
-      <c r="G47" s="30" t="s">
-        <v>126</v>
+      <c r="F47" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1">
         <f>B19*P25*24*365</f>
         <v>376.68</v>
       </c>
-      <c r="J47" s="67">
+      <c r="J47" s="55">
         <f t="shared" ref="J47" si="7">SUM(H47:I47)</f>
         <v>376.68</v>
       </c>
-      <c r="K47" s="67">
+      <c r="K47" s="55">
         <f>J47/365</f>
         <v>1.032</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F48" s="67"/>
-      <c r="G48" s="30" t="s">
-        <v>127</v>
+      <c r="F48" s="55"/>
+      <c r="G48" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
-      <c r="J48" s="67"/>
-      <c r="K48" s="67"/>
+      <c r="J48" s="55"/>
+      <c r="K48" s="55"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F49" s="67" t="s">
-        <v>158</v>
-      </c>
-      <c r="G49" s="30" t="s">
-        <v>126</v>
+      <c r="F49" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="G49" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1">
         <f>B19*O25*24*365</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="J49" s="67">
+      <c r="J49" s="55">
         <f t="shared" ref="J49" si="8">SUM(H49:I49)</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="K49" s="67">
+      <c r="K49" s="55">
         <f>J49/365</f>
         <v>4.3200000000000001E-6</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F50" s="67"/>
-      <c r="G50" s="30" t="s">
-        <v>127</v>
+      <c r="F50" s="55"/>
+      <c r="G50" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="J50" s="67"/>
-      <c r="K50" s="67"/>
+      <c r="J50" s="55"/>
+      <c r="K50" s="55"/>
     </row>
     <row r="51" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="8" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B51">
         <f>(B47/Лист1!Q1)/10000</f>
         <v>1.4469473904748054</v>
       </c>
       <c r="C51" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B52">
         <f>B51*1.25</f>
         <v>1.8086842380935066</v>
       </c>
       <c r="C52" t="s">
-        <v>203</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H52" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="I52" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="J52" s="39"/>
-    </row>
-    <row r="53" spans="1:11" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G53" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="H53" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="I53" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="J53" s="44" t="s">
         <v>193</v>
       </c>
+      <c r="G52" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="H52" s="69" t="s">
+        <v>220</v>
+      </c>
+      <c r="I52" s="79" t="s">
+        <v>219</v>
+      </c>
+      <c r="J52" s="78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="80"/>
+      <c r="J53" s="77"/>
     </row>
     <row r="54" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B54">
         <f>SUM(I16:I21)</f>
         <v>15</v>
       </c>
       <c r="C54" t="s">
-        <v>215</v>
-      </c>
-      <c r="G54" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="G54" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="H54" s="21">
+      <c r="H54" s="17">
         <f>K33*1000/$D$25</f>
         <v>2048.9318982387476</v>
       </c>
-      <c r="I54" s="36">
+      <c r="I54" s="30">
         <f>K33/J71</f>
         <v>2390.4205479452053</v>
       </c>
-      <c r="J54" s="43">
+      <c r="J54" s="35">
         <f>H54/J71</f>
         <v>682.97729941291584</v>
       </c>
@@ -4680,15 +4853,15 @@
       <c r="G55" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H55" s="32">
+      <c r="H55" s="28">
         <f>K35*1000/$D$25</f>
         <v>8.2295107632093938</v>
       </c>
-      <c r="I55" s="37">
+      <c r="I55" s="31">
         <f>K35/J78</f>
         <v>576.0657534246576</v>
       </c>
-      <c r="J55" s="41">
+      <c r="J55" s="33">
         <f>H55/J78</f>
         <v>164.59021526418786</v>
       </c>
@@ -4697,49 +4870,49 @@
       <c r="G56" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="28">
         <f>K37*1000/$D$25</f>
         <v>98.788884540117408</v>
       </c>
-      <c r="I56" s="37">
+      <c r="I56" s="31">
         <f>K37/J68</f>
         <v>8644.0273972602736</v>
       </c>
-      <c r="J56" s="41">
+      <c r="J56" s="33">
         <f>H56/J68</f>
         <v>2469.7221135029354</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G57" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="H57" s="32">
+        <v>127</v>
+      </c>
+      <c r="H57" s="28">
         <f>K39*1000/$D$25</f>
         <v>3.6304109589041103</v>
       </c>
-      <c r="I57" s="37">
+      <c r="I57" s="31">
         <f>K39/J70</f>
         <v>42354.794520547955</v>
       </c>
-      <c r="J57" s="41">
+      <c r="J57" s="33">
         <f>H57/J70</f>
         <v>12101.369863013702</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G58" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="H58" s="32">
+        <v>128</v>
+      </c>
+      <c r="H58" s="28">
         <f>K41*1000/$D$25</f>
         <v>0</v>
       </c>
-      <c r="I58" s="37">
+      <c r="I58" s="31">
         <f>K41/J84</f>
         <v>0</v>
       </c>
-      <c r="J58" s="41">
+      <c r="J58" s="33">
         <f>H58</f>
         <v>0</v>
       </c>
@@ -4748,471 +4921,467 @@
       <c r="G59" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="H59" s="32">
+      <c r="H59" s="28">
         <f>K43*1000/$D$25</f>
         <v>180.44853228962816</v>
       </c>
-      <c r="I59" s="37">
+      <c r="I59" s="31">
         <f>K43/J74</f>
         <v>126313.97260273973</v>
       </c>
-      <c r="J59" s="41">
+      <c r="J59" s="33">
         <f>H59/J74</f>
         <v>36089.706457925633</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G60" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="H60" s="32">
+        <v>129</v>
+      </c>
+      <c r="H60" s="28">
         <f>K45*1000/$D$25</f>
         <v>9.6868884540117435</v>
       </c>
-      <c r="I60" s="37">
+      <c r="I60" s="31">
         <f>K45/J69</f>
         <v>678.08219178082197</v>
       </c>
-      <c r="J60" s="41">
+      <c r="J60" s="33">
         <f>H60/J69</f>
         <v>193.73776908023487</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G61" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H61" s="32">
+        <v>130</v>
+      </c>
+      <c r="H61" s="28">
         <f>K47*1000/$D$25</f>
         <v>0.29485714285714287</v>
       </c>
-      <c r="I61" s="37">
+      <c r="I61" s="31">
         <f>K47/J85</f>
         <v>17.200000000000003</v>
       </c>
-      <c r="J61" s="41">
+      <c r="J61" s="33">
         <f>H61/J85</f>
         <v>4.9142857142857146</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G62" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="H62" s="33">
+      <c r="G62" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="H62" s="29">
         <f>K49*1000/$D$25</f>
         <v>1.2342857142857142E-6</v>
       </c>
-      <c r="I62" s="38">
+      <c r="I62" s="32">
         <f>K49/J81</f>
         <v>4.32</v>
       </c>
-      <c r="J62" s="42">
+      <c r="J62" s="34">
         <f>H62/J81</f>
         <v>1.2342857142857142</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G64" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="H64" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="I64" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="J64" s="72"/>
+      <c r="G64" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="H64" s="69" t="s">
+        <v>217</v>
+      </c>
+      <c r="I64" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="J64" s="68"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G65" s="69"/>
-      <c r="H65" s="20"/>
+      <c r="G65" s="47"/>
+      <c r="H65" s="70"/>
       <c r="I65" s="73"/>
       <c r="J65" s="74"/>
     </row>
     <row r="66" spans="1:10" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G66" s="69"/>
-      <c r="H66" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="I66" s="75" t="s">
-        <v>177</v>
-      </c>
+      <c r="G66" s="47"/>
+      <c r="H66" s="70"/>
+      <c r="I66" s="75"/>
       <c r="J66" s="76"/>
     </row>
     <row r="67" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="70"/>
-      <c r="H67" s="34"/>
-      <c r="I67" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="J67" s="13" t="s">
-        <v>179</v>
+      <c r="G67" s="48"/>
+      <c r="H67" s="71"/>
+      <c r="I67" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G68" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="H68" s="13">
+        <v>170</v>
+      </c>
+      <c r="H68" s="12">
         <v>2</v>
       </c>
-      <c r="I68" s="13">
+      <c r="I68" s="12">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="J68" s="13">
+      <c r="J68" s="12">
         <v>0.04</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B69">
         <v>0.4</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H69" s="13">
+        <v>129</v>
+      </c>
+      <c r="H69" s="12">
         <v>3</v>
       </c>
-      <c r="I69" s="13">
+      <c r="I69" s="12">
         <v>0.15</v>
       </c>
-      <c r="J69" s="13">
+      <c r="J69" s="12">
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="8" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="H70" s="13">
+        <v>171</v>
+      </c>
+      <c r="H70" s="12">
         <v>1</v>
       </c>
-      <c r="I70" s="13">
+      <c r="I70" s="12">
         <v>1E-3</v>
       </c>
-      <c r="J70" s="13">
+      <c r="J70" s="12">
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="31.5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B71">
         <v>1.5</v>
       </c>
-      <c r="G71" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="H71" s="68">
+      <c r="G71" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="H71" s="46">
         <v>3</v>
       </c>
-      <c r="I71" s="68">
+      <c r="I71" s="46">
         <v>5</v>
       </c>
-      <c r="J71" s="68">
+      <c r="J71" s="46">
         <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
-      <c r="G72" s="31"/>
-      <c r="H72" s="69"/>
-      <c r="I72" s="69"/>
-      <c r="J72" s="69"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="47"/>
+      <c r="I72" s="47"/>
+      <c r="J72" s="47"/>
     </row>
     <row r="73" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H73" s="70"/>
-      <c r="I73" s="70"/>
-      <c r="J73" s="70"/>
+        <v>173</v>
+      </c>
+      <c r="H73" s="48"/>
+      <c r="I73" s="48"/>
+      <c r="J73" s="48"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G74" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="H74" s="68">
+      <c r="G74" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="H74" s="46">
         <v>4</v>
       </c>
-      <c r="I74" s="68">
+      <c r="I74" s="46">
         <v>0.03</v>
       </c>
-      <c r="J74" s="68">
+      <c r="J74" s="46">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G75" s="31"/>
-      <c r="H75" s="69"/>
-      <c r="I75" s="69"/>
-      <c r="J75" s="69"/>
+      <c r="G75" s="27"/>
+      <c r="H75" s="47"/>
+      <c r="I75" s="47"/>
+      <c r="J75" s="47"/>
     </row>
     <row r="76" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G76" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="H76" s="70"/>
-      <c r="I76" s="70"/>
-      <c r="J76" s="70"/>
+        <v>175</v>
+      </c>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
+      <c r="J76" s="48"/>
     </row>
     <row r="77" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G77" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="H77" s="13">
+        <v>176</v>
+      </c>
+      <c r="H77" s="12">
         <v>3</v>
       </c>
-      <c r="I77" s="13">
+      <c r="I77" s="12">
         <v>0.5</v>
       </c>
-      <c r="J77" s="13">
+      <c r="J77" s="12">
         <v>0.15</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="G78" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="H78" s="68">
+    <row r="78" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G78" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H78" s="46">
         <v>2</v>
       </c>
-      <c r="I78" s="68">
+      <c r="I78" s="46">
         <v>0.5</v>
       </c>
-      <c r="J78" s="68">
+      <c r="J78" s="46">
         <v>0.05</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G79" s="31"/>
-      <c r="H79" s="69"/>
-      <c r="I79" s="69"/>
-      <c r="J79" s="69"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="47"/>
+      <c r="I79" s="47"/>
+      <c r="J79" s="47"/>
     </row>
     <row r="80" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G80" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="H80" s="70"/>
-      <c r="I80" s="70"/>
-      <c r="J80" s="70"/>
+        <v>178</v>
+      </c>
+      <c r="H80" s="48"/>
+      <c r="I80" s="48"/>
+      <c r="J80" s="48"/>
     </row>
     <row r="81" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G81" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="H81" s="68">
+      <c r="G81" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="H81" s="46">
         <v>1</v>
       </c>
-      <c r="I81" s="77"/>
-      <c r="J81" s="80">
+      <c r="I81" s="49"/>
+      <c r="J81" s="52">
         <f>10^-6</f>
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="82" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G82" s="31"/>
-      <c r="H82" s="69"/>
-      <c r="I82" s="78"/>
-      <c r="J82" s="81"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="47"/>
+      <c r="I82" s="50"/>
+      <c r="J82" s="53"/>
     </row>
     <row r="83" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G83" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="H83" s="70"/>
-      <c r="I83" s="79"/>
-      <c r="J83" s="82"/>
-    </row>
-    <row r="84" spans="7:10" ht="51" thickBot="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="H83" s="48"/>
+      <c r="I83" s="51"/>
+      <c r="J83" s="54"/>
+    </row>
+    <row r="84" spans="7:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G84" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="H84" s="13">
+        <v>181</v>
+      </c>
+      <c r="H84" s="12">
         <v>3</v>
       </c>
-      <c r="I84" s="13">
+      <c r="I84" s="12">
         <v>0.5</v>
       </c>
-      <c r="J84" s="13">
+      <c r="J84" s="12">
         <v>0.15</v>
       </c>
     </row>
-    <row r="85" spans="7:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G85" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="H85" s="13">
+        <v>182</v>
+      </c>
+      <c r="H85" s="12">
         <v>2</v>
       </c>
-      <c r="I85" s="13">
+      <c r="I85" s="12">
         <v>0.4</v>
       </c>
-      <c r="J85" s="13">
+      <c r="J85" s="12">
         <v>0.06</v>
       </c>
     </row>
     <row r="86" spans="7:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="87" spans="7:10" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G87" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="H87" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="I87" s="52" t="s">
-        <v>195</v>
+      <c r="G87" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="H87" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="I87" s="43" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G88" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="H88" s="49">
+      <c r="G88" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="H88" s="40">
         <f>K33*1000/$D$25</f>
         <v>2048.9318982387476</v>
       </c>
-      <c r="I88" s="49">
+      <c r="I88" s="40">
         <f>K33/J71</f>
         <v>2390.4205479452053</v>
       </c>
     </row>
     <row r="89" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G89" s="46" t="s">
+      <c r="G89" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="H89" s="47">
+      <c r="H89" s="38">
         <f>K35*1000/$D$25</f>
         <v>8.2295107632093938</v>
       </c>
-      <c r="I89" s="47">
+      <c r="I89" s="38">
         <f>K35/J78</f>
         <v>576.0657534246576</v>
       </c>
     </row>
     <row r="90" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G90" s="46" t="s">
+      <c r="G90" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="H90" s="47">
+      <c r="H90" s="38">
         <f>K37*1000/$D$25</f>
         <v>98.788884540117408</v>
       </c>
-      <c r="I90" s="47">
+      <c r="I90" s="38">
         <f>K37/J68</f>
         <v>8644.0273972602736</v>
       </c>
     </row>
     <row r="91" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G91" s="46" t="s">
+      <c r="G91" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="H91" s="47">
+      <c r="H91" s="38">
         <f>K39*1000/$D$25</f>
         <v>3.6304109589041103</v>
       </c>
-      <c r="I91" s="47">
+      <c r="I91" s="38">
         <f>K39/J70</f>
         <v>42354.794520547955</v>
       </c>
     </row>
     <row r="92" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G92" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="H92" s="47">
+      <c r="G92" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="H92" s="38">
         <f>K41*1000/$D$25</f>
         <v>0</v>
       </c>
-      <c r="I92" s="47">
+      <c r="I92" s="38">
         <f>K41/J84</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="7:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="G93" s="47" t="s">
-        <v>196</v>
-      </c>
-      <c r="H93" s="47">
+      <c r="G93" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H93" s="38">
         <f>K43*1000/$D$25</f>
         <v>180.44853228962816</v>
       </c>
-      <c r="I93" s="47">
+      <c r="I93" s="38">
         <f>K43/J74</f>
         <v>126313.97260273973</v>
       </c>
     </row>
     <row r="94" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G94" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="H94" s="47">
+      <c r="G94" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="H94" s="38">
         <f>K45*1000/$D$25</f>
         <v>9.6868884540117435</v>
       </c>
-      <c r="I94" s="47">
+      <c r="I94" s="38">
         <f>K45/J69</f>
         <v>678.08219178082197</v>
       </c>
     </row>
     <row r="95" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G95" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="H95" s="47">
+      <c r="G95" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="H95" s="38">
         <f>K47*1000/$D$25</f>
         <v>0.29485714285714287</v>
       </c>
-      <c r="I95" s="47">
+      <c r="I95" s="38">
         <f>K47/J85</f>
         <v>17.200000000000003</v>
       </c>
     </row>
     <row r="96" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G96" s="48" t="s">
-        <v>197</v>
-      </c>
-      <c r="H96" s="50">
+      <c r="G96" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="H96" s="41">
         <f>K49*1000/$D$25</f>
         <v>1.2342857142857142E-6</v>
       </c>
-      <c r="I96" s="50">
+      <c r="I96" s="41">
         <f>K49/J81</f>
         <v>4.32</v>
       </c>
     </row>
     <row r="98" spans="7:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G98" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="H98" s="14" t="s">
+      <c r="G98" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H98" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I98" s="14" t="s">
+      <c r="I98" s="13" t="s">
         <v>73</v>
       </c>
     </row>
@@ -5265,38 +5434,19 @@
       <c r="I104" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="59">
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="J81:J83"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="H74:H76"/>
-    <mergeCell ref="I74:I76"/>
-    <mergeCell ref="J74:J76"/>
-    <mergeCell ref="G64:G67"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="K47:K48"/>
+  <mergeCells count="62">
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="H23:P23"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="P26:P27"/>
     <mergeCell ref="F31:G32"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="I31:I32"/>
@@ -5313,20 +5463,344 @@
     <mergeCell ref="J35:J36"/>
     <mergeCell ref="K35:K36"/>
     <mergeCell ref="F37:F38"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="H23:P23"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="N26:N27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="G64:G67"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="H64:H67"/>
+    <mergeCell ref="I64:J66"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="J74:J76"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="J81:J83"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24692D00-5DB8-4A31-A496-F2C39E600400}">
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" style="84" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="84" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="84" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="84" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="84" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="84" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="84"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="81" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="82" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" s="83" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1" s="83" t="s">
+        <v>214</v>
+      </c>
+      <c r="E1" s="83" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" s="82" t="s">
+        <v>222</v>
+      </c>
+      <c r="H1" s="96"/>
+    </row>
+    <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="85" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="86">
+        <f>Лист2!J33</f>
+        <v>2617510.5</v>
+      </c>
+      <c r="C2" s="86">
+        <f>Лист2!J71</f>
+        <v>3</v>
+      </c>
+      <c r="D2" s="86">
+        <f>1/C2</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E2" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="86">
+        <f>B2*E2*D2</f>
+        <v>436251.75</v>
+      </c>
+      <c r="G2" s="87"/>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="85" t="s">
+        <v>223</v>
+      </c>
+      <c r="B3" s="86">
+        <f>Лист2!J35</f>
+        <v>10513.2</v>
+      </c>
+      <c r="C3" s="86">
+        <f>Лист2!J78</f>
+        <v>0.05</v>
+      </c>
+      <c r="D3" s="86">
+        <f t="shared" ref="D3:D10" si="0">1/C3</f>
+        <v>20</v>
+      </c>
+      <c r="E3" s="86">
+        <v>1</v>
+      </c>
+      <c r="F3" s="86">
+        <f t="shared" ref="F3:F10" si="1">B3*E3*D3</f>
+        <v>210264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="85" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="86">
+        <f>Лист2!J37</f>
+        <v>126202.8</v>
+      </c>
+      <c r="C4" s="86">
+        <f>Лист2!J68</f>
+        <v>0.04</v>
+      </c>
+      <c r="D4" s="86">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="E4" s="86">
+        <v>1</v>
+      </c>
+      <c r="F4" s="86">
+        <f t="shared" si="1"/>
+        <v>3155070</v>
+      </c>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="85" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="86">
+        <f>Лист2!J39</f>
+        <v>4637.8500000000004</v>
+      </c>
+      <c r="C5" s="86">
+        <f>Лист2!J70</f>
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="D5" s="86">
+        <f t="shared" si="0"/>
+        <v>3333.3333333333335</v>
+      </c>
+      <c r="E5" s="86">
+        <v>4</v>
+      </c>
+      <c r="F5" s="86">
+        <f t="shared" si="1"/>
+        <v>61838000.000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="85" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" s="86">
+        <f>Лист2!J41</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="86">
+        <f>Лист2!J84</f>
+        <v>0.15</v>
+      </c>
+      <c r="D6" s="86">
+        <f t="shared" si="0"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="E6" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="85" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="86">
+        <f>Лист2!J43</f>
+        <v>230523</v>
+      </c>
+      <c r="C7" s="86">
+        <f>Лист2!J74</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D7" s="86">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E7" s="86">
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="86">
+        <f t="shared" si="1"/>
+        <v>115261500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="85" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="86">
+        <f>Лист2!J45</f>
+        <v>12375</v>
+      </c>
+      <c r="C8" s="86">
+        <f>Лист2!J69</f>
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="86">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E8" s="86">
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="86">
+        <f t="shared" si="1"/>
+        <v>618750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="86">
+        <f>Лист2!J47</f>
+        <v>376.68</v>
+      </c>
+      <c r="C9" s="86">
+        <f>Лист2!J85</f>
+        <v>0.06</v>
+      </c>
+      <c r="D9" s="86">
+        <f t="shared" si="0"/>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="E9" s="86">
+        <v>1</v>
+      </c>
+      <c r="F9" s="86">
+        <f t="shared" si="1"/>
+        <v>6278.0000000000009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="88" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" s="89">
+        <f>Лист2!J49</f>
+        <v>1.5767999999999999E-3</v>
+      </c>
+      <c r="C10" s="90">
+        <f>Лист2!J81</f>
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="D10" s="89">
+        <f t="shared" si="0"/>
+        <v>1000000</v>
+      </c>
+      <c r="E10" s="91">
+        <v>2.5</v>
+      </c>
+      <c r="F10" s="86">
+        <f t="shared" si="1"/>
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="92" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="95">
+        <f>SUM(F2:F10)</f>
+        <v>181530055.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" s="84">
+        <v>2.4</v>
+      </c>
+      <c r="C13" s="84" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" s="84">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B15" s="84">
+        <f>B13*B14*F11</f>
+        <v>731929184.78400004</v>
+      </c>
+      <c r="C15" s="84" t="s">
+        <v>229</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Лаб1.xlsx
+++ b/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Лаб1.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codespace\Файлы\1 курс\2 семестр\Экология\Лабы\18.02.25 - 1-ая лаба\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32554071-56B9-4BAA-AB0D-BC1F49420787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947FD314-2E73-42E8-BF56-60517F1B0A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_Hlk153478266" localSheetId="1">Лист2!$K$19</definedName>
   </definedNames>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="257">
   <si>
     <t>V(ов) л</t>
   </si>
@@ -1610,9 +1613,6 @@
     <t>Ку</t>
   </si>
   <si>
-    <t>Кс</t>
-  </si>
-  <si>
     <t>Кв</t>
   </si>
   <si>
@@ -1635,18 +1635,6 @@
   </si>
   <si>
     <t>fM</t>
-  </si>
-  <si>
-    <t>Класс опаности</t>
-  </si>
-  <si>
-    <t>Предельно допустимые концентрации, мг/м3 (ПДК)</t>
-  </si>
-  <si>
-    <t>Объем воздуха, необходимый для разбавления, м3 (Vвр)</t>
-  </si>
-  <si>
-    <t>Концентрация вредных веществ на учетной территории, мг/м3, (СВВ)</t>
   </si>
   <si>
     <r>
@@ -1840,6 +1828,418 @@
   </si>
   <si>
     <t>σ</t>
+  </si>
+  <si>
+    <t>Вредное</t>
+  </si>
+  <si>
+    <t>Концентрация вредных</t>
+  </si>
+  <si>
+    <t>Объем воздуха,</t>
+  </si>
+  <si>
+    <t>вещество</t>
+  </si>
+  <si>
+    <r>
+      <t>веществ на учетной территории, мг/м</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>, (С</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ВВ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>необходимый для разбавления, м</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (Vв</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>р</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Класс</t>
+  </si>
+  <si>
+    <t>Предельно допустимые</t>
+  </si>
+  <si>
+    <t>опасности</t>
+  </si>
+  <si>
+    <r>
+      <t>концентрации, мг/м</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t> (ПДК)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                  </t>
+  </si>
+  <si>
+    <t>Кт</t>
+  </si>
+  <si>
+    <r>
+      <t>Кду</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <vertAlign val="subscript"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>со</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>мг/м</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>К</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>тi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Доля транспорта в потоке (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>∙К</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>тi</t>
+    </r>
+  </si>
+  <si>
+    <t>ТУТ ХЗ ЧЁ С ЧЕМ СЧИТАТЬ БЛИН</t>
+  </si>
+  <si>
+    <t>Лёгкий грузовой</t>
+  </si>
+  <si>
+    <t>Тяжёлый грузовой</t>
+  </si>
+  <si>
+    <t>Легковой</t>
+  </si>
+  <si>
+    <t>Автобус</t>
+  </si>
+  <si>
+    <t>Пробеговое выделение вредных компонентов,  (Квв п)</t>
+  </si>
+  <si>
+    <r>
+      <t>Расчетные концентрации с учетом дополнительных условий, мг/м</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>, (Кду вв)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ПДК</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">СС,  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>мг/м</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>веществ на учетной территории, мг/м</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>, (С</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ВВ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Сажа (С)</t>
+  </si>
+  <si>
+    <t>&lt;-</t>
+  </si>
+  <si>
+    <t>тут всё поёбано в последнем столбце, поправишь</t>
   </si>
 </sst>
 </file>
@@ -1850,7 +2250,7 @@
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2046,6 +2446,52 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <vertAlign val="subscript"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2061,7 +2507,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -2340,29 +2786,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -2370,7 +2799,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2383,15 +2812,162 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2399,9 +2975,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2441,6 +3026,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2450,9 +3041,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2475,155 +3070,31 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2825,7 +3296,261 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>329045</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>126595</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Рисунок 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F019291-7812-463E-8603-277C9D9936EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11344275" y="26069925"/>
+          <a:ext cx="4234295" cy="621895"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>160812</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>681579</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>130096</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Рисунок 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB9DA910-29A3-453A-BCA8-8BF53FBD978D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9847737" y="24022051"/>
+          <a:ext cx="6083367" cy="606345"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>216479</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>510886</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>117868</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Рисунок 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D28D2D49-575E-4363-8769-544EE5B1AFEE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="12884729"/>
+          <a:ext cx="4397086" cy="520514"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>389660</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>54417</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Рисунок 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74619FEF-D390-41D1-923B-9F94B4646A6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="15087600"/>
+          <a:ext cx="4885459" cy="2997642"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>8659</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>34636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>147204</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>85031</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Рисунок 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B391DB68-C31E-498E-B6A4-1D29EFEF0C9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11162434" y="26637961"/>
+          <a:ext cx="4234295" cy="621895"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Лист1"/>
+      <sheetName val="Лист2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="Q1">
+            <v>1.65E-3</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27">
+            <v>19.761401157120002</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46">
+            <v>389.70873005464478</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3570,1871 +4295,2139 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:Q115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30" style="58" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="58" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="9.140625" style="58"/>
+    <col min="7" max="7" width="20" style="58" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" style="58" customWidth="1"/>
+    <col min="9" max="9" width="25" style="58" customWidth="1"/>
+    <col min="10" max="10" width="22" style="58" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" style="58" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" style="58" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="58" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="58"/>
+    <col min="15" max="15" width="19.28515625" style="58" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" style="58" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" style="58" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="58"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="Q1" s="1"/>
+      <c r="Q1" s="59"/>
     </row>
     <row r="2" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="58">
         <v>1.3380000000000001</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="58" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="59">
         <f>B4</f>
         <v>5</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="59">
         <f>B8</f>
         <v>75000</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="59"/>
+      <c r="L2" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
+      <c r="O2" s="59"/>
+      <c r="P2" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="59" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="58">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="K3" s="1" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="K3" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="59">
         <f>11/100</f>
         <v>0.11</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="59">
         <f>B10</f>
         <v>8250</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Q3" s="59" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="58">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="K4" s="1" t="s">
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="K4" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="M4" s="1"/>
-      <c r="O4" s="1" t="s">
+      <c r="M4" s="59"/>
+      <c r="O4" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1" t="s">
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="58">
         <v>15000</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="59" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="K5" s="1" t="s">
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="K5" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="M5" s="1"/>
-      <c r="O5" s="1" t="s">
+      <c r="M5" s="59"/>
+      <c r="O5" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1" t="s">
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="K6" s="1" t="s">
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="K6" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="M6" s="1"/>
-      <c r="O6" s="1" t="s">
+      <c r="M6" s="59"/>
+      <c r="O6" s="59" t="s">
         <v>77</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="P6" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="59"/>
     </row>
     <row r="7" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="58">
         <f>B4/B3</f>
         <v>0.25</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="K7" s="1" t="s">
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="K7" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="M7" s="1"/>
-      <c r="O7" s="1" t="s">
+      <c r="M7" s="59"/>
+      <c r="O7" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="P7" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="59"/>
     </row>
     <row r="8" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="58">
         <f>B4*B5</f>
         <v>75000</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="M8" s="1"/>
-      <c r="O8" s="1" t="s">
+      <c r="M8" s="59"/>
+      <c r="O8" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="P8" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="Q8" s="1"/>
+      <c r="Q8" s="59"/>
     </row>
     <row r="9" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O9" s="1" t="s">
+      <c r="O9" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="59">
         <f>SUM(P3:P8)</f>
         <v>8250</v>
       </c>
-      <c r="Q9" s="1"/>
+      <c r="Q9" s="59"/>
     </row>
     <row r="10" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="58">
         <f>B8*M3</f>
         <v>8250</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="60" t="s">
+      <c r="H10" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="61"/>
-      <c r="M10" s="62"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="30"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="58">
         <v>0.75</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="59"/>
-      <c r="H11" s="12" t="s">
+      <c r="G11" s="27"/>
+      <c r="H11" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="K11" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="65" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
-      <c r="G12" s="11" t="s">
+      <c r="A12" s="61"/>
+      <c r="G12" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="65">
         <v>395</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="65">
         <v>1.6</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="65">
         <v>20</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="65">
         <v>0.7</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="65">
         <v>34</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="65">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="58">
         <f>B10*B11</f>
         <v>6187.5</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="58" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="65">
         <v>9</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="65">
         <v>6</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="65">
         <v>33</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="65" t="s">
         <v>118</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="65">
         <v>20</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="65">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="58">
         <f>B13</f>
         <v>6187.5</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="58" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G15" s="24" t="s">
+      <c r="G15" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="67" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="58">
         <f>B14*B2</f>
         <v>8278.875</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="58" t="s">
         <v>104</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="65">
         <f>B4</f>
         <v>5</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="81">
         <f>H16*3</f>
         <v>15</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="81">
         <f>B21*I16*2</f>
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="58">
         <f>B16/1000</f>
         <v>8.2788749999999993</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
     </row>
     <row r="19" spans="1:16" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="58">
         <f>B20*B21</f>
         <v>1</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="58">
         <f>B4</f>
         <v>5</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="58">
         <f>0.2</f>
         <v>0.2</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="81"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="58">
         <f>H34</f>
         <v>0</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="74" t="s">
         <v>133</v>
       </c>
-      <c r="H23" s="63" t="s">
+      <c r="H23" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="65"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="33"/>
     </row>
     <row r="24" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="76" t="s">
         <v>135</v>
       </c>
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="J24" s="76" t="s">
         <v>137</v>
       </c>
-      <c r="K24" s="20" t="s">
+      <c r="K24" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="76" t="s">
         <v>139</v>
       </c>
-      <c r="M24" s="20" t="s">
+      <c r="M24" s="76" t="s">
         <v>113</v>
       </c>
-      <c r="N24" s="21" t="s">
+      <c r="N24" s="77" t="s">
         <v>140</v>
       </c>
-      <c r="O24" s="22" t="s">
+      <c r="O24" s="78" t="s">
         <v>141</v>
       </c>
-      <c r="P24" s="19" t="s">
+      <c r="P24" s="75" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="58">
         <f>B26*B27*B28</f>
         <v>3.4999999999999999E-6</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="58">
         <f>D26*D27*D28</f>
         <v>3500</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="76">
         <v>19.8</v>
       </c>
-      <c r="I25" s="20">
+      <c r="I25" s="76">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J25" s="20">
+      <c r="J25" s="76">
         <v>0.28000000000000003</v>
       </c>
-      <c r="K25" s="20" t="s">
+      <c r="K25" s="76" t="s">
         <v>142</v>
       </c>
-      <c r="L25" s="20">
+      <c r="L25" s="76">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M25" s="20">
+      <c r="M25" s="76">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="N25" s="21"/>
-      <c r="O25" s="22">
+      <c r="N25" s="77"/>
+      <c r="O25" s="78">
         <f>0.18*10^-6</f>
         <v>1.8E-7</v>
       </c>
-      <c r="P25" s="19">
+      <c r="P25" s="75">
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="58">
         <f>B21</f>
         <v>0.2</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="58">
         <f t="shared" ref="D26:D27" si="0">B26*1000</f>
         <v>200</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="G26" s="23" t="s">
+      <c r="G26" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="H26" s="66">
+      <c r="H26" s="34">
         <v>37.299999999999997</v>
       </c>
-      <c r="I26" s="66">
+      <c r="I26" s="34">
         <v>6.9</v>
       </c>
-      <c r="J26" s="66">
+      <c r="J26" s="34">
         <v>0.8</v>
       </c>
-      <c r="K26" s="66" t="s">
+      <c r="K26" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="L26" s="66">
+      <c r="L26" s="34">
         <v>0.19</v>
       </c>
-      <c r="M26" s="66">
+      <c r="M26" s="34">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="N26" s="66">
+      <c r="N26" s="34">
         <v>0.85</v>
       </c>
-      <c r="O26" s="66" t="s">
+      <c r="O26" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="P26" s="66">
+      <c r="P26" s="34">
         <v>0.23400000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="58" t="s">
         <v>163</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="58">
         <f>10/1000</f>
         <v>0.01</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="58">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="75" t="s">
         <v>144</v>
       </c>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="67"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="67"/>
-      <c r="P27" s="67"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
     </row>
     <row r="28" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="58" t="s">
         <v>164</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="58">
         <f>1.75/1000</f>
         <v>1.75E-3</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="58">
         <f>B28*1000</f>
         <v>1.75</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="75" t="s">
         <v>146</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="76">
         <v>28.5</v>
       </c>
-      <c r="I28" s="20">
+      <c r="I28" s="76">
         <v>3.5</v>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="76">
         <v>0.6</v>
       </c>
-      <c r="K28" s="20" t="s">
+      <c r="K28" s="76" t="s">
         <v>142</v>
       </c>
-      <c r="L28" s="20">
+      <c r="L28" s="76">
         <v>0.11</v>
       </c>
-      <c r="M28" s="20">
+      <c r="M28" s="76">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="N28" s="21">
+      <c r="N28" s="77">
         <v>0.88</v>
       </c>
-      <c r="O28" s="22" t="s">
+      <c r="O28" s="78" t="s">
         <v>147</v>
       </c>
-      <c r="P28" s="19">
+      <c r="P28" s="75">
         <v>0.83199999999999996</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="75" t="s">
         <v>148</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="76">
         <v>6.2</v>
       </c>
-      <c r="I29" s="20">
+      <c r="I29" s="76">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J29" s="20">
+      <c r="J29" s="76">
         <v>3.5</v>
       </c>
-      <c r="K29" s="20">
+      <c r="K29" s="76">
         <v>0.3</v>
       </c>
-      <c r="L29" s="20">
+      <c r="L29" s="76">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M29" s="20" t="s">
+      <c r="M29" s="76" t="s">
         <v>142</v>
       </c>
-      <c r="N29" s="21"/>
-      <c r="O29" s="22" t="s">
+      <c r="N29" s="77"/>
+      <c r="O29" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="P29" s="19">
+      <c r="P29" s="75">
         <v>4.72</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="61" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F31" s="56" t="s">
+      <c r="F31" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56" t="s">
+      <c r="G31" s="36"/>
+      <c r="H31" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="I31" s="56" t="s">
+      <c r="I31" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="J31" s="57" t="s">
+      <c r="J31" s="56" t="s">
         <v>124</v>
       </c>
-      <c r="K31" s="57"/>
+      <c r="K31" s="56"/>
     </row>
     <row r="32" spans="1:16" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="58">
         <v>16.7</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="1" t="s">
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="59" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="61" t="s">
         <v>190</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="58">
         <f>B17/B32</f>
         <v>0.49574101796407183</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="F33" s="55" t="s">
+      <c r="F33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="26" t="s">
+      <c r="G33" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H33" s="59">
         <f>B13*H12</f>
         <v>2444062.5</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I33" s="59">
         <f>B19*H25*24*365</f>
         <v>173448.00000000003</v>
       </c>
-      <c r="J33" s="55">
+      <c r="J33" s="37">
         <f>SUM(H33:I33)</f>
         <v>2617510.5</v>
       </c>
-      <c r="K33" s="55">
+      <c r="K33" s="37">
         <f>J33/365</f>
         <v>7171.2616438356163</v>
       </c>
-      <c r="N33" s="45"/>
+      <c r="N33" s="105"/>
     </row>
     <row r="34" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="61" t="s">
         <v>192</v>
       </c>
-      <c r="B34">
-        <f>Лист1!B46/10000</f>
+      <c r="B34" s="58">
+        <f>[1]Лист1!B46/10000</f>
         <v>3.8970873005464479E-2</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="F34" s="55"/>
-      <c r="G34" s="26" t="s">
+      <c r="F34" s="37"/>
+      <c r="G34" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="H34" s="1"/>
-      <c r="J34" s="55"/>
-      <c r="K34" s="55"/>
+      <c r="H34" s="59"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
     </row>
     <row r="35" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="61" t="s">
         <v>191</v>
       </c>
-      <c r="B35" s="44">
+      <c r="B35" s="104">
         <f>B34+B33</f>
         <v>0.53471189096953631</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="F35" s="55" t="s">
+      <c r="F35" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G35" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="59">
         <f>B13*I12</f>
         <v>9900</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I35" s="59">
         <f>B19*L25*24*365</f>
         <v>613.20000000000005</v>
       </c>
-      <c r="J35" s="55">
+      <c r="J35" s="37">
         <f t="shared" ref="J35" si="1">SUM(H35:I35)</f>
         <v>10513.2</v>
       </c>
-      <c r="K35" s="55">
+      <c r="K35" s="37">
         <f>J35/365</f>
         <v>28.80328767123288</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="26" t="s">
+      <c r="A36" s="61"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="37"/>
+      <c r="K36" s="37"/>
     </row>
     <row r="37" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="60" t="s">
         <v>194</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="58">
         <f>B35*1.25</f>
         <v>0.66838986371192033</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="F37" s="55" t="s">
+      <c r="F37" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="26" t="s">
+      <c r="G37" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="59">
         <f>B13*J12</f>
         <v>123750</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37" s="59">
         <f>B19*J25*24*365</f>
         <v>2452.8000000000002</v>
       </c>
-      <c r="J37" s="55">
+      <c r="J37" s="37">
         <f t="shared" ref="J37" si="2">SUM(H37:I37)</f>
         <v>126202.8</v>
       </c>
-      <c r="K37" s="55">
+      <c r="K37" s="37">
         <f>J37/365</f>
         <v>345.76109589041096</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F38" s="55"/>
-      <c r="G38" s="26" t="s">
+      <c r="F38" s="37"/>
+      <c r="G38" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="37"/>
+      <c r="K38" s="37"/>
     </row>
     <row r="39" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="61" t="s">
         <v>196</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="58">
         <v>12</v>
       </c>
-      <c r="F39" s="55" t="s">
+      <c r="F39" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="G39" s="26" t="s">
+      <c r="G39" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="59">
         <f>B13*K12</f>
         <v>4331.25</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I39" s="59">
         <f>B19*M25*24*365</f>
         <v>306.60000000000002</v>
       </c>
-      <c r="J39" s="55">
+      <c r="J39" s="37">
         <f t="shared" ref="J39" si="3">SUM(H39:I39)</f>
         <v>4637.8500000000004</v>
       </c>
-      <c r="K39" s="55">
+      <c r="K39" s="37">
         <f>J39/365</f>
         <v>12.706438356164385</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="61" t="s">
         <v>197</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="58">
         <v>16</v>
       </c>
-      <c r="F40" s="55"/>
-      <c r="G40" s="26" t="s">
+      <c r="F40" s="37"/>
+      <c r="G40" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="55"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="37"/>
+      <c r="K40" s="37"/>
     </row>
     <row r="41" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="60" t="s">
         <v>195</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="58">
         <f>B39+B40</f>
         <v>28</v>
       </c>
-      <c r="F41" s="55" t="s">
+      <c r="F41" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="G41" s="26" t="s">
+      <c r="G41" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="59">
         <f>B13*N25</f>
         <v>0</v>
       </c>
-      <c r="I41" s="1">
+      <c r="I41" s="59">
         <f>B19*N25</f>
         <v>0</v>
       </c>
-      <c r="J41" s="55">
+      <c r="J41" s="37">
         <f t="shared" ref="J41" si="4">SUM(H41:I41)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="55">
+      <c r="K41" s="37">
         <f>J41/365</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="60" t="s">
         <v>198</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="58">
         <f>B39+2*B40</f>
         <v>44</v>
       </c>
-      <c r="F42" s="55"/>
-      <c r="G42" s="26" t="s">
+      <c r="F42" s="37"/>
+      <c r="G42" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="55"/>
-      <c r="K42" s="55"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="37"/>
+      <c r="K42" s="37"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F43" s="55" t="s">
+      <c r="F43" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="G43" s="26" t="s">
+      <c r="G43" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43" s="59">
         <f>B13*L12</f>
         <v>210375</v>
       </c>
-      <c r="I43" s="1">
+      <c r="I43" s="59">
         <f>B19*I25*24*365</f>
         <v>20148</v>
       </c>
-      <c r="J43" s="55">
+      <c r="J43" s="37">
         <f t="shared" ref="J43" si="5">SUM(H43:I43)</f>
         <v>230523</v>
       </c>
-      <c r="K43" s="55">
+      <c r="K43" s="37">
         <f>J43/365</f>
         <v>631.56986301369864</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="60" t="s">
         <v>199</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="58">
         <f>B42/B41</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="F44" s="55"/>
-      <c r="G44" s="26" t="s">
+      <c r="F44" s="37"/>
+      <c r="G44" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="55"/>
-      <c r="K44" s="55"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37"/>
     </row>
     <row r="45" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="58">
         <f>J33/1000</f>
         <v>2617.5104999999999</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="58" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="55" t="s">
+      <c r="F45" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="G45" s="26" t="s">
+      <c r="G45" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="H45" s="1">
+      <c r="H45" s="59">
         <f>B13*M12</f>
         <v>12375</v>
       </c>
-      <c r="I45" s="1"/>
-      <c r="J45" s="55">
+      <c r="I45" s="59"/>
+      <c r="J45" s="37">
         <f t="shared" ref="J45" si="6">SUM(H45:I45)</f>
         <v>12375</v>
       </c>
-      <c r="K45" s="55">
+      <c r="K45" s="37">
         <f>J45/365</f>
         <v>33.904109589041099</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="B46">
-        <f>(B44*B45)+(Лист1!B27*1000)</f>
+      <c r="B46" s="58">
+        <f>(B44*B45)+([1]Лист1!B27*1000)</f>
         <v>23874.631942834287</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="58" t="s">
         <v>104</v>
       </c>
-      <c r="F46" s="55"/>
-      <c r="G46" s="26" t="s">
+      <c r="F46" s="37"/>
+      <c r="G46" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="55"/>
-      <c r="K46" s="55"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="37"/>
     </row>
     <row r="47" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="58">
         <f>B46/1000</f>
         <v>23.874631942834288</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="F47" s="55" t="s">
+      <c r="F47" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G47" s="26" t="s">
+      <c r="G47" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1">
+      <c r="H47" s="59"/>
+      <c r="I47" s="59">
         <f>B19*P25*24*365</f>
         <v>376.68</v>
       </c>
-      <c r="J47" s="55">
+      <c r="J47" s="37">
         <f t="shared" ref="J47" si="7">SUM(H47:I47)</f>
         <v>376.68</v>
       </c>
-      <c r="K47" s="55">
+      <c r="K47" s="37">
         <f>J47/365</f>
         <v>1.032</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F48" s="55"/>
-      <c r="G48" s="26" t="s">
+      <c r="F48" s="37"/>
+      <c r="G48" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="55"/>
-      <c r="K48" s="55"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="37"/>
+      <c r="K48" s="37"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F49" s="55" t="s">
+      <c r="F49" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="G49" s="26" t="s">
+      <c r="G49" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1">
+      <c r="H49" s="59"/>
+      <c r="I49" s="59">
         <f>B19*O25*24*365</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="J49" s="55">
+      <c r="J49" s="37">
         <f t="shared" ref="J49" si="8">SUM(H49:I49)</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="K49" s="55">
+      <c r="K49" s="37">
         <f>J49/365</f>
         <v>4.3200000000000001E-6</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F50" s="55"/>
-      <c r="G50" s="26" t="s">
+      <c r="F50" s="37"/>
+      <c r="G50" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="55"/>
-      <c r="K50" s="55"/>
+      <c r="H50" s="59"/>
+      <c r="I50" s="59"/>
+      <c r="J50" s="37"/>
+      <c r="K50" s="37"/>
     </row>
     <row r="51" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="B51">
-        <f>(B47/Лист1!Q1)/10000</f>
+      <c r="B51" s="58">
+        <f>(B47/[1]Лист1!Q1)/10000</f>
         <v>1.4469473904748054</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="58" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="60" t="s">
         <v>203</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="58">
         <f>B51*1.25</f>
         <v>1.8086842380935066</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="G52" s="69" t="s">
-        <v>153</v>
-      </c>
-      <c r="H52" s="69" t="s">
-        <v>220</v>
-      </c>
-      <c r="I52" s="79" t="s">
-        <v>219</v>
-      </c>
-      <c r="J52" s="78" t="s">
+      <c r="G52" s="62" t="s">
+        <v>228</v>
+      </c>
+      <c r="H52" s="64" t="s">
+        <v>229</v>
+      </c>
+      <c r="I52" s="69" t="s">
+        <v>230</v>
+      </c>
+      <c r="J52" s="91"/>
+    </row>
+    <row r="53" spans="1:11" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G53" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="H53" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="I53" s="87" t="s">
+        <v>233</v>
+      </c>
+      <c r="J53" s="95" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G53" s="71"/>
-      <c r="H53" s="71"/>
-      <c r="I53" s="80"/>
-      <c r="J53" s="77"/>
-    </row>
     <row r="54" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="60" t="s">
         <v>204</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="58">
         <f>SUM(I16:I21)</f>
         <v>15</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="58" t="s">
         <v>205</v>
       </c>
-      <c r="G54" s="16" t="s">
+      <c r="G54" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="H54" s="17">
+      <c r="H54" s="73">
         <f>K33*1000/$D$25</f>
         <v>2048.9318982387476</v>
       </c>
-      <c r="I54" s="30">
+      <c r="I54" s="88">
         <f>K33/J71</f>
         <v>2390.4205479452053</v>
       </c>
-      <c r="J54" s="35">
+      <c r="J54" s="94">
         <f>H54/J71</f>
         <v>682.97729941291584</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G55" s="10" t="s">
+      <c r="G55" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="H55" s="28">
+      <c r="H55" s="84">
         <f>K35*1000/$D$25</f>
         <v>8.2295107632093938</v>
       </c>
-      <c r="I55" s="31">
+      <c r="I55" s="89">
         <f>K35/J78</f>
         <v>576.0657534246576</v>
       </c>
-      <c r="J55" s="33">
+      <c r="J55" s="92">
         <f>H55/J78</f>
         <v>164.59021526418786</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G56" s="10" t="s">
+      <c r="G56" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="H56" s="28">
+      <c r="H56" s="84">
         <f>K37*1000/$D$25</f>
         <v>98.788884540117408</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="89">
         <f>K37/J68</f>
         <v>8644.0273972602736</v>
       </c>
-      <c r="J56" s="33">
+      <c r="J56" s="92">
         <f>H56/J68</f>
         <v>2469.7221135029354</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G57" s="10" t="s">
+      <c r="G57" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="H57" s="28">
+      <c r="H57" s="84">
         <f>K39*1000/$D$25</f>
         <v>3.6304109589041103</v>
       </c>
-      <c r="I57" s="31">
+      <c r="I57" s="89">
         <f>K39/J70</f>
         <v>42354.794520547955</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="92">
         <f>H57/J70</f>
         <v>12101.369863013702</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G58" s="10" t="s">
+      <c r="G58" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="H58" s="28">
+      <c r="H58" s="84">
         <f>K41*1000/$D$25</f>
         <v>0</v>
       </c>
-      <c r="I58" s="31">
+      <c r="I58" s="89">
         <f>K41/J84</f>
         <v>0</v>
       </c>
-      <c r="J58" s="33">
+      <c r="J58" s="92">
         <f>H58</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G59" s="10" t="s">
+      <c r="G59" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="H59" s="28">
+      <c r="H59" s="84">
         <f>K43*1000/$D$25</f>
         <v>180.44853228962816</v>
       </c>
-      <c r="I59" s="31">
+      <c r="I59" s="89">
         <f>K43/J74</f>
         <v>126313.97260273973</v>
       </c>
-      <c r="J59" s="33">
+      <c r="J59" s="92">
         <f>H59/J74</f>
         <v>36089.706457925633</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G60" s="10" t="s">
+      <c r="G60" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="H60" s="28">
+      <c r="H60" s="84">
         <f>K45*1000/$D$25</f>
         <v>9.6868884540117435</v>
       </c>
-      <c r="I60" s="31">
+      <c r="I60" s="89">
         <f>K45/J69</f>
         <v>678.08219178082197</v>
       </c>
-      <c r="J60" s="33">
+      <c r="J60" s="92">
         <f>H60/J69</f>
         <v>193.73776908023487</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G61" s="10" t="s">
+      <c r="G61" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="H61" s="28">
+      <c r="H61" s="84">
         <f>K47*1000/$D$25</f>
         <v>0.29485714285714287</v>
       </c>
-      <c r="I61" s="31">
+      <c r="I61" s="89">
         <f>K47/J85</f>
         <v>17.200000000000003</v>
       </c>
-      <c r="J61" s="33">
+      <c r="J61" s="92">
         <f>H61/J85</f>
         <v>4.9142857142857146</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G62" s="24" t="s">
+      <c r="G62" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="H62" s="29">
+      <c r="H62" s="85">
         <f>K49*1000/$D$25</f>
         <v>1.2342857142857142E-6</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="90">
         <f>K49/J81</f>
         <v>4.32</v>
       </c>
-      <c r="J62" s="34">
+      <c r="J62" s="93">
         <f>H62/J81</f>
         <v>1.2342857142857142</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G64" s="46" t="s">
+      <c r="G64" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="H64" s="69" t="s">
-        <v>217</v>
-      </c>
-      <c r="I64" s="72" t="s">
-        <v>218</v>
-      </c>
-      <c r="J64" s="68"/>
+      <c r="H64" s="64" t="s">
+        <v>234</v>
+      </c>
+      <c r="I64" s="50" t="s">
+        <v>235</v>
+      </c>
+      <c r="J64" s="51"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G65" s="47"/>
-      <c r="H65" s="70"/>
-      <c r="I65" s="73"/>
-      <c r="J65" s="74"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="72"/>
+      <c r="I65" s="52"/>
+      <c r="J65" s="53"/>
     </row>
     <row r="66" spans="1:10" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G66" s="47"/>
-      <c r="H66" s="70"/>
-      <c r="I66" s="75"/>
-      <c r="J66" s="76"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="71" t="s">
+        <v>236</v>
+      </c>
+      <c r="I66" s="54" t="s">
+        <v>237</v>
+      </c>
+      <c r="J66" s="55"/>
     </row>
     <row r="67" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="48"/>
-      <c r="H67" s="71"/>
-      <c r="I67" s="12" t="s">
+      <c r="G67" s="40"/>
+      <c r="H67" s="86"/>
+      <c r="I67" s="65" t="s">
         <v>168</v>
       </c>
-      <c r="J67" s="12" t="s">
+      <c r="J67" s="65" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="11" t="s">
+      <c r="G68" s="63" t="s">
         <v>170</v>
       </c>
-      <c r="H68" s="12">
+      <c r="H68" s="65">
         <v>2</v>
       </c>
-      <c r="I68" s="12">
+      <c r="I68" s="65">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="J68" s="12">
+      <c r="J68" s="65">
         <v>0.04</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="60" t="s">
         <v>206</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="58">
         <v>0.4</v>
       </c>
-      <c r="G69" s="11" t="s">
+      <c r="G69" s="63" t="s">
         <v>129</v>
       </c>
-      <c r="H69" s="12">
+      <c r="H69" s="65">
         <v>3</v>
       </c>
-      <c r="I69" s="12">
+      <c r="I69" s="65">
         <v>0.15</v>
       </c>
-      <c r="J69" s="12">
+      <c r="J69" s="65">
         <v>0.05</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="60" t="s">
         <v>207</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="58">
         <v>1</v>
       </c>
-      <c r="G70" s="11" t="s">
+      <c r="G70" s="63" t="s">
         <v>171</v>
       </c>
-      <c r="H70" s="12">
+      <c r="H70" s="65">
         <v>1</v>
       </c>
-      <c r="I70" s="12">
+      <c r="I70" s="65">
         <v>1E-3</v>
       </c>
-      <c r="J70" s="12">
+      <c r="J70" s="65">
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="60" t="s">
+        <v>238</v>
+      </c>
+      <c r="B71" s="58">
+        <v>1.5</v>
+      </c>
+      <c r="G71" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="H71" s="38">
+        <v>3</v>
+      </c>
+      <c r="I71" s="38">
+        <v>5</v>
+      </c>
+      <c r="J71" s="38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A72" s="60" t="s">
         <v>208</v>
       </c>
-      <c r="B71">
-        <v>1.5</v>
-      </c>
-      <c r="G71" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="H71" s="46">
+      <c r="B72" s="58">
+        <v>1</v>
+      </c>
+      <c r="G72" s="83"/>
+      <c r="H72" s="39"/>
+      <c r="I72" s="39"/>
+      <c r="J72" s="39"/>
+    </row>
+    <row r="73" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="60" t="s">
+        <v>209</v>
+      </c>
+      <c r="B73" s="58">
+        <v>1</v>
+      </c>
+      <c r="G73" s="63" t="s">
+        <v>173</v>
+      </c>
+      <c r="H73" s="40"/>
+      <c r="I73" s="40"/>
+      <c r="J73" s="40"/>
+    </row>
+    <row r="74" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G74" s="70" t="s">
+        <v>174</v>
+      </c>
+      <c r="H74" s="38">
+        <v>4</v>
+      </c>
+      <c r="I74" s="38">
+        <v>0.03</v>
+      </c>
+      <c r="J74" s="38">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A75" s="60" t="s">
+        <v>239</v>
+      </c>
+      <c r="B75" s="58">
+        <f>SUM(J99:J102)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G75" s="83"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
+      <c r="J75" s="39"/>
+    </row>
+    <row r="76" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G76" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
+      <c r="J76" s="40"/>
+    </row>
+    <row r="77" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="112" t="s">
+        <v>240</v>
+      </c>
+      <c r="B77" s="58">
+        <f>(0.5+0.01*B54*B75)*B69*B70*B71*B72*B73</f>
+        <v>0.33000000000000007</v>
+      </c>
+      <c r="C77" s="58" t="s">
+        <v>241</v>
+      </c>
+      <c r="G77" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="H77" s="65">
         <v>3</v>
       </c>
-      <c r="I71" s="46">
-        <v>5</v>
-      </c>
-      <c r="J71" s="46">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A72" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="B72">
+      <c r="I77" s="65">
+        <v>0.5</v>
+      </c>
+      <c r="J77" s="65">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G78" s="70" t="s">
+        <v>177</v>
+      </c>
+      <c r="H78" s="38">
+        <v>2</v>
+      </c>
+      <c r="I78" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="J78" s="38">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G79" s="83"/>
+      <c r="H79" s="39"/>
+      <c r="I79" s="39"/>
+      <c r="J79" s="39"/>
+    </row>
+    <row r="80" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G80" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
+      <c r="J80" s="40"/>
+    </row>
+    <row r="81" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G81" s="70" t="s">
+        <v>179</v>
+      </c>
+      <c r="H81" s="38">
         <v>1</v>
       </c>
-      <c r="G72" s="27"/>
-      <c r="H72" s="47"/>
-      <c r="I72" s="47"/>
-      <c r="J72" s="47"/>
-    </row>
-    <row r="73" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="G73" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="H73" s="48"/>
-      <c r="I73" s="48"/>
-      <c r="J73" s="48"/>
-    </row>
-    <row r="74" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G74" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="H74" s="46">
-        <v>4</v>
-      </c>
-      <c r="I74" s="46">
-        <v>0.03</v>
-      </c>
-      <c r="J74" s="46">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G75" s="27"/>
-      <c r="H75" s="47"/>
-      <c r="I75" s="47"/>
-      <c r="J75" s="47"/>
-    </row>
-    <row r="76" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G76" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
-      <c r="J76" s="48"/>
-    </row>
-    <row r="77" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G77" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="H77" s="12">
-        <v>3</v>
-      </c>
-      <c r="I77" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="J77" s="12">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G78" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H78" s="46">
-        <v>2</v>
-      </c>
-      <c r="I78" s="46">
-        <v>0.5</v>
-      </c>
-      <c r="J78" s="46">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G79" s="27"/>
-      <c r="H79" s="47"/>
-      <c r="I79" s="47"/>
-      <c r="J79" s="47"/>
-    </row>
-    <row r="80" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G80" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
-      <c r="J80" s="48"/>
-    </row>
-    <row r="81" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G81" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="H81" s="46">
-        <v>1</v>
-      </c>
-      <c r="I81" s="49"/>
-      <c r="J81" s="52">
+      <c r="I81" s="48"/>
+      <c r="J81" s="44">
         <f>10^-6</f>
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="82" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G82" s="27"/>
-      <c r="H82" s="47"/>
-      <c r="I82" s="50"/>
-      <c r="J82" s="53"/>
+      <c r="G82" s="83"/>
+      <c r="H82" s="39"/>
+      <c r="I82" s="47"/>
+      <c r="J82" s="45"/>
     </row>
     <row r="83" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G83" s="11" t="s">
+      <c r="G83" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="H83" s="48"/>
-      <c r="I83" s="51"/>
-      <c r="J83" s="54"/>
+      <c r="H83" s="40"/>
+      <c r="I83" s="49"/>
+      <c r="J83" s="46"/>
     </row>
     <row r="84" spans="7:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G84" s="11" t="s">
+      <c r="G84" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="H84" s="12">
+      <c r="H84" s="65">
         <v>3</v>
       </c>
-      <c r="I84" s="12">
+      <c r="I84" s="65">
         <v>0.5</v>
       </c>
-      <c r="J84" s="12">
+      <c r="J84" s="65">
         <v>0.15</v>
       </c>
     </row>
     <row r="85" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G85" s="11" t="s">
+      <c r="G85" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="H85" s="12">
+      <c r="H85" s="65">
         <v>2</v>
       </c>
-      <c r="I85" s="12">
+      <c r="I85" s="65">
         <v>0.4</v>
       </c>
-      <c r="J85" s="12">
+      <c r="J85" s="65">
         <v>0.06</v>
       </c>
     </row>
     <row r="86" spans="7:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="87" spans="7:10" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G87" s="42" t="s">
+      <c r="G87" s="102" t="s">
         <v>153</v>
       </c>
-      <c r="H87" s="43" t="s">
+      <c r="H87" s="103" t="s">
         <v>184</v>
       </c>
-      <c r="I87" s="43" t="s">
+      <c r="I87" s="103" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="88" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G88" s="36" t="s">
+      <c r="G88" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="H88" s="40">
+      <c r="H88" s="100">
         <f>K33*1000/$D$25</f>
         <v>2048.9318982387476</v>
       </c>
-      <c r="I88" s="40">
+      <c r="I88" s="100">
         <f>K33/J71</f>
         <v>2390.4205479452053</v>
       </c>
     </row>
     <row r="89" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G89" s="37" t="s">
+      <c r="G89" s="97" t="s">
         <v>111</v>
       </c>
-      <c r="H89" s="38">
+      <c r="H89" s="98">
         <f>K35*1000/$D$25</f>
         <v>8.2295107632093938</v>
       </c>
-      <c r="I89" s="38">
+      <c r="I89" s="98">
         <f>K35/J78</f>
         <v>576.0657534246576</v>
       </c>
     </row>
     <row r="90" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G90" s="37" t="s">
+      <c r="G90" s="97" t="s">
         <v>112</v>
       </c>
-      <c r="H90" s="38">
+      <c r="H90" s="98">
         <f>K37*1000/$D$25</f>
         <v>98.788884540117408</v>
       </c>
-      <c r="I90" s="38">
+      <c r="I90" s="98">
         <f>K37/J68</f>
         <v>8644.0273972602736</v>
       </c>
     </row>
     <row r="91" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G91" s="37" t="s">
+      <c r="G91" s="97" t="s">
         <v>113</v>
       </c>
-      <c r="H91" s="38">
+      <c r="H91" s="98">
         <f>K39*1000/$D$25</f>
         <v>3.6304109589041103</v>
       </c>
-      <c r="I91" s="38">
+      <c r="I91" s="98">
         <f>K39/J70</f>
         <v>42354.794520547955</v>
       </c>
     </row>
     <row r="92" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G92" s="37" t="s">
+      <c r="G92" s="97" t="s">
         <v>128</v>
       </c>
-      <c r="H92" s="38">
+      <c r="H92" s="98">
         <f>K41*1000/$D$25</f>
         <v>0</v>
       </c>
-      <c r="I92" s="38">
+      <c r="I92" s="98">
         <f>K41/J84</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="7:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="G93" s="38" t="s">
+      <c r="G93" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="H93" s="38">
+      <c r="H93" s="98">
         <f>K43*1000/$D$25</f>
         <v>180.44853228962816</v>
       </c>
-      <c r="I93" s="38">
+      <c r="I93" s="98">
         <f>K43/J74</f>
         <v>126313.97260273973</v>
       </c>
     </row>
     <row r="94" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G94" s="37" t="s">
+      <c r="G94" s="97" t="s">
         <v>129</v>
       </c>
-      <c r="H94" s="38">
+      <c r="H94" s="98">
         <f>K45*1000/$D$25</f>
         <v>9.6868884540117435</v>
       </c>
-      <c r="I94" s="38">
+      <c r="I94" s="98">
         <f>K45/J69</f>
         <v>678.08219178082197</v>
       </c>
     </row>
     <row r="95" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G95" s="37" t="s">
+      <c r="G95" s="97" t="s">
         <v>130</v>
       </c>
-      <c r="H95" s="38">
+      <c r="H95" s="98">
         <f>K47*1000/$D$25</f>
         <v>0.29485714285714287</v>
       </c>
-      <c r="I95" s="38">
+      <c r="I95" s="98">
         <f>K47/J85</f>
         <v>17.200000000000003</v>
       </c>
     </row>
     <row r="96" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G96" s="39" t="s">
+      <c r="G96" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="H96" s="41">
+      <c r="H96" s="101">
         <f>K49*1000/$D$25</f>
         <v>1.2342857142857142E-6</v>
       </c>
-      <c r="I96" s="41">
+      <c r="I96" s="101">
         <f>K49/J81</f>
         <v>4.32</v>
       </c>
     </row>
-    <row r="98" spans="7:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G98" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="H98" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="I98" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="99" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G99" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H99" s="1">
-        <f>B101</f>
+    <row r="98" spans="7:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G98" s="66" t="s">
+        <v>210</v>
+      </c>
+      <c r="H98" s="110" t="s">
+        <v>242</v>
+      </c>
+      <c r="I98" s="110" t="s">
+        <v>243</v>
+      </c>
+      <c r="J98" s="110" t="s">
+        <v>244</v>
+      </c>
+      <c r="K98" s="111" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="99" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G99" s="59" t="s">
+        <v>246</v>
+      </c>
+      <c r="H99" s="59">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I99" s="59">
+        <f>H3/$B$54</f>
         <v>0</v>
       </c>
-      <c r="I99" s="1">
-        <f>B105</f>
+      <c r="J99" s="59">
+        <f>H99*I99</f>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G100" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-    </row>
-    <row r="101" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G101" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G102" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-    </row>
-    <row r="103" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G103" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-    </row>
-    <row r="104" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G104" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
+    <row r="100" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G100" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="H100" s="59">
+        <v>0.2</v>
+      </c>
+      <c r="I100" s="59">
+        <f>H7/$B$54</f>
+        <v>0</v>
+      </c>
+      <c r="J100" s="59">
+        <f t="shared" ref="J100:J102" si="9">H100*I100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G101" s="59" t="s">
+        <v>248</v>
+      </c>
+      <c r="H101" s="59">
+        <v>1</v>
+      </c>
+      <c r="I101" s="59">
+        <f>H2/$B$54</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J101" s="59">
+        <f t="shared" si="9"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="102" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G102" s="59" t="s">
+        <v>249</v>
+      </c>
+      <c r="H102" s="59">
+        <v>3.7</v>
+      </c>
+      <c r="I102" s="59">
+        <f>H4/$B$54</f>
+        <v>0</v>
+      </c>
+      <c r="J102" s="59">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="7:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G104" s="107" t="s">
+        <v>228</v>
+      </c>
+      <c r="H104" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="I104" s="64" t="s">
+        <v>229</v>
+      </c>
+      <c r="J104" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="K104" s="41" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="105" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G105" s="108"/>
+      <c r="H105" s="57"/>
+      <c r="I105" s="72"/>
+      <c r="J105" s="39"/>
+      <c r="K105" s="42"/>
+    </row>
+    <row r="106" spans="7:11" ht="54" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G106" s="109" t="s">
+        <v>231</v>
+      </c>
+      <c r="H106" s="35"/>
+      <c r="I106" s="65" t="s">
+        <v>253</v>
+      </c>
+      <c r="J106" s="40"/>
+      <c r="K106" s="43"/>
+    </row>
+    <row r="107" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G107" s="107" t="s">
+        <v>110</v>
+      </c>
+      <c r="H107" s="62">
+        <f>H25</f>
+        <v>19.8</v>
+      </c>
+      <c r="I107" s="84">
+        <v>2048.9318982387476</v>
+      </c>
+      <c r="J107" s="64">
+        <f>(H107*$B$77)/$J$54</f>
+        <v>9.5669358346413529E-3</v>
+      </c>
+      <c r="K107" s="113">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G108" s="107" t="s">
+        <v>111</v>
+      </c>
+      <c r="H108" s="62">
+        <f>L25</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I108" s="84">
+        <v>8.2295107632093938</v>
+      </c>
+      <c r="J108" s="64">
+        <f t="shared" ref="J108:J115" si="10">(H108*$B$77)/$J$54</f>
+        <v>3.3822500425499734E-5</v>
+      </c>
+      <c r="K108" s="113">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="109" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G109" s="107" t="s">
+        <v>112</v>
+      </c>
+      <c r="H109" s="62">
+        <f>J25</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I109" s="84">
+        <v>98.788884540117408</v>
+      </c>
+      <c r="J109" s="64">
+        <f t="shared" si="10"/>
+        <v>1.3529000170199893E-4</v>
+      </c>
+      <c r="K109" s="113">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="110" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G110" s="107" t="s">
+        <v>127</v>
+      </c>
+      <c r="H110" s="62">
+        <f>M25</f>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I110" s="84">
+        <v>3.6304109589041103</v>
+      </c>
+      <c r="J110" s="64">
+        <f t="shared" si="10"/>
+        <v>1.6911250212749867E-5</v>
+      </c>
+      <c r="K110" s="113">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="111" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G111" s="107" t="s">
+        <v>128</v>
+      </c>
+      <c r="H111" s="62">
+        <f>N25</f>
+        <v>0</v>
+      </c>
+      <c r="I111" s="84">
+        <v>0</v>
+      </c>
+      <c r="J111" s="64">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K111" s="113">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="112" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G112" s="107" t="s">
+        <v>114</v>
+      </c>
+      <c r="H112" s="62">
+        <f>I25</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I112" s="84">
+        <v>180.44853228962816</v>
+      </c>
+      <c r="J112" s="64">
+        <f t="shared" si="10"/>
+        <v>1.1113107282664197E-3</v>
+      </c>
+      <c r="K112" s="113">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="7:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G113" s="107" t="s">
+        <v>254</v>
+      </c>
+      <c r="H113" s="62" t="str">
+        <f>K25</f>
+        <v>-</v>
+      </c>
+      <c r="I113" s="84">
+        <v>9.6868884540117435</v>
+      </c>
+      <c r="J113" s="64" t="e">
+        <f t="shared" si="10"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K113" s="113">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="114" spans="7:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G114" s="107" t="s">
+        <v>130</v>
+      </c>
+      <c r="H114" s="62">
+        <f>P25</f>
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I114" s="84">
+        <v>0.29485714285714287</v>
+      </c>
+      <c r="J114" s="64">
+        <f t="shared" si="10"/>
+        <v>2.0776678832806975E-5</v>
+      </c>
+      <c r="K114" s="113">
+        <v>0.06</v>
+      </c>
+      <c r="M114" s="58" t="s">
+        <v>255</v>
+      </c>
+      <c r="N114" s="58" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="115" spans="7:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G115" s="106" t="s">
+        <v>131</v>
+      </c>
+      <c r="H115" s="80">
+        <f>O25</f>
+        <v>1.8E-7</v>
+      </c>
+      <c r="I115" s="90">
+        <v>1.2342857142857142E-6</v>
+      </c>
+      <c r="J115" s="102">
+        <f t="shared" si="10"/>
+        <v>8.6972143951285028E-11</v>
+      </c>
+      <c r="K115" s="114">
+        <v>45818</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="H104:H106"/>
+    <mergeCell ref="J104:J106"/>
+    <mergeCell ref="K104:K106"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="H10:M10"/>
     <mergeCell ref="H23:P23"/>
@@ -5453,50 +6446,47 @@
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="J37:J38"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="K49:K50"/>
     <mergeCell ref="F33:F34"/>
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="K33:K34"/>
     <mergeCell ref="F35:F36"/>
     <mergeCell ref="J35:J36"/>
     <mergeCell ref="K35:K36"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="J81:J83"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="J74:J76"/>
+    <mergeCell ref="G64:G67"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="I66:J66"/>
     <mergeCell ref="F43:F44"/>
     <mergeCell ref="J43:J44"/>
     <mergeCell ref="K43:K44"/>
     <mergeCell ref="F45:F46"/>
     <mergeCell ref="J45:J46"/>
     <mergeCell ref="K45:K46"/>
-    <mergeCell ref="G64:G67"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="H64:H67"/>
-    <mergeCell ref="I64:J66"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="J52:J53"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="H74:H76"/>
-    <mergeCell ref="I74:I76"/>
-    <mergeCell ref="J74:J76"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="J81:J83"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="F37:F38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5508,296 +6498,296 @@
   <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="84" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="84" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="84" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="84" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="84" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="84" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="84"/>
+    <col min="1" max="1" width="11.7109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="82" t="s">
-        <v>221</v>
-      </c>
-      <c r="C1" s="83" t="s">
+      <c r="D1" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="D1" s="83" t="s">
+      <c r="E1" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="E1" s="83" t="s">
-        <v>215</v>
-      </c>
-      <c r="F1" s="82" t="s">
-        <v>222</v>
-      </c>
-      <c r="H1" s="96"/>
+      <c r="F1" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="86">
+      <c r="B2" s="15">
         <f>Лист2!J33</f>
         <v>2617510.5</v>
       </c>
-      <c r="C2" s="86">
+      <c r="C2" s="15">
         <f>Лист2!J71</f>
         <v>3</v>
       </c>
-      <c r="D2" s="86">
+      <c r="D2" s="15">
         <f>1/C2</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="E2" s="86">
+      <c r="E2" s="15">
         <v>0.5</v>
       </c>
-      <c r="F2" s="86">
+      <c r="F2" s="15">
         <f>B2*E2*D2</f>
         <v>436251.75</v>
       </c>
-      <c r="G2" s="87"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="85" t="s">
-        <v>223</v>
-      </c>
-      <c r="B3" s="86">
+      <c r="A3" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3" s="15">
         <f>Лист2!J35</f>
         <v>10513.2</v>
       </c>
-      <c r="C3" s="86">
+      <c r="C3" s="15">
         <f>Лист2!J78</f>
         <v>0.05</v>
       </c>
-      <c r="D3" s="86">
+      <c r="D3" s="15">
         <f t="shared" ref="D3:D10" si="0">1/C3</f>
         <v>20</v>
       </c>
-      <c r="E3" s="86">
+      <c r="E3" s="15">
         <v>1</v>
       </c>
-      <c r="F3" s="86">
+      <c r="F3" s="15">
         <f t="shared" ref="F3:F10" si="1">B3*E3*D3</f>
         <v>210264</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="85" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="86">
+      <c r="A4" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="15">
         <f>Лист2!J37</f>
         <v>126202.8</v>
       </c>
-      <c r="C4" s="86">
+      <c r="C4" s="15">
         <f>Лист2!J68</f>
         <v>0.04</v>
       </c>
-      <c r="D4" s="86">
+      <c r="D4" s="15">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="15">
         <v>1</v>
       </c>
-      <c r="F4" s="86">
+      <c r="F4" s="15">
         <f t="shared" si="1"/>
         <v>3155070</v>
       </c>
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="86">
+      <c r="B5" s="15">
         <f>Лист2!J39</f>
         <v>4637.8500000000004</v>
       </c>
-      <c r="C5" s="86">
+      <c r="C5" s="15">
         <f>Лист2!J70</f>
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="15">
         <f t="shared" si="0"/>
         <v>3333.3333333333335</v>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="15">
         <v>4</v>
       </c>
-      <c r="F5" s="86">
+      <c r="F5" s="15">
         <f t="shared" si="1"/>
         <v>61838000.000000007</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="85" t="s">
-        <v>225</v>
-      </c>
-      <c r="B6" s="86">
+      <c r="A6" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="15">
         <f>Лист2!J41</f>
         <v>0</v>
       </c>
-      <c r="C6" s="86">
+      <c r="C6" s="15">
         <f>Лист2!J84</f>
         <v>0.15</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="15">
         <f t="shared" si="0"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="15">
         <v>0.5</v>
       </c>
-      <c r="F6" s="86">
+      <c r="F6" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="85" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="86">
+      <c r="A7" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" s="15">
         <f>Лист2!J43</f>
         <v>230523</v>
       </c>
-      <c r="C7" s="86">
+      <c r="C7" s="15">
         <f>Лист2!J74</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="15">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="15">
         <v>2.5</v>
       </c>
-      <c r="F7" s="86">
+      <c r="F7" s="15">
         <f t="shared" si="1"/>
         <v>115261500</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="B8" s="86">
+      <c r="B8" s="15">
         <f>Лист2!J45</f>
         <v>12375</v>
       </c>
-      <c r="C8" s="86">
+      <c r="C8" s="15">
         <f>Лист2!J69</f>
         <v>0.05</v>
       </c>
-      <c r="D8" s="86">
+      <c r="D8" s="15">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="15">
         <v>2.5</v>
       </c>
-      <c r="F8" s="86">
+      <c r="F8" s="15">
         <f t="shared" si="1"/>
         <v>618750</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="86">
+      <c r="B9" s="15">
         <f>Лист2!J47</f>
         <v>376.68</v>
       </c>
-      <c r="C9" s="86">
+      <c r="C9" s="15">
         <f>Лист2!J85</f>
         <v>0.06</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="15">
         <f t="shared" si="0"/>
         <v>16.666666666666668</v>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="15">
         <v>1</v>
       </c>
-      <c r="F9" s="86">
+      <c r="F9" s="15">
         <f t="shared" si="1"/>
         <v>6278.0000000000009</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88" t="s">
-        <v>227</v>
-      </c>
-      <c r="B10" s="89">
+      <c r="A10" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="18">
         <f>Лист2!J49</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="C10" s="90">
+      <c r="C10" s="19">
         <f>Лист2!J81</f>
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="D10" s="89">
+      <c r="D10" s="18">
         <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
-      <c r="E10" s="91">
+      <c r="E10" s="20">
         <v>2.5</v>
       </c>
-      <c r="F10" s="86">
+      <c r="F10" s="15">
         <f t="shared" si="1"/>
         <v>3942</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="92" t="s">
-        <v>216</v>
-      </c>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="95">
+      <c r="A11" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="24">
         <f>SUM(F2:F10)</f>
         <v>181530055.75</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="B13" s="84">
+        <v>225</v>
+      </c>
+      <c r="B13" s="13">
         <v>2.4</v>
       </c>
-      <c r="C13" s="84" t="s">
-        <v>231</v>
+      <c r="C13" s="13" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="B14" s="84">
+        <v>227</v>
+      </c>
+      <c r="B14" s="13">
         <v>1.68</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="B15" s="84">
+        <v>223</v>
+      </c>
+      <c r="B15" s="13">
         <f>B13*B14*F11</f>
         <v>731929184.78400004</v>
       </c>
-      <c r="C15" s="84" t="s">
-        <v>229</v>
+      <c r="C15" s="13" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Лаб1.xlsx
+++ b/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Лаб1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codespace\Файлы\1 курс\2 семестр\Экология\Лабы\18.02.25 - 1-ая лаба\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luvidmi\Desktop\gitRep\Codespace\Файлы\1 курс\2 семестр\Экология\Лабы\18.02.25 - 1-ая лаба\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947FD314-2E73-42E8-BF56-60517F1B0A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D4D92A-B803-4791-A10F-16150C706994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="254">
   <si>
     <t>V(ов) л</t>
   </si>
@@ -2105,9 +2105,6 @@
     </r>
   </si>
   <si>
-    <t>ТУТ ХЗ ЧЁ С ЧЕМ СЧИТАТЬ БЛИН</t>
-  </si>
-  <si>
     <t>Лёгкий грузовой</t>
   </si>
   <si>
@@ -2234,12 +2231,6 @@
   </si>
   <si>
     <t>Сажа (С)</t>
-  </si>
-  <si>
-    <t>&lt;-</t>
-  </si>
-  <si>
-    <t>тут всё поёбано в последнем столбце, поправишь</t>
   </si>
 </sst>
 </file>
@@ -2250,12 +2241,20 @@
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2797,302 +2796,302 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3298,50 +3297,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>329045</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>126595</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Рисунок 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F019291-7812-463E-8603-277C9D9936EC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11344275" y="26069925"/>
-          <a:ext cx="4234295" cy="621895"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>160812</xdr:colOff>
       <xdr:row>88</xdr:row>
@@ -3464,50 +3419,6 @@
         <a:xfrm>
           <a:off x="1" y="15087600"/>
           <a:ext cx="4885459" cy="2997642"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>8659</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>34636</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>147204</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>85031</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Рисунок 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B391DB68-C31E-498E-B6A4-1D29EFEF0C9E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11162434" y="26637961"/>
-          <a:ext cx="4234295" cy="621895"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4298,2133 +4209,2171 @@
   <dimension ref="A1:Q115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" style="58" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="58" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="9.140625" style="58"/>
-    <col min="7" max="7" width="20" style="58" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" style="58" customWidth="1"/>
-    <col min="9" max="9" width="25" style="58" customWidth="1"/>
-    <col min="10" max="10" width="22" style="58" customWidth="1"/>
-    <col min="11" max="11" width="19.28515625" style="58" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" style="58" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" style="58" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="58"/>
-    <col min="15" max="15" width="19.28515625" style="58" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" style="58" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" style="58" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="58"/>
+    <col min="1" max="1" width="30" style="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="9.140625" style="26"/>
+    <col min="7" max="7" width="20" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" style="26" customWidth="1"/>
+    <col min="9" max="9" width="25" style="26" customWidth="1"/>
+    <col min="10" max="10" width="22" style="26" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="26"/>
+    <col min="15" max="15" width="19.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" style="26" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="K1" s="59" t="s">
+      <c r="K1" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="59" t="s">
+      <c r="L1" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="M1" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="O1" s="59" t="s">
+      <c r="O1" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="P1" s="59" t="s">
+      <c r="P1" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="Q1" s="59"/>
+      <c r="Q1" s="27"/>
     </row>
     <row r="2" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="58">
+      <c r="B2" s="26">
         <v>1.3380000000000001</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="59" t="s">
+      <c r="G2" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="59">
+      <c r="H2" s="27">
         <f>B4</f>
         <v>5</v>
       </c>
-      <c r="I2" s="59">
+      <c r="I2" s="27">
         <f>B8</f>
         <v>75000</v>
       </c>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59" t="s">
+      <c r="K2" s="27"/>
+      <c r="L2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="M2" s="59" t="s">
+      <c r="M2" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59" t="s">
+      <c r="O2" s="27"/>
+      <c r="P2" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="Q2" s="59" t="s">
+      <c r="Q2" s="27" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="26">
         <v>20</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="G3" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="K3" s="59" t="s">
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="K3" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="59" t="s">
+      <c r="L3" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="M3" s="59">
+      <c r="M3" s="27">
         <f>11/100</f>
         <v>0.11</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="P3" s="59">
+      <c r="P3" s="27">
         <f>B10</f>
         <v>8250</v>
       </c>
-      <c r="Q3" s="59" t="s">
+      <c r="Q3" s="27" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="58">
+      <c r="B4" s="26">
         <v>5</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="59" t="s">
+      <c r="G4" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="K4" s="59" t="s">
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="K4" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="59" t="s">
+      <c r="L4" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="M4" s="59"/>
-      <c r="O4" s="59" t="s">
+      <c r="M4" s="27"/>
+      <c r="O4" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="59" t="s">
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="58">
+      <c r="B5" s="26">
         <v>15000</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="59" t="s">
+      <c r="G5" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="K5" s="59" t="s">
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="K5" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="L5" s="59" t="s">
+      <c r="L5" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="M5" s="59"/>
-      <c r="O5" s="59" t="s">
+      <c r="M5" s="27"/>
+      <c r="O5" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="P5" s="59"/>
-      <c r="Q5" s="59" t="s">
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G6" s="59" t="s">
+      <c r="G6" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="K6" s="59" t="s">
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="K6" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="L6" s="59" t="s">
+      <c r="L6" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="M6" s="59"/>
-      <c r="O6" s="59" t="s">
+      <c r="M6" s="27"/>
+      <c r="O6" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="P6" s="59" t="s">
+      <c r="P6" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="Q6" s="59"/>
+      <c r="Q6" s="27"/>
     </row>
     <row r="7" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="58">
+      <c r="B7" s="26">
         <f>B4/B3</f>
         <v>0.25</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="59" t="s">
+      <c r="G7" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="K7" s="59" t="s">
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="K7" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="L7" s="59" t="s">
+      <c r="L7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="M7" s="59"/>
-      <c r="O7" s="59" t="s">
+      <c r="M7" s="27"/>
+      <c r="O7" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="P7" s="59" t="s">
+      <c r="P7" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="Q7" s="59"/>
+      <c r="Q7" s="27"/>
     </row>
     <row r="8" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="58">
+      <c r="B8" s="26">
         <f>B4*B5</f>
         <v>75000</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="59" t="s">
+      <c r="K8" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="L8" s="59" t="s">
+      <c r="L8" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="M8" s="59"/>
-      <c r="O8" s="59" t="s">
+      <c r="M8" s="27"/>
+      <c r="O8" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="P8" s="59" t="s">
+      <c r="P8" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="Q8" s="59"/>
+      <c r="Q8" s="27"/>
     </row>
     <row r="9" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O9" s="59" t="s">
+      <c r="O9" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="P9" s="59">
+      <c r="P9" s="27">
         <f>SUM(P3:P8)</f>
         <v>8250</v>
       </c>
-      <c r="Q9" s="59"/>
+      <c r="Q9" s="27"/>
     </row>
     <row r="10" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="61" t="s">
+      <c r="A10" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="58">
+      <c r="B10" s="26">
         <f>B8*M3</f>
         <v>8250</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="91" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="30"/>
+      <c r="I10" s="94"/>
+      <c r="J10" s="94"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="94"/>
+      <c r="M10" s="95"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="58">
+      <c r="B11" s="26">
         <v>0.75</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="65" t="s">
+      <c r="G11" s="92"/>
+      <c r="H11" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="I11" s="65" t="s">
+      <c r="I11" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="J11" s="65" t="s">
+      <c r="J11" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="65" t="s">
+      <c r="K11" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="L11" s="65" t="s">
+      <c r="L11" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="M11" s="65" t="s">
+      <c r="M11" s="33" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="61"/>
-      <c r="G12" s="63" t="s">
+      <c r="A12" s="29"/>
+      <c r="G12" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="65">
+      <c r="H12" s="33">
         <v>395</v>
       </c>
-      <c r="I12" s="65">
+      <c r="I12" s="33">
         <v>1.6</v>
       </c>
-      <c r="J12" s="65">
+      <c r="J12" s="33">
         <v>20</v>
       </c>
-      <c r="K12" s="65">
+      <c r="K12" s="33">
         <v>0.7</v>
       </c>
-      <c r="L12" s="65">
+      <c r="L12" s="33">
         <v>34</v>
       </c>
-      <c r="M12" s="65">
+      <c r="M12" s="33">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="58">
+      <c r="B13" s="26">
         <f>B10*B11</f>
         <v>6187.5</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="H13" s="65">
+      <c r="H13" s="33">
         <v>9</v>
       </c>
-      <c r="I13" s="65">
+      <c r="I13" s="33">
         <v>6</v>
       </c>
-      <c r="J13" s="65">
+      <c r="J13" s="33">
         <v>33</v>
       </c>
-      <c r="K13" s="65" t="s">
+      <c r="K13" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="L13" s="65">
+      <c r="L13" s="33">
         <v>20</v>
       </c>
-      <c r="M13" s="65">
+      <c r="M13" s="33">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="58">
+      <c r="B14" s="26">
         <f>B13</f>
         <v>6187.5</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="26" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G15" s="80" t="s">
+      <c r="G15" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="H15" s="67" t="s">
+      <c r="H15" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="I15" s="67" t="s">
+      <c r="I15" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="J15" s="67" t="s">
+      <c r="J15" s="35" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="61" t="s">
+      <c r="A16" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="58">
+      <c r="B16" s="26">
         <f>B14*B2</f>
         <v>8278.875</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="G16" s="63" t="s">
+      <c r="G16" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="65">
+      <c r="H16" s="33">
         <f>B4</f>
         <v>5</v>
       </c>
-      <c r="I16" s="81">
+      <c r="I16" s="49">
         <f>H16*3</f>
         <v>15</v>
       </c>
-      <c r="J16" s="81">
+      <c r="J16" s="49">
         <f>B21*I16*2</f>
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="58">
+      <c r="B17" s="26">
         <f>B16/1000</f>
         <v>8.2788749999999993</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="G17" s="63" t="s">
+      <c r="G17" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="65"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G18" s="63" t="s">
+      <c r="G18" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="H18" s="65"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="1:16" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="58">
+      <c r="B19" s="26">
         <f>B20*B21</f>
         <v>1</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="G19" s="63" t="s">
+      <c r="G19" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="H19" s="65"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="81"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="58" t="s">
+      <c r="A20" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="B20" s="58">
+      <c r="B20" s="26">
         <f>B4</f>
         <v>5</v>
       </c>
-      <c r="G20" s="63" t="s">
+      <c r="G20" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="H20" s="65"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="58" t="s">
+      <c r="A21" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="B21" s="58">
+      <c r="B21" s="26">
         <f>0.2</f>
         <v>0.2</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="G21" s="63" t="s">
+      <c r="G21" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="H21" s="65"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="B23" s="58">
+      <c r="B23" s="26">
         <f>H34</f>
         <v>0</v>
       </c>
-      <c r="G23" s="74" t="s">
+      <c r="G23" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="H23" s="31" t="s">
+      <c r="H23" s="96" t="s">
         <v>134</v>
       </c>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-      <c r="P23" s="33"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="97"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="97"/>
+      <c r="M23" s="97"/>
+      <c r="N23" s="97"/>
+      <c r="O23" s="97"/>
+      <c r="P23" s="98"/>
     </row>
     <row r="24" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G24" s="75" t="s">
+      <c r="G24" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="H24" s="76" t="s">
+      <c r="H24" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="I24" s="76" t="s">
+      <c r="I24" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="J24" s="76" t="s">
+      <c r="J24" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="K24" s="76" t="s">
+      <c r="K24" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="L24" s="76" t="s">
+      <c r="L24" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="M24" s="76" t="s">
+      <c r="M24" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="N24" s="77" t="s">
+      <c r="N24" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="O24" s="78" t="s">
+      <c r="O24" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="P24" s="75" t="s">
+      <c r="P24" s="43" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="58">
+      <c r="B25" s="26">
         <f>B26*B27*B28</f>
         <v>3.4999999999999999E-6</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="26">
         <f>D26*D27*D28</f>
         <v>3500</v>
       </c>
-      <c r="E25" s="58" t="s">
+      <c r="E25" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="G25" s="75" t="s">
+      <c r="G25" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="76">
+      <c r="H25" s="44">
         <v>19.8</v>
       </c>
-      <c r="I25" s="76">
+      <c r="I25" s="44">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J25" s="76">
+      <c r="J25" s="44">
         <v>0.28000000000000003</v>
       </c>
-      <c r="K25" s="76" t="s">
+      <c r="K25" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="L25" s="76">
+      <c r="L25" s="44">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M25" s="76">
+      <c r="M25" s="44">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="N25" s="77"/>
-      <c r="O25" s="78">
+      <c r="N25" s="45"/>
+      <c r="O25" s="46">
         <f>0.18*10^-6</f>
         <v>1.8E-7</v>
       </c>
-      <c r="P25" s="75">
+      <c r="P25" s="43">
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="58">
+      <c r="B26" s="26">
         <f>B21</f>
         <v>0.2</v>
       </c>
-      <c r="D26" s="58">
+      <c r="D26" s="26">
         <f t="shared" ref="D26:D27" si="0">B26*1000</f>
         <v>200</v>
       </c>
-      <c r="E26" s="58" t="s">
+      <c r="E26" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="G26" s="79" t="s">
+      <c r="G26" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="82">
         <v>37.299999999999997</v>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="82">
         <v>6.9</v>
       </c>
-      <c r="J26" s="34">
+      <c r="J26" s="82">
         <v>0.8</v>
       </c>
-      <c r="K26" s="34" t="s">
+      <c r="K26" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="82">
         <v>0.19</v>
       </c>
-      <c r="M26" s="34">
+      <c r="M26" s="82">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="N26" s="34">
+      <c r="N26" s="82">
         <v>0.85</v>
       </c>
-      <c r="O26" s="34" t="s">
+      <c r="O26" s="82" t="s">
         <v>145</v>
       </c>
-      <c r="P26" s="34">
+      <c r="P26" s="82">
         <v>0.23400000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="58" t="s">
+      <c r="A27" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="B27" s="58">
+      <c r="B27" s="26">
         <f>10/1000</f>
         <v>0.01</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="D27" s="58">
+      <c r="D27" s="26">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E27" s="58" t="s">
+      <c r="E27" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="G27" s="75" t="s">
+      <c r="G27" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="84"/>
+      <c r="P27" s="84"/>
     </row>
     <row r="28" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="58" t="s">
+      <c r="A28" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="B28" s="58">
+      <c r="B28" s="26">
         <f>1.75/1000</f>
         <v>1.75E-3</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="D28" s="58">
+      <c r="D28" s="26">
         <f>B28*1000</f>
         <v>1.75</v>
       </c>
-      <c r="E28" s="58" t="s">
+      <c r="E28" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="G28" s="75" t="s">
+      <c r="G28" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="H28" s="76">
+      <c r="H28" s="44">
         <v>28.5</v>
       </c>
-      <c r="I28" s="76">
+      <c r="I28" s="44">
         <v>3.5</v>
       </c>
-      <c r="J28" s="76">
+      <c r="J28" s="44">
         <v>0.6</v>
       </c>
-      <c r="K28" s="76" t="s">
+      <c r="K28" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="L28" s="76">
+      <c r="L28" s="44">
         <v>0.11</v>
       </c>
-      <c r="M28" s="76">
+      <c r="M28" s="44">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="N28" s="77">
+      <c r="N28" s="45">
         <v>0.88</v>
       </c>
-      <c r="O28" s="78" t="s">
+      <c r="O28" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="P28" s="75">
+      <c r="P28" s="43">
         <v>0.83199999999999996</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G29" s="75" t="s">
+      <c r="G29" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="H29" s="76">
+      <c r="H29" s="44">
         <v>6.2</v>
       </c>
-      <c r="I29" s="76">
+      <c r="I29" s="44">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J29" s="76">
+      <c r="J29" s="44">
         <v>3.5</v>
       </c>
-      <c r="K29" s="76">
+      <c r="K29" s="44">
         <v>0.3</v>
       </c>
-      <c r="L29" s="76">
+      <c r="L29" s="44">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M29" s="76" t="s">
+      <c r="M29" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="N29" s="77"/>
-      <c r="O29" s="78" t="s">
+      <c r="N29" s="45"/>
+      <c r="O29" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="P29" s="75">
+      <c r="P29" s="43">
         <v>4.72</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A30" s="61" t="s">
+      <c r="A30" s="29" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F31" s="36" t="s">
+      <c r="F31" s="99" t="s">
         <v>153</v>
       </c>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36" t="s">
+      <c r="G31" s="99"/>
+      <c r="H31" s="99" t="s">
         <v>122</v>
       </c>
-      <c r="I31" s="36" t="s">
+      <c r="I31" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="J31" s="56" t="s">
+      <c r="J31" s="100" t="s">
         <v>124</v>
       </c>
-      <c r="K31" s="56"/>
+      <c r="K31" s="100"/>
     </row>
     <row r="32" spans="1:16" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A32" s="61" t="s">
+      <c r="A32" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="B32" s="58">
+      <c r="B32" s="26">
         <v>16.7</v>
       </c>
-      <c r="C32" s="58" t="s">
+      <c r="C32" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="59" t="s">
+      <c r="F32" s="99"/>
+      <c r="G32" s="99"/>
+      <c r="H32" s="99"/>
+      <c r="I32" s="99"/>
+      <c r="J32" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="K32" s="59" t="s">
+      <c r="K32" s="27" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A33" s="61" t="s">
+      <c r="A33" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="B33" s="58">
+      <c r="B33" s="26">
         <f>B17/B32</f>
         <v>0.49574101796407183</v>
       </c>
-      <c r="C33" s="58" t="s">
+      <c r="C33" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F33" s="37" t="s">
+      <c r="F33" s="101" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="82" t="s">
+      <c r="G33" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H33" s="59">
+      <c r="H33" s="27">
         <f>B13*H12</f>
         <v>2444062.5</v>
       </c>
-      <c r="I33" s="59">
+      <c r="I33" s="27">
         <f>B19*H25*24*365</f>
         <v>173448.00000000003</v>
       </c>
-      <c r="J33" s="37">
+      <c r="J33" s="101">
         <f>SUM(H33:I33)</f>
         <v>2617510.5</v>
       </c>
-      <c r="K33" s="37">
+      <c r="K33" s="101">
         <f>J33/365</f>
         <v>7171.2616438356163</v>
       </c>
-      <c r="N33" s="105"/>
+      <c r="N33" s="73"/>
     </row>
     <row r="34" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A34" s="61" t="s">
+      <c r="A34" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="B34" s="58">
+      <c r="B34" s="26">
         <f>[1]Лист1!B46/10000</f>
         <v>3.8970873005464479E-2</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F34" s="37"/>
-      <c r="G34" s="82" t="s">
+      <c r="F34" s="101"/>
+      <c r="G34" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="H34" s="59"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
+      <c r="H34" s="27"/>
+      <c r="J34" s="101"/>
+      <c r="K34" s="101"/>
     </row>
     <row r="35" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A35" s="61" t="s">
+      <c r="A35" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="B35" s="104">
+      <c r="B35" s="72">
         <f>B34+B33</f>
         <v>0.53471189096953631</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="101" t="s">
         <v>119</v>
       </c>
-      <c r="G35" s="82" t="s">
+      <c r="G35" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H35" s="59">
+      <c r="H35" s="27">
         <f>B13*I12</f>
         <v>9900</v>
       </c>
-      <c r="I35" s="59">
+      <c r="I35" s="27">
         <f>B19*L25*24*365</f>
         <v>613.20000000000005</v>
       </c>
-      <c r="J35" s="37">
+      <c r="J35" s="101">
         <f t="shared" ref="J35" si="1">SUM(H35:I35)</f>
         <v>10513.2</v>
       </c>
-      <c r="K35" s="37">
+      <c r="K35" s="101">
         <f>J35/365</f>
         <v>28.80328767123288</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="61"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="82" t="s">
+      <c r="A36" s="29"/>
+      <c r="F36" s="101"/>
+      <c r="G36" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
-      <c r="J36" s="37"/>
-      <c r="K36" s="37"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="101"/>
+      <c r="K36" s="101"/>
     </row>
     <row r="37" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A37" s="60" t="s">
+      <c r="A37" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="B37" s="58">
+      <c r="B37" s="26">
         <f>B35*1.25</f>
         <v>0.66838986371192033</v>
       </c>
-      <c r="C37" s="58" t="s">
+      <c r="C37" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="101" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="82" t="s">
+      <c r="G37" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H37" s="59">
+      <c r="H37" s="27">
         <f>B13*J12</f>
         <v>123750</v>
       </c>
-      <c r="I37" s="59">
+      <c r="I37" s="27">
         <f>B19*J25*24*365</f>
         <v>2452.8000000000002</v>
       </c>
-      <c r="J37" s="37">
+      <c r="J37" s="101">
         <f t="shared" ref="J37" si="2">SUM(H37:I37)</f>
         <v>126202.8</v>
       </c>
-      <c r="K37" s="37">
+      <c r="K37" s="101">
         <f>J37/365</f>
         <v>345.76109589041096</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F38" s="37"/>
-      <c r="G38" s="82" t="s">
+      <c r="F38" s="101"/>
+      <c r="G38" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="H38" s="59"/>
-      <c r="I38" s="59"/>
-      <c r="J38" s="37"/>
-      <c r="K38" s="37"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="101"/>
+      <c r="K38" s="101"/>
     </row>
     <row r="39" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="61" t="s">
+      <c r="A39" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="B39" s="58">
+      <c r="B39" s="26">
         <v>12</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="101" t="s">
         <v>113</v>
       </c>
-      <c r="G39" s="82" t="s">
+      <c r="G39" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H39" s="59">
+      <c r="H39" s="27">
         <f>B13*K12</f>
         <v>4331.25</v>
       </c>
-      <c r="I39" s="59">
+      <c r="I39" s="27">
         <f>B19*M25*24*365</f>
         <v>306.60000000000002</v>
       </c>
-      <c r="J39" s="37">
+      <c r="J39" s="101">
         <f t="shared" ref="J39" si="3">SUM(H39:I39)</f>
         <v>4637.8500000000004</v>
       </c>
-      <c r="K39" s="37">
+      <c r="K39" s="101">
         <f>J39/365</f>
         <v>12.706438356164385</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="61" t="s">
+      <c r="A40" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="B40" s="58">
+      <c r="B40" s="26">
         <v>16</v>
       </c>
-      <c r="F40" s="37"/>
-      <c r="G40" s="82" t="s">
+      <c r="F40" s="101"/>
+      <c r="G40" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="59"/>
-      <c r="I40" s="59"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="37"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="101"/>
+      <c r="K40" s="101"/>
     </row>
     <row r="41" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="60" t="s">
+      <c r="A41" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="B41" s="58">
+      <c r="B41" s="26">
         <f>B39+B40</f>
         <v>28</v>
       </c>
-      <c r="F41" s="37" t="s">
+      <c r="F41" s="101" t="s">
         <v>132</v>
       </c>
-      <c r="G41" s="82" t="s">
+      <c r="G41" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H41" s="59">
+      <c r="H41" s="27">
         <f>B13*N25</f>
         <v>0</v>
       </c>
-      <c r="I41" s="59">
+      <c r="I41" s="27">
         <f>B19*N25</f>
         <v>0</v>
       </c>
-      <c r="J41" s="37">
+      <c r="J41" s="101">
         <f t="shared" ref="J41" si="4">SUM(H41:I41)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="37">
+      <c r="K41" s="101">
         <f>J41/365</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A42" s="60" t="s">
+      <c r="A42" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="B42" s="58">
+      <c r="B42" s="26">
         <f>B39+2*B40</f>
         <v>44</v>
       </c>
-      <c r="F42" s="37"/>
-      <c r="G42" s="82" t="s">
+      <c r="F42" s="101"/>
+      <c r="G42" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="H42" s="59"/>
-      <c r="I42" s="59"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="37"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="101"/>
+      <c r="K42" s="101"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F43" s="37" t="s">
+      <c r="F43" s="101" t="s">
         <v>121</v>
       </c>
-      <c r="G43" s="82" t="s">
+      <c r="G43" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H43" s="59">
+      <c r="H43" s="27">
         <f>B13*L12</f>
         <v>210375</v>
       </c>
-      <c r="I43" s="59">
+      <c r="I43" s="27">
         <f>B19*I25*24*365</f>
         <v>20148</v>
       </c>
-      <c r="J43" s="37">
+      <c r="J43" s="101">
         <f t="shared" ref="J43" si="5">SUM(H43:I43)</f>
         <v>230523</v>
       </c>
-      <c r="K43" s="37">
+      <c r="K43" s="101">
         <f>J43/365</f>
         <v>631.56986301369864</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="60" t="s">
+      <c r="A44" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="B44" s="58">
+      <c r="B44" s="26">
         <f>B42/B41</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="82" t="s">
+      <c r="F44" s="101"/>
+      <c r="G44" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="H44" s="59"/>
-      <c r="I44" s="59"/>
-      <c r="J44" s="37"/>
-      <c r="K44" s="37"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="101"/>
+      <c r="K44" s="101"/>
     </row>
     <row r="45" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="60" t="s">
+      <c r="A45" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="B45" s="58">
+      <c r="B45" s="26">
         <f>J33/1000</f>
         <v>2617.5104999999999</v>
       </c>
-      <c r="C45" s="58" t="s">
+      <c r="C45" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="37" t="s">
+      <c r="F45" s="101" t="s">
         <v>129</v>
       </c>
-      <c r="G45" s="82" t="s">
+      <c r="G45" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H45" s="59">
+      <c r="H45" s="27">
         <f>B13*M12</f>
         <v>12375</v>
       </c>
-      <c r="I45" s="59"/>
-      <c r="J45" s="37">
+      <c r="I45" s="27"/>
+      <c r="J45" s="101">
         <f t="shared" ref="J45" si="6">SUM(H45:I45)</f>
         <v>12375</v>
       </c>
-      <c r="K45" s="37">
+      <c r="K45" s="101">
         <f>J45/365</f>
         <v>33.904109589041099</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="60" t="s">
+      <c r="A46" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="B46" s="58">
+      <c r="B46" s="26">
         <f>(B44*B45)+([1]Лист1!B27*1000)</f>
         <v>23874.631942834287</v>
       </c>
-      <c r="C46" s="58" t="s">
+      <c r="C46" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="F46" s="37"/>
-      <c r="G46" s="82" t="s">
+      <c r="F46" s="101"/>
+      <c r="G46" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="H46" s="59"/>
-      <c r="I46" s="59"/>
-      <c r="J46" s="37"/>
-      <c r="K46" s="37"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="101"/>
+      <c r="K46" s="101"/>
     </row>
     <row r="47" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="60" t="s">
+      <c r="A47" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="B47" s="58">
+      <c r="B47" s="26">
         <f>B46/1000</f>
         <v>23.874631942834288</v>
       </c>
-      <c r="C47" s="58" t="s">
+      <c r="C47" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="F47" s="37" t="s">
+      <c r="F47" s="101" t="s">
         <v>156</v>
       </c>
-      <c r="G47" s="82" t="s">
+      <c r="G47" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H47" s="59"/>
-      <c r="I47" s="59">
+      <c r="H47" s="27"/>
+      <c r="I47" s="27">
         <f>B19*P25*24*365</f>
         <v>376.68</v>
       </c>
-      <c r="J47" s="37">
+      <c r="J47" s="101">
         <f t="shared" ref="J47" si="7">SUM(H47:I47)</f>
         <v>376.68</v>
       </c>
-      <c r="K47" s="37">
+      <c r="K47" s="101">
         <f>J47/365</f>
         <v>1.032</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F48" s="37"/>
-      <c r="G48" s="82" t="s">
+      <c r="F48" s="101"/>
+      <c r="G48" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="H48" s="59"/>
-      <c r="I48" s="59"/>
-      <c r="J48" s="37"/>
-      <c r="K48" s="37"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="101"/>
+      <c r="K48" s="101"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F49" s="37" t="s">
+      <c r="F49" s="101" t="s">
         <v>157</v>
       </c>
-      <c r="G49" s="82" t="s">
+      <c r="G49" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="H49" s="59"/>
-      <c r="I49" s="59">
+      <c r="H49" s="27"/>
+      <c r="I49" s="27">
         <f>B19*O25*24*365</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="J49" s="37">
+      <c r="J49" s="101">
         <f t="shared" ref="J49" si="8">SUM(H49:I49)</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="K49" s="37">
+      <c r="K49" s="101">
         <f>J49/365</f>
         <v>4.3200000000000001E-6</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F50" s="37"/>
-      <c r="G50" s="82" t="s">
+      <c r="F50" s="101"/>
+      <c r="G50" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="H50" s="59"/>
-      <c r="I50" s="59"/>
-      <c r="J50" s="37"/>
-      <c r="K50" s="37"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+      <c r="J50" s="101"/>
+      <c r="K50" s="101"/>
     </row>
     <row r="51" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="60" t="s">
+      <c r="A51" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="B51" s="58">
+      <c r="B51" s="26">
         <f>(B47/[1]Лист1!Q1)/10000</f>
         <v>1.4469473904748054</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="26" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="60" t="s">
+      <c r="A52" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="B52" s="58">
+      <c r="B52" s="26">
         <f>B51*1.25</f>
         <v>1.8086842380935066</v>
       </c>
-      <c r="C52" s="58" t="s">
+      <c r="C52" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="G52" s="62" t="s">
+      <c r="G52" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="H52" s="64" t="s">
+      <c r="H52" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="I52" s="69" t="s">
+      <c r="I52" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="J52" s="91"/>
+      <c r="J52" s="59"/>
     </row>
     <row r="53" spans="1:11" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G53" s="63" t="s">
+      <c r="G53" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="H53" s="65" t="s">
+      <c r="H53" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="I53" s="87" t="s">
+      <c r="I53" s="55" t="s">
         <v>233</v>
       </c>
-      <c r="J53" s="95" t="s">
+      <c r="J53" s="63" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="60" t="s">
+      <c r="A54" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="B54" s="58">
+      <c r="B54" s="26">
         <f>SUM(I16:I21)</f>
         <v>15</v>
       </c>
-      <c r="C54" s="58" t="s">
+      <c r="C54" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="G54" s="70" t="s">
+      <c r="G54" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="H54" s="73">
+      <c r="H54" s="41">
         <f>K33*1000/$D$25</f>
         <v>2048.9318982387476</v>
       </c>
-      <c r="I54" s="88">
+      <c r="I54" s="56">
         <f>K33/J71</f>
         <v>2390.4205479452053</v>
       </c>
-      <c r="J54" s="94">
+      <c r="J54" s="62">
         <f>H54/J71</f>
         <v>682.97729941291584</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G55" s="62" t="s">
+      <c r="G55" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="H55" s="84">
+      <c r="H55" s="52">
         <f>K35*1000/$D$25</f>
         <v>8.2295107632093938</v>
       </c>
-      <c r="I55" s="89">
+      <c r="I55" s="57">
         <f>K35/J78</f>
         <v>576.0657534246576</v>
       </c>
-      <c r="J55" s="92">
+      <c r="J55" s="60">
         <f>H55/J78</f>
         <v>164.59021526418786</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G56" s="62" t="s">
+      <c r="G56" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="H56" s="84">
+      <c r="H56" s="52">
         <f>K37*1000/$D$25</f>
         <v>98.788884540117408</v>
       </c>
-      <c r="I56" s="89">
+      <c r="I56" s="57">
         <f>K37/J68</f>
         <v>8644.0273972602736</v>
       </c>
-      <c r="J56" s="92">
+      <c r="J56" s="60">
         <f>H56/J68</f>
         <v>2469.7221135029354</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G57" s="62" t="s">
+      <c r="G57" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="H57" s="84">
+      <c r="H57" s="52">
         <f>K39*1000/$D$25</f>
         <v>3.6304109589041103</v>
       </c>
-      <c r="I57" s="89">
+      <c r="I57" s="57">
         <f>K39/J70</f>
         <v>42354.794520547955</v>
       </c>
-      <c r="J57" s="92">
+      <c r="J57" s="60">
         <f>H57/J70</f>
         <v>12101.369863013702</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="H58" s="84">
+      <c r="H58" s="52">
         <f>K41*1000/$D$25</f>
         <v>0</v>
       </c>
-      <c r="I58" s="89">
+      <c r="I58" s="57">
         <f>K41/J84</f>
         <v>0</v>
       </c>
-      <c r="J58" s="92">
+      <c r="J58" s="60">
         <f>H58</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G59" s="62" t="s">
+      <c r="G59" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="H59" s="84">
+      <c r="H59" s="52">
         <f>K43*1000/$D$25</f>
         <v>180.44853228962816</v>
       </c>
-      <c r="I59" s="89">
+      <c r="I59" s="57">
         <f>K43/J74</f>
         <v>126313.97260273973</v>
       </c>
-      <c r="J59" s="92">
+      <c r="J59" s="60">
         <f>H59/J74</f>
         <v>36089.706457925633</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G60" s="62" t="s">
+      <c r="G60" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="H60" s="84">
+      <c r="H60" s="52">
         <f>K45*1000/$D$25</f>
         <v>9.6868884540117435</v>
       </c>
-      <c r="I60" s="89">
+      <c r="I60" s="57">
         <f>K45/J69</f>
         <v>678.08219178082197</v>
       </c>
-      <c r="J60" s="92">
+      <c r="J60" s="60">
         <f>H60/J69</f>
         <v>193.73776908023487</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G61" s="62" t="s">
+      <c r="G61" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="H61" s="84">
+      <c r="H61" s="52">
         <f>K47*1000/$D$25</f>
         <v>0.29485714285714287</v>
       </c>
-      <c r="I61" s="89">
+      <c r="I61" s="57">
         <f>K47/J85</f>
         <v>17.200000000000003</v>
       </c>
-      <c r="J61" s="92">
+      <c r="J61" s="60">
         <f>H61/J85</f>
         <v>4.9142857142857146</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G62" s="80" t="s">
+      <c r="G62" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="H62" s="85">
+      <c r="H62" s="53">
         <f>K49*1000/$D$25</f>
         <v>1.2342857142857142E-6</v>
       </c>
-      <c r="I62" s="90">
+      <c r="I62" s="58">
         <f>K49/J81</f>
         <v>4.32</v>
       </c>
-      <c r="J62" s="93">
+      <c r="J62" s="61">
         <f>H62/J81</f>
         <v>1.2342857142857142</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G64" s="38" t="s">
+      <c r="G64" s="85" t="s">
         <v>153</v>
       </c>
-      <c r="H64" s="64" t="s">
+      <c r="H64" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="I64" s="50" t="s">
+      <c r="I64" s="108" t="s">
         <v>235</v>
       </c>
-      <c r="J64" s="51"/>
+      <c r="J64" s="109"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G65" s="39"/>
-      <c r="H65" s="72"/>
-      <c r="I65" s="52"/>
-      <c r="J65" s="53"/>
+      <c r="G65" s="86"/>
+      <c r="H65" s="40"/>
+      <c r="I65" s="110"/>
+      <c r="J65" s="111"/>
     </row>
     <row r="66" spans="1:10" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G66" s="39"/>
-      <c r="H66" s="71" t="s">
+      <c r="G66" s="86"/>
+      <c r="H66" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="I66" s="54" t="s">
+      <c r="I66" s="112" t="s">
         <v>237</v>
       </c>
-      <c r="J66" s="55"/>
+      <c r="J66" s="113"/>
     </row>
     <row r="67" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="40"/>
-      <c r="H67" s="86"/>
-      <c r="I67" s="65" t="s">
+      <c r="G67" s="87"/>
+      <c r="H67" s="54"/>
+      <c r="I67" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="J67" s="65" t="s">
+      <c r="J67" s="33" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="63" t="s">
+      <c r="G68" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="H68" s="65">
+      <c r="H68" s="33">
         <v>2</v>
       </c>
-      <c r="I68" s="65">
+      <c r="I68" s="33">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="J68" s="65">
+      <c r="J68" s="33">
         <v>0.04</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="60" t="s">
+      <c r="A69" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="B69" s="58">
+      <c r="B69" s="26">
         <v>0.4</v>
       </c>
-      <c r="G69" s="63" t="s">
+      <c r="G69" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="H69" s="65">
+      <c r="H69" s="33">
         <v>3</v>
       </c>
-      <c r="I69" s="65">
+      <c r="I69" s="33">
         <v>0.15</v>
       </c>
-      <c r="J69" s="65">
+      <c r="J69" s="33">
         <v>0.05</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="60" t="s">
+      <c r="A70" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="B70" s="58">
+      <c r="B70" s="26">
         <v>1</v>
       </c>
-      <c r="G70" s="63" t="s">
+      <c r="G70" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="H70" s="65">
+      <c r="H70" s="33">
         <v>1</v>
       </c>
-      <c r="I70" s="65">
+      <c r="I70" s="33">
         <v>1E-3</v>
       </c>
-      <c r="J70" s="65">
+      <c r="J70" s="33">
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A71" s="60" t="s">
+      <c r="A71" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="B71" s="58">
+      <c r="B71" s="26">
         <v>1.5</v>
       </c>
-      <c r="G71" s="70" t="s">
+      <c r="G71" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="H71" s="38">
+      <c r="H71" s="85">
         <v>3</v>
       </c>
-      <c r="I71" s="38">
+      <c r="I71" s="85">
         <v>5</v>
       </c>
-      <c r="J71" s="38">
+      <c r="J71" s="85">
         <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A72" s="60" t="s">
+      <c r="A72" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="B72" s="58">
+      <c r="B72" s="26">
         <v>1</v>
       </c>
-      <c r="G72" s="83"/>
-      <c r="H72" s="39"/>
-      <c r="I72" s="39"/>
-      <c r="J72" s="39"/>
+      <c r="G72" s="51"/>
+      <c r="H72" s="86"/>
+      <c r="I72" s="86"/>
+      <c r="J72" s="86"/>
     </row>
     <row r="73" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="60" t="s">
+      <c r="A73" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="B73" s="58">
+      <c r="B73" s="26">
         <v>1</v>
       </c>
-      <c r="G73" s="63" t="s">
+      <c r="G73" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="H73" s="40"/>
-      <c r="I73" s="40"/>
-      <c r="J73" s="40"/>
+      <c r="H73" s="87"/>
+      <c r="I73" s="87"/>
+      <c r="J73" s="87"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G74" s="70" t="s">
+      <c r="G74" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="H74" s="38">
+      <c r="H74" s="85">
         <v>4</v>
       </c>
-      <c r="I74" s="38">
+      <c r="I74" s="85">
         <v>0.03</v>
       </c>
-      <c r="J74" s="38">
+      <c r="J74" s="85">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A75" s="60" t="s">
+      <c r="A75" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="B75" s="58">
+      <c r="B75" s="26">
         <f>SUM(J99:J102)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="G75" s="83"/>
-      <c r="H75" s="39"/>
-      <c r="I75" s="39"/>
-      <c r="J75" s="39"/>
+        <v>5</v>
+      </c>
+      <c r="G75" s="51"/>
+      <c r="H75" s="86"/>
+      <c r="I75" s="86"/>
+      <c r="J75" s="86"/>
     </row>
     <row r="76" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G76" s="63" t="s">
+      <c r="G76" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="H76" s="40"/>
-      <c r="I76" s="40"/>
-      <c r="J76" s="40"/>
+      <c r="H76" s="87"/>
+      <c r="I76" s="87"/>
+      <c r="J76" s="87"/>
     </row>
     <row r="77" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="112" t="s">
+      <c r="A77" s="80" t="s">
         <v>240</v>
       </c>
-      <c r="B77" s="58">
+      <c r="B77" s="26">
         <f>(0.5+0.01*B54*B75)*B69*B70*B71*B72*B73</f>
-        <v>0.33000000000000007</v>
-      </c>
-      <c r="C77" s="58" t="s">
+        <v>0.75</v>
+      </c>
+      <c r="C77" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="G77" s="63" t="s">
+      <c r="G77" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="H77" s="65">
+      <c r="H77" s="33">
         <v>3</v>
       </c>
-      <c r="I77" s="65">
+      <c r="I77" s="33">
         <v>0.5</v>
       </c>
-      <c r="J77" s="65">
+      <c r="J77" s="33">
         <v>0.15</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G78" s="70" t="s">
+      <c r="G78" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="H78" s="38">
+      <c r="H78" s="85">
         <v>2</v>
       </c>
-      <c r="I78" s="38">
+      <c r="I78" s="85">
         <v>0.5</v>
       </c>
-      <c r="J78" s="38">
+      <c r="J78" s="85">
         <v>0.05</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G79" s="83"/>
-      <c r="H79" s="39"/>
-      <c r="I79" s="39"/>
-      <c r="J79" s="39"/>
+      <c r="G79" s="51"/>
+      <c r="H79" s="86"/>
+      <c r="I79" s="86"/>
+      <c r="J79" s="86"/>
     </row>
     <row r="80" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G80" s="63" t="s">
+      <c r="G80" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="H80" s="40"/>
-      <c r="I80" s="40"/>
-      <c r="J80" s="40"/>
+      <c r="H80" s="87"/>
+      <c r="I80" s="87"/>
+      <c r="J80" s="87"/>
     </row>
     <row r="81" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G81" s="70" t="s">
+      <c r="G81" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="H81" s="38">
+      <c r="H81" s="85">
         <v>1</v>
       </c>
-      <c r="I81" s="48"/>
-      <c r="J81" s="44">
+      <c r="I81" s="102"/>
+      <c r="J81" s="105">
         <f>10^-6</f>
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="82" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G82" s="83"/>
-      <c r="H82" s="39"/>
-      <c r="I82" s="47"/>
-      <c r="J82" s="45"/>
+      <c r="G82" s="51"/>
+      <c r="H82" s="86"/>
+      <c r="I82" s="103"/>
+      <c r="J82" s="106"/>
     </row>
     <row r="83" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G83" s="63" t="s">
+      <c r="G83" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="H83" s="40"/>
-      <c r="I83" s="49"/>
-      <c r="J83" s="46"/>
+      <c r="H83" s="87"/>
+      <c r="I83" s="104"/>
+      <c r="J83" s="107"/>
     </row>
     <row r="84" spans="7:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G84" s="63" t="s">
+      <c r="G84" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="H84" s="65">
+      <c r="H84" s="33">
         <v>3</v>
       </c>
-      <c r="I84" s="65">
+      <c r="I84" s="33">
         <v>0.5</v>
       </c>
-      <c r="J84" s="65">
+      <c r="J84" s="33">
         <v>0.15</v>
       </c>
     </row>
     <row r="85" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G85" s="63" t="s">
+      <c r="G85" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="H85" s="65">
+      <c r="H85" s="33">
         <v>2</v>
       </c>
-      <c r="I85" s="65">
+      <c r="I85" s="33">
         <v>0.4</v>
       </c>
-      <c r="J85" s="65">
+      <c r="J85" s="33">
         <v>0.06</v>
       </c>
     </row>
     <row r="86" spans="7:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="87" spans="7:10" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G87" s="102" t="s">
+      <c r="G87" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="H87" s="103" t="s">
+      <c r="H87" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="I87" s="103" t="s">
+      <c r="I87" s="71" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="88" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G88" s="96" t="s">
+      <c r="G88" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="H88" s="100">
+      <c r="H88" s="68">
         <f>K33*1000/$D$25</f>
         <v>2048.9318982387476</v>
       </c>
-      <c r="I88" s="100">
+      <c r="I88" s="68">
         <f>K33/J71</f>
         <v>2390.4205479452053</v>
       </c>
     </row>
     <row r="89" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G89" s="97" t="s">
+      <c r="G89" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="H89" s="98">
+      <c r="H89" s="66">
         <f>K35*1000/$D$25</f>
         <v>8.2295107632093938</v>
       </c>
-      <c r="I89" s="98">
+      <c r="I89" s="66">
         <f>K35/J78</f>
         <v>576.0657534246576</v>
       </c>
     </row>
     <row r="90" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G90" s="97" t="s">
+      <c r="G90" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="H90" s="98">
+      <c r="H90" s="66">
         <f>K37*1000/$D$25</f>
         <v>98.788884540117408</v>
       </c>
-      <c r="I90" s="98">
+      <c r="I90" s="66">
         <f>K37/J68</f>
         <v>8644.0273972602736</v>
       </c>
     </row>
     <row r="91" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G91" s="97" t="s">
+      <c r="G91" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="H91" s="98">
+      <c r="H91" s="66">
         <f>K39*1000/$D$25</f>
         <v>3.6304109589041103</v>
       </c>
-      <c r="I91" s="98">
+      <c r="I91" s="66">
         <f>K39/J70</f>
         <v>42354.794520547955</v>
       </c>
     </row>
     <row r="92" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G92" s="97" t="s">
+      <c r="G92" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="H92" s="98">
+      <c r="H92" s="66">
         <f>K41*1000/$D$25</f>
         <v>0</v>
       </c>
-      <c r="I92" s="98">
+      <c r="I92" s="66">
         <f>K41/J84</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="7:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="G93" s="98" t="s">
+      <c r="G93" s="66" t="s">
         <v>186</v>
       </c>
-      <c r="H93" s="98">
+      <c r="H93" s="66">
         <f>K43*1000/$D$25</f>
         <v>180.44853228962816</v>
       </c>
-      <c r="I93" s="98">
+      <c r="I93" s="66">
         <f>K43/J74</f>
         <v>126313.97260273973</v>
       </c>
     </row>
     <row r="94" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G94" s="97" t="s">
+      <c r="G94" s="65" t="s">
         <v>129</v>
       </c>
-      <c r="H94" s="98">
+      <c r="H94" s="66">
         <f>K45*1000/$D$25</f>
         <v>9.6868884540117435</v>
       </c>
-      <c r="I94" s="98">
+      <c r="I94" s="66">
         <f>K45/J69</f>
         <v>678.08219178082197</v>
       </c>
     </row>
     <row r="95" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G95" s="97" t="s">
+      <c r="G95" s="65" t="s">
         <v>130</v>
       </c>
-      <c r="H95" s="98">
+      <c r="H95" s="66">
         <f>K47*1000/$D$25</f>
         <v>0.29485714285714287</v>
       </c>
-      <c r="I95" s="98">
+      <c r="I95" s="66">
         <f>K47/J85</f>
         <v>17.200000000000003</v>
       </c>
     </row>
     <row r="96" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G96" s="99" t="s">
+      <c r="G96" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="H96" s="101">
+      <c r="H96" s="69">
         <f>K49*1000/$D$25</f>
         <v>1.2342857142857142E-6</v>
       </c>
-      <c r="I96" s="101">
+      <c r="I96" s="69">
         <f>K49/J81</f>
         <v>4.32</v>
       </c>
     </row>
     <row r="98" spans="7:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G98" s="66" t="s">
+      <c r="G98" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="H98" s="110" t="s">
+      <c r="H98" s="78" t="s">
         <v>242</v>
       </c>
-      <c r="I98" s="110" t="s">
+      <c r="I98" s="78" t="s">
         <v>243</v>
       </c>
-      <c r="J98" s="110" t="s">
+      <c r="J98" s="78" t="s">
         <v>244</v>
       </c>
-      <c r="K98" s="111" t="s">
+      <c r="K98" s="79"/>
+    </row>
+    <row r="99" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G99" s="27" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="99" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G99" s="59" t="s">
-        <v>246</v>
-      </c>
-      <c r="H99" s="59">
+      <c r="H99" s="27">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I99" s="59">
+      <c r="I99" s="27">
         <f>H3/$B$54</f>
         <v>0</v>
       </c>
-      <c r="J99" s="59">
+      <c r="J99" s="27">
         <f>H99*I99</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G100" s="59" t="s">
-        <v>247</v>
-      </c>
-      <c r="H100" s="59">
+      <c r="G100" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="H100" s="27">
         <v>0.2</v>
       </c>
-      <c r="I100" s="59">
+      <c r="I100" s="27">
         <f>H7/$B$54</f>
         <v>0</v>
       </c>
-      <c r="J100" s="59">
+      <c r="J100" s="27">
         <f t="shared" ref="J100:J102" si="9">H100*I100</f>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G101" s="59" t="s">
+      <c r="G101" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="H101" s="27">
+        <v>1</v>
+      </c>
+      <c r="I101" s="27">
+        <v>5</v>
+      </c>
+      <c r="J101" s="27">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G102" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="H101" s="59">
-        <v>1</v>
-      </c>
-      <c r="I101" s="59">
-        <f>H2/$B$54</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J101" s="59">
-        <f t="shared" si="9"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="102" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G102" s="59" t="s">
-        <v>249</v>
-      </c>
-      <c r="H102" s="59">
+      <c r="H102" s="27">
         <v>3.7</v>
       </c>
-      <c r="I102" s="59">
+      <c r="I102" s="27">
         <f>H4/$B$54</f>
         <v>0</v>
       </c>
-      <c r="J102" s="59">
+      <c r="J102" s="27">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="104" spans="7:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G104" s="107" t="s">
+      <c r="G104" s="75" t="s">
         <v>228</v>
       </c>
-      <c r="H104" s="34" t="s">
+      <c r="H104" s="82" t="s">
+        <v>249</v>
+      </c>
+      <c r="I104" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="J104" s="85" t="s">
         <v>250</v>
       </c>
-      <c r="I104" s="64" t="s">
-        <v>229</v>
-      </c>
-      <c r="J104" s="38" t="s">
+      <c r="K104" s="88" t="s">
         <v>251</v>
       </c>
-      <c r="K104" s="41" t="s">
+    </row>
+    <row r="105" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G105" s="76"/>
+      <c r="H105" s="83"/>
+      <c r="I105" s="40"/>
+      <c r="J105" s="86"/>
+      <c r="K105" s="89"/>
+    </row>
+    <row r="106" spans="7:11" ht="54" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G106" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="H106" s="84"/>
+      <c r="I106" s="33" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="105" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G105" s="108"/>
-      <c r="H105" s="57"/>
-      <c r="I105" s="72"/>
-      <c r="J105" s="39"/>
-      <c r="K105" s="42"/>
-    </row>
-    <row r="106" spans="7:11" ht="54" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G106" s="109" t="s">
-        <v>231</v>
-      </c>
-      <c r="H106" s="35"/>
-      <c r="I106" s="65" t="s">
-        <v>253</v>
-      </c>
-      <c r="J106" s="40"/>
-      <c r="K106" s="43"/>
+      <c r="J106" s="87"/>
+      <c r="K106" s="90"/>
     </row>
     <row r="107" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G107" s="107" t="s">
+      <c r="G107" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="H107" s="62">
+      <c r="H107" s="30">
         <f>H25</f>
         <v>19.8</v>
       </c>
-      <c r="I107" s="84">
+      <c r="I107" s="52">
         <v>2048.9318982387476</v>
       </c>
-      <c r="J107" s="64">
+      <c r="J107" s="32">
         <f>(H107*$B$77)/$J$54</f>
-        <v>9.5669358346413529E-3</v>
-      </c>
-      <c r="K107" s="113">
+        <v>2.1743035987821256E-2</v>
+      </c>
+      <c r="K107" s="81">
         <v>3</v>
       </c>
     </row>
     <row r="108" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G108" s="107" t="s">
+      <c r="G108" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="H108" s="62">
+      <c r="H108" s="30">
         <f>L25</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I108" s="84">
+      <c r="I108" s="52">
         <v>8.2295107632093938</v>
       </c>
-      <c r="J108" s="64">
+      <c r="J108" s="32">
         <f t="shared" ref="J108:J115" si="10">(H108*$B$77)/$J$54</f>
-        <v>3.3822500425499734E-5</v>
-      </c>
-      <c r="K108" s="113">
+        <v>7.6869319148863016E-5</v>
+      </c>
+      <c r="K108" s="81">
         <v>0.05</v>
       </c>
     </row>
     <row r="109" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G109" s="107" t="s">
+      <c r="G109" s="75" t="s">
         <v>112</v>
       </c>
-      <c r="H109" s="62">
+      <c r="H109" s="30">
         <f>J25</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="I109" s="84">
+      <c r="I109" s="52">
         <v>98.788884540117408</v>
       </c>
-      <c r="J109" s="64">
+      <c r="J109" s="32">
         <f t="shared" si="10"/>
-        <v>1.3529000170199893E-4</v>
-      </c>
-      <c r="K109" s="113">
+        <v>3.0747727659545207E-4</v>
+      </c>
+      <c r="K109" s="81">
         <v>0.04</v>
       </c>
     </row>
     <row r="110" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G110" s="107" t="s">
+      <c r="G110" s="75" t="s">
         <v>127</v>
       </c>
-      <c r="H110" s="62">
+      <c r="H110" s="30">
         <f>M25</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I110" s="84">
+      <c r="I110" s="52">
         <v>3.6304109589041103</v>
       </c>
-      <c r="J110" s="64">
+      <c r="J110" s="32">
         <f t="shared" si="10"/>
-        <v>1.6911250212749867E-5</v>
-      </c>
-      <c r="K110" s="113">
+        <v>3.8434659574431508E-5</v>
+      </c>
+      <c r="K110" s="81">
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="111" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G111" s="107" t="s">
+      <c r="G111" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="H111" s="62">
+      <c r="H111" s="30">
         <f>N25</f>
         <v>0</v>
       </c>
-      <c r="I111" s="84">
+      <c r="I111" s="52">
         <v>0</v>
       </c>
-      <c r="J111" s="64">
+      <c r="J111" s="32">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K111" s="113">
+      <c r="K111" s="81">
         <v>0.15</v>
       </c>
     </row>
     <row r="112" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G112" s="107" t="s">
+      <c r="G112" s="75" t="s">
         <v>114</v>
       </c>
-      <c r="H112" s="62">
+      <c r="H112" s="30">
         <f>I25</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="I112" s="84">
+      <c r="I112" s="52">
         <v>180.44853228962816</v>
       </c>
-      <c r="J112" s="64">
+      <c r="J112" s="32">
         <f t="shared" si="10"/>
-        <v>1.1113107282664197E-3</v>
-      </c>
-      <c r="K112" s="113">
+        <v>2.5257062006054988E-3</v>
+      </c>
+      <c r="K112" s="81">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="113" spans="7:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G113" s="107" t="s">
-        <v>254</v>
-      </c>
-      <c r="H113" s="62" t="str">
+    <row r="113" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G113" s="75" t="s">
+        <v>253</v>
+      </c>
+      <c r="H113" s="30" t="str">
         <f>K25</f>
         <v>-</v>
       </c>
-      <c r="I113" s="84">
+      <c r="I113" s="52">
         <v>9.6868884540117435</v>
       </c>
-      <c r="J113" s="64" t="e">
+      <c r="J113" s="32" t="e">
         <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
-      <c r="K113" s="113">
+      <c r="K113" s="81">
         <v>0.05</v>
       </c>
     </row>
-    <row r="114" spans="7:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G114" s="107" t="s">
+    <row r="114" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G114" s="75" t="s">
         <v>130</v>
       </c>
-      <c r="H114" s="62">
+      <c r="H114" s="30">
         <f>P25</f>
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="I114" s="84">
+      <c r="I114" s="52">
         <v>0.29485714285714287</v>
       </c>
-      <c r="J114" s="64">
+      <c r="J114" s="32">
         <f t="shared" si="10"/>
-        <v>2.0776678832806975E-5</v>
-      </c>
-      <c r="K114" s="113">
+        <v>4.7219724620015856E-5</v>
+      </c>
+      <c r="K114" s="81">
         <v>0.06</v>
       </c>
-      <c r="M114" s="58" t="s">
-        <v>255</v>
-      </c>
-      <c r="N114" s="58" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="115" spans="7:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G115" s="106" t="s">
+    </row>
+    <row r="115" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G115" s="74" t="s">
         <v>131</v>
       </c>
-      <c r="H115" s="80">
+      <c r="H115" s="48">
         <f>O25</f>
         <v>1.8E-7</v>
       </c>
-      <c r="I115" s="90">
+      <c r="I115" s="58">
         <v>1.2342857142857142E-6</v>
       </c>
-      <c r="J115" s="102">
+      <c r="J115" s="70">
         <f t="shared" si="10"/>
-        <v>8.6972143951285028E-11</v>
+        <v>1.9766396352564775E-10</v>
       </c>
       <c r="K115" s="114">
-        <v>45818</v>
+        <f>1/10^6</f>
+        <v>9.9999999999999995E-7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="G64:G67"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="J74:J76"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="J81:J83"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="K37:K38"/>
     <mergeCell ref="H104:H106"/>
     <mergeCell ref="J104:J106"/>
     <mergeCell ref="K104:K106"/>
@@ -6441,52 +6390,6 @@
     <mergeCell ref="O26:O27"/>
     <mergeCell ref="P26:P27"/>
     <mergeCell ref="F31:G32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="J81:J83"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="H74:H76"/>
-    <mergeCell ref="I74:I76"/>
-    <mergeCell ref="J74:J76"/>
-    <mergeCell ref="G64:G67"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="F37:F38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Лаб1.xlsx
+++ b/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Лаб1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luvidmi\Desktop\gitRep\Codespace\Файлы\1 курс\2 семестр\Экология\Лабы\18.02.25 - 1-ая лаба\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D4D92A-B803-4791-A10F-16150C706994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF92BF8-E968-406E-96D3-B6D595094958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="257">
   <si>
     <t>V(ов) л</t>
   </si>
@@ -2231,6 +2231,15 @@
   </si>
   <si>
     <t>Сажа (С)</t>
+  </si>
+  <si>
+    <t>Минимальное количество кислорода на 1 человека</t>
+  </si>
+  <si>
+    <t>на 1 машину, т</t>
+  </si>
+  <si>
+    <t>на 1 человека, т</t>
   </si>
 </sst>
 </file>
@@ -2492,7 +2501,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2502,6 +2511,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2798,7 +2813,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2995,6 +3010,63 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3005,15 +3077,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3046,54 +3109,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3216,7 +3233,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>510886</xdr:colOff>
+      <xdr:colOff>82261</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>117868</xdr:rowOff>
     </xdr:to>
@@ -3259,8 +3276,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>389660</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>570635</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>54417</xdr:rowOff>
     </xdr:to>
@@ -3348,7 +3365,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>510886</xdr:colOff>
+      <xdr:colOff>82261</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>117868</xdr:rowOff>
     </xdr:to>
@@ -3391,8 +3408,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>389660</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>570635</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>54417</xdr:rowOff>
     </xdr:to>
@@ -3960,6 +3977,13 @@
       <c r="C15" s="4" t="s">
         <v>46</v>
       </c>
+      <c r="F15" s="115">
+        <f>B15/20</f>
+        <v>3.7494033407999998</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -4211,7 +4235,9 @@
   <cols>
     <col min="1" max="1" width="30" style="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="9.140625" style="26"/>
+    <col min="3" max="3" width="9.140625" style="26"/>
+    <col min="4" max="4" width="15.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.28515625" style="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" style="26" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" style="26" customWidth="1"/>
     <col min="9" max="9" width="25" style="26" customWidth="1"/>
@@ -4487,17 +4513,17 @@
       <c r="C10" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="91" t="s">
+      <c r="G10" s="107" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="93" t="s">
+      <c r="H10" s="109" t="s">
         <v>109</v>
       </c>
-      <c r="I10" s="94"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="95"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="111"/>
     </row>
     <row r="11" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29" t="s">
@@ -4509,7 +4535,7 @@
       <c r="C11" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="92"/>
+      <c r="G11" s="108"/>
       <c r="H11" s="33" t="s">
         <v>110</v>
       </c>
@@ -4623,6 +4649,12 @@
       <c r="C16" s="26" t="s">
         <v>104</v>
       </c>
+      <c r="D16" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>255</v>
+      </c>
       <c r="G16" s="31" t="s">
         <v>74</v>
       </c>
@@ -4649,6 +4681,13 @@
       </c>
       <c r="C17" s="26" t="s">
         <v>107</v>
+      </c>
+      <c r="D17" s="116">
+        <v>3.7494033407999998</v>
+      </c>
+      <c r="E17" s="26">
+        <f>B17/5</f>
+        <v>1.6557749999999998</v>
       </c>
       <c r="G17" s="31" t="s">
         <v>75</v>
@@ -4728,17 +4767,17 @@
       <c r="G23" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="H23" s="96" t="s">
+      <c r="H23" s="112" t="s">
         <v>134</v>
       </c>
-      <c r="I23" s="97"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="97"/>
-      <c r="L23" s="97"/>
-      <c r="M23" s="97"/>
-      <c r="N23" s="97"/>
-      <c r="O23" s="97"/>
-      <c r="P23" s="98"/>
+      <c r="I23" s="113"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="113"/>
+      <c r="L23" s="113"/>
+      <c r="M23" s="113"/>
+      <c r="N23" s="113"/>
+      <c r="O23" s="113"/>
+      <c r="P23" s="114"/>
     </row>
     <row r="24" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G24" s="43" t="s">
@@ -4829,7 +4868,7 @@
         <v>0.2</v>
       </c>
       <c r="D26" s="26">
-        <f t="shared" ref="D26:D27" si="0">B26*1000</f>
+        <f>B26*1000</f>
         <v>200</v>
       </c>
       <c r="E26" s="26" t="s">
@@ -4838,31 +4877,31 @@
       <c r="G26" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="H26" s="82">
+      <c r="H26" s="101">
         <v>37.299999999999997</v>
       </c>
-      <c r="I26" s="82">
+      <c r="I26" s="101">
         <v>6.9</v>
       </c>
-      <c r="J26" s="82">
+      <c r="J26" s="101">
         <v>0.8</v>
       </c>
-      <c r="K26" s="82" t="s">
+      <c r="K26" s="101" t="s">
         <v>142</v>
       </c>
-      <c r="L26" s="82">
+      <c r="L26" s="101">
         <v>0.19</v>
       </c>
-      <c r="M26" s="82">
+      <c r="M26" s="101">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="N26" s="82">
+      <c r="N26" s="101">
         <v>0.85</v>
       </c>
-      <c r="O26" s="82" t="s">
+      <c r="O26" s="101" t="s">
         <v>145</v>
       </c>
-      <c r="P26" s="82">
+      <c r="P26" s="101">
         <v>0.23400000000000001</v>
       </c>
     </row>
@@ -4878,7 +4917,7 @@
         <v>160</v>
       </c>
       <c r="D27" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D26:D27" si="0">B27*1000</f>
         <v>10</v>
       </c>
       <c r="E27" s="26" t="s">
@@ -4887,15 +4926,15 @@
       <c r="G27" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="H27" s="84"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="84"/>
-      <c r="M27" s="84"/>
-      <c r="N27" s="84"/>
-      <c r="O27" s="84"/>
-      <c r="P27" s="84"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="103"/>
+      <c r="K27" s="103"/>
+      <c r="L27" s="103"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="103"/>
+      <c r="O27" s="103"/>
+      <c r="P27" s="103"/>
     </row>
     <row r="28" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="26" t="s">
@@ -5029,7 +5068,7 @@
       <c r="C33" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F33" s="101" t="s">
+      <c r="F33" s="83" t="s">
         <v>135</v>
       </c>
       <c r="G33" s="50" t="s">
@@ -5043,11 +5082,11 @@
         <f>B19*H25*24*365</f>
         <v>173448.00000000003</v>
       </c>
-      <c r="J33" s="101">
+      <c r="J33" s="83">
         <f>SUM(H33:I33)</f>
         <v>2617510.5</v>
       </c>
-      <c r="K33" s="101">
+      <c r="K33" s="83">
         <f>J33/365</f>
         <v>7171.2616438356163</v>
       </c>
@@ -5064,13 +5103,13 @@
       <c r="C34" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F34" s="101"/>
+      <c r="F34" s="83"/>
       <c r="G34" s="50" t="s">
         <v>126</v>
       </c>
       <c r="H34" s="27"/>
-      <c r="J34" s="101"/>
-      <c r="K34" s="101"/>
+      <c r="J34" s="83"/>
+      <c r="K34" s="83"/>
     </row>
     <row r="35" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A35" s="29" t="s">
@@ -5083,7 +5122,7 @@
       <c r="C35" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F35" s="101" t="s">
+      <c r="F35" s="83" t="s">
         <v>119</v>
       </c>
       <c r="G35" s="50" t="s">
@@ -5097,25 +5136,25 @@
         <f>B19*L25*24*365</f>
         <v>613.20000000000005</v>
       </c>
-      <c r="J35" s="101">
+      <c r="J35" s="83">
         <f t="shared" ref="J35" si="1">SUM(H35:I35)</f>
         <v>10513.2</v>
       </c>
-      <c r="K35" s="101">
+      <c r="K35" s="83">
         <f>J35/365</f>
         <v>28.80328767123288</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A36" s="29"/>
-      <c r="F36" s="101"/>
+      <c r="F36" s="83"/>
       <c r="G36" s="50" t="s">
         <v>126</v>
       </c>
       <c r="H36" s="27"/>
       <c r="I36" s="27"/>
-      <c r="J36" s="101"/>
-      <c r="K36" s="101"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="83"/>
     </row>
     <row r="37" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A37" s="28" t="s">
@@ -5128,7 +5167,7 @@
       <c r="C37" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F37" s="101" t="s">
+      <c r="F37" s="83" t="s">
         <v>120</v>
       </c>
       <c r="G37" s="50" t="s">
@@ -5142,24 +5181,24 @@
         <f>B19*J25*24*365</f>
         <v>2452.8000000000002</v>
       </c>
-      <c r="J37" s="101">
+      <c r="J37" s="83">
         <f t="shared" ref="J37" si="2">SUM(H37:I37)</f>
         <v>126202.8</v>
       </c>
-      <c r="K37" s="101">
+      <c r="K37" s="83">
         <f>J37/365</f>
         <v>345.76109589041096</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F38" s="101"/>
+      <c r="F38" s="83"/>
       <c r="G38" s="50" t="s">
         <v>126</v>
       </c>
       <c r="H38" s="27"/>
       <c r="I38" s="27"/>
-      <c r="J38" s="101"/>
-      <c r="K38" s="101"/>
+      <c r="J38" s="83"/>
+      <c r="K38" s="83"/>
     </row>
     <row r="39" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="29" t="s">
@@ -5168,7 +5207,7 @@
       <c r="B39" s="26">
         <v>12</v>
       </c>
-      <c r="F39" s="101" t="s">
+      <c r="F39" s="83" t="s">
         <v>113</v>
       </c>
       <c r="G39" s="50" t="s">
@@ -5182,11 +5221,11 @@
         <f>B19*M25*24*365</f>
         <v>306.60000000000002</v>
       </c>
-      <c r="J39" s="101">
+      <c r="J39" s="83">
         <f t="shared" ref="J39" si="3">SUM(H39:I39)</f>
         <v>4637.8500000000004</v>
       </c>
-      <c r="K39" s="101">
+      <c r="K39" s="83">
         <f>J39/365</f>
         <v>12.706438356164385</v>
       </c>
@@ -5198,14 +5237,14 @@
       <c r="B40" s="26">
         <v>16</v>
       </c>
-      <c r="F40" s="101"/>
+      <c r="F40" s="83"/>
       <c r="G40" s="50" t="s">
         <v>126</v>
       </c>
       <c r="H40" s="27"/>
       <c r="I40" s="27"/>
-      <c r="J40" s="101"/>
-      <c r="K40" s="101"/>
+      <c r="J40" s="83"/>
+      <c r="K40" s="83"/>
     </row>
     <row r="41" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="28" t="s">
@@ -5215,7 +5254,7 @@
         <f>B39+B40</f>
         <v>28</v>
       </c>
-      <c r="F41" s="101" t="s">
+      <c r="F41" s="83" t="s">
         <v>132</v>
       </c>
       <c r="G41" s="50" t="s">
@@ -5229,11 +5268,11 @@
         <f>B19*N25</f>
         <v>0</v>
       </c>
-      <c r="J41" s="101">
+      <c r="J41" s="83">
         <f t="shared" ref="J41" si="4">SUM(H41:I41)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="101">
+      <c r="K41" s="83">
         <f>J41/365</f>
         <v>0</v>
       </c>
@@ -5246,17 +5285,17 @@
         <f>B39+2*B40</f>
         <v>44</v>
       </c>
-      <c r="F42" s="101"/>
+      <c r="F42" s="83"/>
       <c r="G42" s="50" t="s">
         <v>126</v>
       </c>
       <c r="H42" s="27"/>
       <c r="I42" s="27"/>
-      <c r="J42" s="101"/>
-      <c r="K42" s="101"/>
+      <c r="J42" s="83"/>
+      <c r="K42" s="83"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F43" s="101" t="s">
+      <c r="F43" s="83" t="s">
         <v>121</v>
       </c>
       <c r="G43" s="50" t="s">
@@ -5270,11 +5309,11 @@
         <f>B19*I25*24*365</f>
         <v>20148</v>
       </c>
-      <c r="J43" s="101">
+      <c r="J43" s="83">
         <f t="shared" ref="J43" si="5">SUM(H43:I43)</f>
         <v>230523</v>
       </c>
-      <c r="K43" s="101">
+      <c r="K43" s="83">
         <f>J43/365</f>
         <v>631.56986301369864</v>
       </c>
@@ -5287,14 +5326,14 @@
         <f>B42/B41</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="F44" s="101"/>
+      <c r="F44" s="83"/>
       <c r="G44" s="50" t="s">
         <v>126</v>
       </c>
       <c r="H44" s="27"/>
       <c r="I44" s="27"/>
-      <c r="J44" s="101"/>
-      <c r="K44" s="101"/>
+      <c r="J44" s="83"/>
+      <c r="K44" s="83"/>
     </row>
     <row r="45" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="28" t="s">
@@ -5307,7 +5346,7 @@
       <c r="C45" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="101" t="s">
+      <c r="F45" s="83" t="s">
         <v>129</v>
       </c>
       <c r="G45" s="50" t="s">
@@ -5318,11 +5357,11 @@
         <v>12375</v>
       </c>
       <c r="I45" s="27"/>
-      <c r="J45" s="101">
+      <c r="J45" s="83">
         <f t="shared" ref="J45" si="6">SUM(H45:I45)</f>
         <v>12375</v>
       </c>
-      <c r="K45" s="101">
+      <c r="K45" s="83">
         <f>J45/365</f>
         <v>33.904109589041099</v>
       </c>
@@ -5338,14 +5377,14 @@
       <c r="C46" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="F46" s="101"/>
+      <c r="F46" s="83"/>
       <c r="G46" s="50" t="s">
         <v>126</v>
       </c>
       <c r="H46" s="27"/>
       <c r="I46" s="27"/>
-      <c r="J46" s="101"/>
-      <c r="K46" s="101"/>
+      <c r="J46" s="83"/>
+      <c r="K46" s="83"/>
     </row>
     <row r="47" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="28" t="s">
@@ -5358,7 +5397,7 @@
       <c r="C47" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="F47" s="101" t="s">
+      <c r="F47" s="83" t="s">
         <v>156</v>
       </c>
       <c r="G47" s="50" t="s">
@@ -5369,27 +5408,27 @@
         <f>B19*P25*24*365</f>
         <v>376.68</v>
       </c>
-      <c r="J47" s="101">
+      <c r="J47" s="83">
         <f t="shared" ref="J47" si="7">SUM(H47:I47)</f>
         <v>376.68</v>
       </c>
-      <c r="K47" s="101">
+      <c r="K47" s="83">
         <f>J47/365</f>
         <v>1.032</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F48" s="101"/>
+      <c r="F48" s="83"/>
       <c r="G48" s="50" t="s">
         <v>126</v>
       </c>
       <c r="H48" s="27"/>
       <c r="I48" s="27"/>
-      <c r="J48" s="101"/>
-      <c r="K48" s="101"/>
+      <c r="J48" s="83"/>
+      <c r="K48" s="83"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F49" s="101" t="s">
+      <c r="F49" s="83" t="s">
         <v>157</v>
       </c>
       <c r="G49" s="50" t="s">
@@ -5400,24 +5439,24 @@
         <f>B19*O25*24*365</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="J49" s="101">
+      <c r="J49" s="83">
         <f t="shared" ref="J49" si="8">SUM(H49:I49)</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="K49" s="101">
+      <c r="K49" s="83">
         <f>J49/365</f>
         <v>4.3200000000000001E-6</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F50" s="101"/>
+      <c r="F50" s="83"/>
       <c r="G50" s="50" t="s">
         <v>126</v>
       </c>
       <c r="H50" s="27"/>
       <c r="I50" s="27"/>
-      <c r="J50" s="101"/>
-      <c r="K50" s="101"/>
+      <c r="J50" s="83"/>
+      <c r="K50" s="83"/>
     </row>
     <row r="51" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="28" t="s">
@@ -5632,35 +5671,35 @@
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G64" s="85" t="s">
+      <c r="G64" s="84" t="s">
         <v>153</v>
       </c>
       <c r="H64" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="I64" s="108" t="s">
+      <c r="I64" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="J64" s="109"/>
+      <c r="J64" s="88"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G65" s="86"/>
+      <c r="G65" s="85"/>
       <c r="H65" s="40"/>
-      <c r="I65" s="110"/>
-      <c r="J65" s="111"/>
+      <c r="I65" s="89"/>
+      <c r="J65" s="90"/>
     </row>
     <row r="66" spans="1:10" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G66" s="86"/>
+      <c r="G66" s="85"/>
       <c r="H66" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="I66" s="112" t="s">
+      <c r="I66" s="91" t="s">
         <v>237</v>
       </c>
-      <c r="J66" s="113"/>
+      <c r="J66" s="92"/>
     </row>
     <row r="67" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="87"/>
+      <c r="G67" s="86"/>
       <c r="H67" s="54"/>
       <c r="I67" s="33" t="s">
         <v>168</v>
@@ -5733,13 +5772,13 @@
       <c r="G71" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="H71" s="85">
+      <c r="H71" s="84">
         <v>3</v>
       </c>
-      <c r="I71" s="85">
+      <c r="I71" s="84">
         <v>5</v>
       </c>
-      <c r="J71" s="85">
+      <c r="J71" s="84">
         <v>3</v>
       </c>
     </row>
@@ -5751,9 +5790,9 @@
         <v>1</v>
       </c>
       <c r="G72" s="51"/>
-      <c r="H72" s="86"/>
-      <c r="I72" s="86"/>
-      <c r="J72" s="86"/>
+      <c r="H72" s="85"/>
+      <c r="I72" s="85"/>
+      <c r="J72" s="85"/>
     </row>
     <row r="73" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="28" t="s">
@@ -5765,21 +5804,21 @@
       <c r="G73" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="H73" s="87"/>
-      <c r="I73" s="87"/>
-      <c r="J73" s="87"/>
+      <c r="H73" s="86"/>
+      <c r="I73" s="86"/>
+      <c r="J73" s="86"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G74" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="H74" s="85">
+      <c r="H74" s="84">
         <v>4</v>
       </c>
-      <c r="I74" s="85">
+      <c r="I74" s="84">
         <v>0.03</v>
       </c>
-      <c r="J74" s="85">
+      <c r="J74" s="84">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
@@ -5792,17 +5831,17 @@
         <v>5</v>
       </c>
       <c r="G75" s="51"/>
-      <c r="H75" s="86"/>
-      <c r="I75" s="86"/>
-      <c r="J75" s="86"/>
+      <c r="H75" s="85"/>
+      <c r="I75" s="85"/>
+      <c r="J75" s="85"/>
     </row>
     <row r="76" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G76" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="H76" s="87"/>
-      <c r="I76" s="87"/>
-      <c r="J76" s="87"/>
+      <c r="H76" s="86"/>
+      <c r="I76" s="86"/>
+      <c r="J76" s="86"/>
     </row>
     <row r="77" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A77" s="80" t="s">
@@ -5832,56 +5871,56 @@
       <c r="G78" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="H78" s="85">
+      <c r="H78" s="84">
         <v>2</v>
       </c>
-      <c r="I78" s="85">
+      <c r="I78" s="84">
         <v>0.5</v>
       </c>
-      <c r="J78" s="85">
+      <c r="J78" s="84">
         <v>0.05</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G79" s="51"/>
-      <c r="H79" s="86"/>
-      <c r="I79" s="86"/>
-      <c r="J79" s="86"/>
+      <c r="H79" s="85"/>
+      <c r="I79" s="85"/>
+      <c r="J79" s="85"/>
     </row>
     <row r="80" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G80" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="H80" s="87"/>
-      <c r="I80" s="87"/>
-      <c r="J80" s="87"/>
+      <c r="H80" s="86"/>
+      <c r="I80" s="86"/>
+      <c r="J80" s="86"/>
     </row>
     <row r="81" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G81" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="H81" s="85">
+      <c r="H81" s="84">
         <v>1</v>
       </c>
-      <c r="I81" s="102"/>
-      <c r="J81" s="105">
+      <c r="I81" s="93"/>
+      <c r="J81" s="96">
         <f>10^-6</f>
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="82" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G82" s="51"/>
-      <c r="H82" s="86"/>
-      <c r="I82" s="103"/>
-      <c r="J82" s="106"/>
+      <c r="H82" s="85"/>
+      <c r="I82" s="94"/>
+      <c r="J82" s="97"/>
     </row>
     <row r="83" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G83" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="H83" s="87"/>
-      <c r="I83" s="104"/>
-      <c r="J83" s="107"/>
+      <c r="H83" s="86"/>
+      <c r="I83" s="95"/>
+      <c r="J83" s="98"/>
     </row>
     <row r="84" spans="7:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G84" s="31" t="s">
@@ -6123,36 +6162,36 @@
       <c r="G104" s="75" t="s">
         <v>228</v>
       </c>
-      <c r="H104" s="82" t="s">
+      <c r="H104" s="101" t="s">
         <v>249</v>
       </c>
       <c r="I104" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="J104" s="85" t="s">
+      <c r="J104" s="84" t="s">
         <v>250</v>
       </c>
-      <c r="K104" s="88" t="s">
+      <c r="K104" s="104" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="105" spans="7:11" x14ac:dyDescent="0.25">
       <c r="G105" s="76"/>
-      <c r="H105" s="83"/>
+      <c r="H105" s="102"/>
       <c r="I105" s="40"/>
-      <c r="J105" s="86"/>
-      <c r="K105" s="89"/>
+      <c r="J105" s="85"/>
+      <c r="K105" s="105"/>
     </row>
     <row r="106" spans="7:11" ht="54" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G106" s="77" t="s">
         <v>231</v>
       </c>
-      <c r="H106" s="84"/>
+      <c r="H106" s="103"/>
       <c r="I106" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="J106" s="87"/>
-      <c r="K106" s="90"/>
+      <c r="J106" s="86"/>
+      <c r="K106" s="106"/>
     </row>
     <row r="107" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G107" s="75" t="s">
@@ -6321,59 +6360,13 @@
         <f t="shared" si="10"/>
         <v>1.9766396352564775E-10</v>
       </c>
-      <c r="K115" s="114">
+      <c r="K115" s="82">
         <f>1/10^6</f>
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="G64:G67"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="H74:H76"/>
-    <mergeCell ref="I74:I76"/>
-    <mergeCell ref="J74:J76"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="J81:J83"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="K37:K38"/>
     <mergeCell ref="H104:H106"/>
     <mergeCell ref="J104:J106"/>
     <mergeCell ref="K104:K106"/>
@@ -6390,6 +6383,52 @@
     <mergeCell ref="O26:O27"/>
     <mergeCell ref="P26:P27"/>
     <mergeCell ref="F31:G32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="J81:J83"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="J74:J76"/>
+    <mergeCell ref="G64:G67"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="K41:K42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Лаб1.xlsx
+++ b/Файлы/1 курс/2 семестр/Экология/Лабы/18.02.25 - 1-ая лаба/Лаб1.xlsx
@@ -8,18 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luvidmi\Desktop\gitRep\Codespace\Файлы\1 курс\2 семестр\Экология\Лабы\18.02.25 - 1-ая лаба\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF92BF8-E968-406E-96D3-B6D595094958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38244D73-17EC-44AE-86BB-7AC616F37034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_Hlk153478266" localSheetId="1">Лист2!$K$19</definedName>
   </definedNames>
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="260">
   <si>
     <t>V(ов) л</t>
   </si>
@@ -1019,23 +1016,6 @@
   </si>
   <si>
     <t>км3</t>
-  </si>
-  <si>
-    <r>
-      <t>С</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ВВ. </t>
-    </r>
   </si>
   <si>
     <r>
@@ -2240,6 +2220,18 @@
   </si>
   <si>
     <t>на 1 человека, т</t>
+  </si>
+  <si>
+    <t>ОЧЕНЬ НИЗКАЯ ИНТЕНСИВНОСТЬ ДВИЖЕНИЯ</t>
+  </si>
+  <si>
+    <t>Территория экологична</t>
+  </si>
+  <si>
+    <t>Ущерб от загрязнения атмосферы</t>
+  </si>
+  <si>
+    <t>Коэффициенты минимальны. Территория экологична</t>
   </si>
 </sst>
 </file>
@@ -2501,7 +2493,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2517,6 +2509,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2813,7 +2817,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2872,7 +2876,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2892,7 +2895,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2984,7 +2986,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3006,23 +3007,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3043,74 +3110,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3176,309 +3187,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>160812</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>681579</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>130095</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Рисунок 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9537370" y="24171235"/>
-          <a:ext cx="6087325" cy="600159"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>216479</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>82261</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>117868</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="12997297"/>
-          <a:ext cx="4390159" cy="524844"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>570635</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>54417</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Рисунок 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="15205364"/>
-          <a:ext cx="4875068" cy="3015827"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>160812</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>681579</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>130096</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Рисунок 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB9DA910-29A3-453A-BCA8-8BF53FBD978D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9847737" y="24022051"/>
-          <a:ext cx="6083367" cy="606345"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>216479</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>82261</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>117868</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Рисунок 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D28D2D49-575E-4363-8769-544EE5B1AFEE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="12884729"/>
-          <a:ext cx="4397086" cy="520514"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>570635</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>54417</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Рисунок 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74619FEF-D390-41D1-923B-9F94B4646A6A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="15087600"/>
-          <a:ext cx="4885459" cy="2997642"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Лист1"/>
-      <sheetName val="Лист2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="Q1">
-            <v>1.65E-3</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27">
-            <v>19.761401157120002</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46">
-            <v>389.70873005464478</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3745,18 +3453,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.7109375" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" customWidth="1"/>
     <col min="16" max="16" width="24" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3797,7 +3505,7 @@
         <v>1.65E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3838,7 +3546,7 @@
         <v>4.62E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3867,7 +3575,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3888,7 +3596,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -3909,7 +3617,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D6" s="1" t="s">
         <v>35</v>
       </c>
@@ -3917,7 +3625,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -3926,7 +3634,7 @@
         <v>74988.066816000006</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -3939,7 +3647,7 @@
       </c>
       <c r="M8" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -3948,7 +3656,7 @@
         <v>4.4000000000000021</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -3957,7 +3665,7 @@
         <v>2623.7952</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -3966,7 +3674,7 @@
         <v>52475.904000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
@@ -3977,15 +3685,15 @@
       <c r="C15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="115">
+      <c r="F15" s="79">
         <f>B15/20</f>
         <v>3.7494033407999998</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
@@ -3994,7 +3702,7 @@
         <v>4.7934719999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -4003,7 +3711,7 @@
         <v>95.869439999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>48</v>
       </c>
@@ -4015,7 +3723,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
@@ -4024,7 +3732,7 @@
         <v>3.9620000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -4033,7 +3741,7 @@
         <v>499.78252800000001</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
@@ -4042,7 +3750,7 @@
         <v>9995.65056</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -4054,7 +3762,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>22</v>
       </c>
@@ -4070,7 +3778,7 @@
         <v>0.1188</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
@@ -4086,7 +3794,7 @@
         <v>0.33263999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>24</v>
       </c>
@@ -4102,7 +3810,7 @@
         <v>7.2000000000000008E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>25</v>
       </c>
@@ -4118,7 +3826,7 @@
         <v>0.52344000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>29</v>
       </c>
@@ -4127,7 +3835,7 @@
         <v>0.52712387021512097</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>30</v>
       </c>
@@ -4136,7 +3844,7 @@
         <v>0.52712387021512097</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>31</v>
       </c>
@@ -4145,7 +3853,7 @@
         <v>2.7617225587648977</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4154,7 +3862,7 @@
         <v>74.592786816</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
@@ -4163,7 +3871,7 @@
         <v>188.7087300546448</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>39</v>
       </c>
@@ -4172,7 +3880,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>40</v>
       </c>
@@ -4181,7 +3889,7 @@
         <v>95.050909769425559</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>41</v>
       </c>
@@ -4197,7 +3905,7 @@
         <v>10.050000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>42</v>
       </c>
@@ -4213,7 +3921,7 @@
         <v>19.485436502732238</v>
       </c>
     </row>
-    <row r="59" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H59" s="4" t="s">
         <v>59</v>
       </c>
@@ -4231,38 +3939,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q115"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" style="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="26"/>
-    <col min="4" max="4" width="15.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="26"/>
+    <col min="4" max="4" width="15.5546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" style="26" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="26" customWidth="1"/>
     <col min="9" max="9" width="25" style="26" customWidth="1"/>
     <col min="10" max="10" width="22" style="26" customWidth="1"/>
-    <col min="11" max="11" width="19.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" style="26" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="26"/>
-    <col min="15" max="15" width="19.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.33203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.21875" style="26" customWidth="1"/>
+    <col min="14" max="14" width="9.109375" style="26"/>
+    <col min="15" max="15" width="19.33203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5546875" style="26" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16" style="26" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="26"/>
+    <col min="18" max="16384" width="9.109375" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="G1" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="33" t="s">
         <v>73</v>
       </c>
       <c r="K1" s="27" t="s">
@@ -4282,14 +3993,14 @@
       </c>
       <c r="Q1" s="27"/>
     </row>
-    <row r="2" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="28" t="s">
+    <row r="2" spans="1:17" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A2" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="27">
         <v>1.3380000000000001</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="27" t="s">
         <v>104</v>
       </c>
       <c r="G2" s="27" t="s">
@@ -4318,14 +4029,14 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+    <row r="3" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <v>20</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="27" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="27" t="s">
@@ -4354,14 +4065,14 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+    <row r="4" spans="1:17" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A4" s="115" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <v>5</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="27" t="s">
         <v>66</v>
       </c>
       <c r="G4" s="27" t="s">
@@ -4384,14 +4095,14 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:17" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A5" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <v>15000</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G5" s="27" t="s">
@@ -4414,7 +4125,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="G6" s="27" t="s">
         <v>78</v>
       </c>
@@ -4435,15 +4146,15 @@
       </c>
       <c r="Q6" s="27"/>
     </row>
-    <row r="7" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+    <row r="7" spans="1:17" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A7" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>B4/B3</f>
         <v>0.25</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="27" t="s">
         <v>70</v>
       </c>
       <c r="G7" s="27" t="s">
@@ -4466,15 +4177,15 @@
       </c>
       <c r="Q7" s="27"/>
     </row>
-    <row r="8" spans="1:17" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A8" s="28" t="s">
+    <row r="8" spans="1:17" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A8" s="114" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <f>B4*B5</f>
         <v>75000</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="27" t="s">
         <v>67</v>
       </c>
       <c r="K8" s="27" t="s">
@@ -4492,7 +4203,7 @@
       </c>
       <c r="Q8" s="27"/>
     </row>
-    <row r="9" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O9" s="27" t="s">
         <v>99</v>
       </c>
@@ -4502,554 +4213,554 @@
       </c>
       <c r="Q9" s="27"/>
     </row>
-    <row r="10" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+    <row r="10" spans="1:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="115" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>B8*M3</f>
         <v>8250</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="107" t="s">
+      <c r="G10" s="89" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="109" t="s">
+      <c r="H10" s="91" t="s">
         <v>109</v>
       </c>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="111"/>
-    </row>
-    <row r="11" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="29" t="s">
+      <c r="I10" s="92"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="92"/>
+      <c r="M10" s="93"/>
+    </row>
+    <row r="11" spans="1:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="115" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <v>0.75</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="108"/>
-      <c r="H11" s="33" t="s">
+      <c r="G11" s="90"/>
+      <c r="H11" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="I11" s="33" t="s">
+      <c r="I11" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="J11" s="33" t="s">
+      <c r="J11" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="33" t="s">
+      <c r="K11" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="L11" s="33" t="s">
+      <c r="L11" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="M11" s="33" t="s">
+      <c r="M11" s="32" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="29"/>
-      <c r="G12" s="31" t="s">
+    <row r="12" spans="1:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="28"/>
+      <c r="G12" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="32">
         <v>395</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="32">
         <v>1.6</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="32">
         <v>20</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="32">
         <v>0.7</v>
       </c>
-      <c r="L12" s="33">
+      <c r="L12" s="32">
         <v>34</v>
       </c>
-      <c r="M12" s="33">
+      <c r="M12" s="32">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="28" t="s">
+    <row r="13" spans="1:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="114" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <f>B10*B11</f>
         <v>6187.5</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="32">
         <v>9</v>
       </c>
-      <c r="I13" s="33">
+      <c r="I13" s="32">
         <v>6</v>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="32">
         <v>33</v>
       </c>
-      <c r="K13" s="33" t="s">
+      <c r="K13" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="L13" s="33">
+      <c r="L13" s="32">
         <v>20</v>
       </c>
-      <c r="M13" s="33">
+      <c r="M13" s="32">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="29" t="s">
+    <row r="14" spans="1:17" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="115" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <f>B13</f>
         <v>6187.5</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="27" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G15" s="48" t="s">
+    <row r="15" spans="1:17" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G15" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="H15" s="35" t="s">
+      <c r="H15" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="I15" s="35" t="s">
+      <c r="I15" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="J15" s="35" t="s">
+      <c r="J15" s="34" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="29" t="s">
+    <row r="16" spans="1:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="27">
         <f>B14*B2</f>
         <v>8278.875</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="E16" s="26" t="s">
+      <c r="D16" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="E16" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="G16" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="33">
+      <c r="H16" s="32">
         <f>B4</f>
         <v>5</v>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="47">
         <f>H16*3</f>
         <v>15</v>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="47">
         <f>B21*I16*2</f>
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="29" t="s">
+    <row r="17" spans="1:16" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="27">
         <f>B16/1000</f>
         <v>8.2788749999999993</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="27" t="s">
         <v>107</v>
       </c>
       <c r="D17" s="116">
         <v>3.7494033407999998</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <f>B17/5</f>
         <v>1.6557749999999998</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="33"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-    </row>
-    <row r="18" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G18" s="31" t="s">
+      <c r="H17" s="32"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+    </row>
+    <row r="18" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G18" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="H18" s="33"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-    </row>
-    <row r="19" spans="1:16" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28" t="s">
+      <c r="H18" s="32"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+    </row>
+    <row r="19" spans="1:16" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="114" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="27">
         <f>B20*B21</f>
         <v>1</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="H19" s="33"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-    </row>
-    <row r="20" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26" t="s">
+      <c r="H19" s="32"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+    </row>
+    <row r="20" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <f>B4</f>
         <v>5</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="C20" s="27"/>
+      <c r="G20" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="H20" s="33"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-    </row>
-    <row r="21" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
+      <c r="H20" s="32"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+    </row>
+    <row r="21" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>0.2</f>
         <v>0.2</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="H21" s="33"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-    </row>
-    <row r="22" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="36" t="s">
+      <c r="H21" s="32"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+    </row>
+    <row r="22" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:16" ht="22.2" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="117" t="s">
         <v>161</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="27">
         <f>H34</f>
         <v>0</v>
       </c>
-      <c r="G23" s="42" t="s">
+      <c r="G23" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="H23" s="112" t="s">
+      <c r="H23" s="94" t="s">
         <v>134</v>
       </c>
-      <c r="I23" s="113"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="113"/>
-      <c r="L23" s="113"/>
-      <c r="M23" s="113"/>
-      <c r="N23" s="113"/>
-      <c r="O23" s="113"/>
-      <c r="P23" s="114"/>
-    </row>
-    <row r="24" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G24" s="43" t="s">
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="95"/>
+      <c r="M23" s="95"/>
+      <c r="N23" s="95"/>
+      <c r="O23" s="95"/>
+      <c r="P23" s="96"/>
+    </row>
+    <row r="24" spans="1:16" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G24" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="I24" s="44" t="s">
+      <c r="I24" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="J24" s="44" t="s">
+      <c r="J24" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="K24" s="44" t="s">
+      <c r="K24" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="L24" s="44" t="s">
+      <c r="L24" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="M24" s="44" t="s">
+      <c r="M24" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="N24" s="45" t="s">
+      <c r="N24" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="O24" s="46" t="s">
+      <c r="O24" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="P24" s="43" t="s">
+      <c r="P24" s="41" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="29" t="s">
+    <row r="25" spans="1:16" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="115" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <f>B26*B27*B28</f>
         <v>3.4999999999999999E-6</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <f>D26*D27*D28</f>
         <v>3500</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="G25" s="43" t="s">
+      <c r="G25" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="44">
+      <c r="H25" s="42">
         <v>19.8</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="42">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J25" s="44">
+      <c r="J25" s="42">
         <v>0.28000000000000003</v>
       </c>
-      <c r="K25" s="44" t="s">
+      <c r="K25" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="L25" s="44">
+      <c r="L25" s="42">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M25" s="44">
+      <c r="M25" s="42">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="N25" s="45"/>
-      <c r="O25" s="46">
+      <c r="N25" s="43"/>
+      <c r="O25" s="44">
         <f>0.18*10^-6</f>
         <v>1.8E-7</v>
       </c>
-      <c r="P25" s="43">
+      <c r="P25" s="41">
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="26" t="s">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="27">
         <f>B21</f>
         <v>0.2</v>
       </c>
-      <c r="D26" s="26">
+      <c r="C26" s="27"/>
+      <c r="D26" s="27">
         <f>B26*1000</f>
         <v>200</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="E26" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="G26" s="47" t="s">
+      <c r="G26" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="H26" s="101">
+      <c r="H26" s="80">
         <v>37.299999999999997</v>
       </c>
-      <c r="I26" s="101">
+      <c r="I26" s="80">
         <v>6.9</v>
       </c>
-      <c r="J26" s="101">
+      <c r="J26" s="80">
         <v>0.8</v>
       </c>
-      <c r="K26" s="101" t="s">
+      <c r="K26" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="L26" s="101">
+      <c r="L26" s="80">
         <v>0.19</v>
       </c>
-      <c r="M26" s="101">
+      <c r="M26" s="80">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="N26" s="101">
+      <c r="N26" s="80">
         <v>0.85</v>
       </c>
-      <c r="O26" s="101" t="s">
+      <c r="O26" s="80" t="s">
         <v>145</v>
       </c>
-      <c r="P26" s="101">
+      <c r="P26" s="80">
         <v>0.23400000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="26" t="s">
+    <row r="27" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="27">
         <f>10/1000</f>
         <v>0.01</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="D27" s="26">
-        <f t="shared" ref="D26:D27" si="0">B27*1000</f>
+      <c r="D27" s="27">
+        <f t="shared" ref="D27" si="0">B27*1000</f>
         <v>10</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="E27" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="G27" s="43" t="s">
+      <c r="G27" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="H27" s="103"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="103"/>
-      <c r="L27" s="103"/>
-      <c r="M27" s="103"/>
-      <c r="N27" s="103"/>
-      <c r="O27" s="103"/>
-      <c r="P27" s="103"/>
-    </row>
-    <row r="28" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="26" t="s">
+      <c r="H27" s="82"/>
+      <c r="I27" s="82"/>
+      <c r="J27" s="82"/>
+      <c r="K27" s="82"/>
+      <c r="L27" s="82"/>
+      <c r="M27" s="82"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="82"/>
+    </row>
+    <row r="28" spans="1:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="27">
         <f>1.75/1000</f>
         <v>1.75E-3</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="27">
         <f>B28*1000</f>
         <v>1.75</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="G28" s="43" t="s">
+      <c r="G28" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="H28" s="44">
+      <c r="H28" s="42">
         <v>28.5</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="42">
         <v>3.5</v>
       </c>
-      <c r="J28" s="44">
+      <c r="J28" s="42">
         <v>0.6</v>
       </c>
-      <c r="K28" s="44" t="s">
+      <c r="K28" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="L28" s="44">
+      <c r="L28" s="42">
         <v>0.11</v>
       </c>
-      <c r="M28" s="44">
+      <c r="M28" s="42">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="N28" s="45">
+      <c r="N28" s="43">
         <v>0.88</v>
       </c>
-      <c r="O28" s="46" t="s">
+      <c r="O28" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="P28" s="43">
+      <c r="P28" s="41">
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G29" s="43" t="s">
+    <row r="29" spans="1:16" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G29" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="H29" s="44">
+      <c r="H29" s="42">
         <v>6.2</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="42">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J29" s="44">
+      <c r="J29" s="42">
         <v>3.5</v>
       </c>
-      <c r="K29" s="44">
+      <c r="K29" s="42">
         <v>0.3</v>
       </c>
-      <c r="L29" s="44">
+      <c r="L29" s="42">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M29" s="44" t="s">
+      <c r="M29" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="N29" s="45"/>
-      <c r="O29" s="46" t="s">
+      <c r="N29" s="43"/>
+      <c r="O29" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="P29" s="43">
+      <c r="P29" s="41">
         <v>4.72</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A30" s="29" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F31" s="99" t="s">
+    <row r="30" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+      <c r="A30" s="28"/>
+    </row>
+    <row r="31" spans="1:16" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="97" t="s">
         <v>153</v>
       </c>
-      <c r="G31" s="99"/>
-      <c r="H31" s="99" t="s">
+      <c r="G31" s="97"/>
+      <c r="H31" s="97" t="s">
         <v>122</v>
       </c>
-      <c r="I31" s="99" t="s">
+      <c r="I31" s="97" t="s">
         <v>123</v>
       </c>
-      <c r="J31" s="100" t="s">
+      <c r="J31" s="98" t="s">
         <v>124</v>
       </c>
-      <c r="K31" s="100"/>
-    </row>
-    <row r="32" spans="1:16" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A32" s="29" t="s">
+      <c r="K31" s="98"/>
+    </row>
+    <row r="32" spans="1:16" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A32" s="115" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="27">
+        <v>16.7</v>
+      </c>
+      <c r="C32" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="B32" s="26">
-        <v>16.7</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="F32" s="99"/>
-      <c r="G32" s="99"/>
-      <c r="H32" s="99"/>
-      <c r="I32" s="99"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="97"/>
+      <c r="I32" s="97"/>
       <c r="J32" s="27" t="s">
         <v>154</v>
       </c>
@@ -5057,21 +4768,21 @@
         <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A33" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="B33" s="26">
+    <row r="33" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A33" s="115" t="s">
+        <v>189</v>
+      </c>
+      <c r="B33" s="27">
         <f>B17/B32</f>
         <v>0.49574101796407183</v>
       </c>
-      <c r="C33" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F33" s="83" t="s">
+      <c r="C33" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" s="99" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="50" t="s">
+      <c r="G33" s="48" t="s">
         <v>125</v>
       </c>
       <c r="H33" s="27">
@@ -5082,50 +4793,49 @@
         <f>B19*H25*24*365</f>
         <v>173448.00000000003</v>
       </c>
-      <c r="J33" s="83">
+      <c r="J33" s="99">
         <f>SUM(H33:I33)</f>
         <v>2617510.5</v>
       </c>
-      <c r="K33" s="83">
+      <c r="K33" s="99">
         <f>J33/365</f>
         <v>7171.2616438356163</v>
       </c>
-      <c r="N33" s="73"/>
-    </row>
-    <row r="34" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A34" s="29" t="s">
+      <c r="N33" s="70"/>
+    </row>
+    <row r="34" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A34" s="115" t="s">
+        <v>191</v>
+      </c>
+      <c r="B34" s="27">
+        <v>3.8970873005464479E-2</v>
+      </c>
+      <c r="C34" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="B34" s="26">
-        <f>[1]Лист1!B46/10000</f>
-        <v>3.8970873005464479E-2</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F34" s="83"/>
-      <c r="G34" s="50" t="s">
+      <c r="F34" s="99"/>
+      <c r="G34" s="48" t="s">
         <v>126</v>
       </c>
       <c r="H34" s="27"/>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-    </row>
-    <row r="35" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A35" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="B35" s="72">
+      <c r="J34" s="99"/>
+      <c r="K34" s="99"/>
+    </row>
+    <row r="35" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A35" s="115" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="118">
         <f>B34+B33</f>
         <v>0.53471189096953631</v>
       </c>
-      <c r="C35" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F35" s="83" t="s">
+      <c r="C35" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="F35" s="99" t="s">
         <v>119</v>
       </c>
-      <c r="G35" s="50" t="s">
+      <c r="G35" s="48" t="s">
         <v>125</v>
       </c>
       <c r="H35" s="27">
@@ -5136,41 +4846,41 @@
         <f>B19*L25*24*365</f>
         <v>613.20000000000005</v>
       </c>
-      <c r="J35" s="83">
+      <c r="J35" s="99">
         <f t="shared" ref="J35" si="1">SUM(H35:I35)</f>
         <v>10513.2</v>
       </c>
-      <c r="K35" s="83">
+      <c r="K35" s="99">
         <f>J35/365</f>
         <v>28.80328767123288</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A36" s="29"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="50" t="s">
+    <row r="36" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A36" s="28"/>
+      <c r="F36" s="99"/>
+      <c r="G36" s="48" t="s">
         <v>126</v>
       </c>
       <c r="H36" s="27"/>
       <c r="I36" s="27"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
-    </row>
-    <row r="37" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A37" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="B37" s="26">
+      <c r="J36" s="99"/>
+      <c r="K36" s="99"/>
+    </row>
+    <row r="37" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A37" s="114" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" s="27">
         <f>B35*1.25</f>
         <v>0.66838986371192033</v>
       </c>
-      <c r="C37" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F37" s="83" t="s">
+      <c r="C37" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="F37" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="50" t="s">
+      <c r="G37" s="48" t="s">
         <v>125</v>
       </c>
       <c r="H37" s="27">
@@ -5181,36 +4891,36 @@
         <f>B19*J25*24*365</f>
         <v>2452.8000000000002</v>
       </c>
-      <c r="J37" s="83">
+      <c r="J37" s="99">
         <f t="shared" ref="J37" si="2">SUM(H37:I37)</f>
         <v>126202.8</v>
       </c>
-      <c r="K37" s="83">
+      <c r="K37" s="99">
         <f>J37/365</f>
         <v>345.76109589041096</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F38" s="83"/>
-      <c r="G38" s="50" t="s">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F38" s="99"/>
+      <c r="G38" s="48" t="s">
         <v>126</v>
       </c>
       <c r="H38" s="27"/>
       <c r="I38" s="27"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-    </row>
-    <row r="39" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="B39" s="26">
+      <c r="J38" s="99"/>
+      <c r="K38" s="99"/>
+    </row>
+    <row r="39" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A39" s="115" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="27">
         <v>12</v>
       </c>
-      <c r="F39" s="83" t="s">
+      <c r="F39" s="99" t="s">
         <v>113</v>
       </c>
-      <c r="G39" s="50" t="s">
+      <c r="G39" s="48" t="s">
         <v>125</v>
       </c>
       <c r="H39" s="27">
@@ -5221,43 +4931,43 @@
         <f>B19*M25*24*365</f>
         <v>306.60000000000002</v>
       </c>
-      <c r="J39" s="83">
+      <c r="J39" s="99">
         <f t="shared" ref="J39" si="3">SUM(H39:I39)</f>
         <v>4637.8500000000004</v>
       </c>
-      <c r="K39" s="83">
+      <c r="K39" s="99">
         <f>J39/365</f>
         <v>12.706438356164385</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A40" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="B40" s="26">
+    <row r="40" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A40" s="115" t="s">
+        <v>196</v>
+      </c>
+      <c r="B40" s="27">
         <v>16</v>
       </c>
-      <c r="F40" s="83"/>
-      <c r="G40" s="50" t="s">
+      <c r="F40" s="99"/>
+      <c r="G40" s="48" t="s">
         <v>126</v>
       </c>
       <c r="H40" s="27"/>
       <c r="I40" s="27"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
-    </row>
-    <row r="41" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="B41" s="26">
+      <c r="J40" s="99"/>
+      <c r="K40" s="99"/>
+    </row>
+    <row r="41" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A41" s="114" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="27">
         <f>B39+B40</f>
         <v>28</v>
       </c>
-      <c r="F41" s="83" t="s">
+      <c r="F41" s="99" t="s">
         <v>132</v>
       </c>
-      <c r="G41" s="50" t="s">
+      <c r="G41" s="48" t="s">
         <v>125</v>
       </c>
       <c r="H41" s="27">
@@ -5268,37 +4978,37 @@
         <f>B19*N25</f>
         <v>0</v>
       </c>
-      <c r="J41" s="83">
+      <c r="J41" s="99">
         <f t="shared" ref="J41" si="4">SUM(H41:I41)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="83">
+      <c r="K41" s="99">
         <f>J41/365</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A42" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B42" s="26">
+    <row r="42" spans="1:14" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="A42" s="114" t="s">
+        <v>197</v>
+      </c>
+      <c r="B42" s="27">
         <f>B39+2*B40</f>
         <v>44</v>
       </c>
-      <c r="F42" s="83"/>
-      <c r="G42" s="50" t="s">
+      <c r="F42" s="99"/>
+      <c r="G42" s="48" t="s">
         <v>126</v>
       </c>
       <c r="H42" s="27"/>
       <c r="I42" s="27"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F43" s="83" t="s">
+      <c r="J42" s="99"/>
+      <c r="K42" s="99"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F43" s="99" t="s">
         <v>121</v>
       </c>
-      <c r="G43" s="50" t="s">
+      <c r="G43" s="48" t="s">
         <v>125</v>
       </c>
       <c r="H43" s="27">
@@ -5309,47 +5019,48 @@
         <f>B19*I25*24*365</f>
         <v>20148</v>
       </c>
-      <c r="J43" s="83">
+      <c r="J43" s="99">
         <f t="shared" ref="J43" si="5">SUM(H43:I43)</f>
         <v>230523</v>
       </c>
-      <c r="K43" s="83">
+      <c r="K43" s="99">
         <f>J43/365</f>
         <v>631.56986301369864</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="B44" s="26">
+    <row r="44" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A44" s="114" t="s">
+        <v>198</v>
+      </c>
+      <c r="B44" s="27">
         <f>B42/B41</f>
         <v>1.5714285714285714</v>
       </c>
-      <c r="F44" s="83"/>
-      <c r="G44" s="50" t="s">
+      <c r="C44" s="27"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="48" t="s">
         <v>126</v>
       </c>
       <c r="H44" s="27"/>
       <c r="I44" s="27"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-    </row>
-    <row r="45" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A45" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="B45" s="26">
+      <c r="J44" s="99"/>
+      <c r="K44" s="99"/>
+    </row>
+    <row r="45" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A45" s="114" t="s">
+        <v>200</v>
+      </c>
+      <c r="B45" s="27">
         <f>J33/1000</f>
         <v>2617.5104999999999</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="83" t="s">
+      <c r="F45" s="99" t="s">
         <v>129</v>
       </c>
-      <c r="G45" s="50" t="s">
+      <c r="G45" s="48" t="s">
         <v>125</v>
       </c>
       <c r="H45" s="27">
@@ -5357,50 +5068,49 @@
         <v>12375</v>
       </c>
       <c r="I45" s="27"/>
-      <c r="J45" s="83">
+      <c r="J45" s="99">
         <f t="shared" ref="J45" si="6">SUM(H45:I45)</f>
         <v>12375</v>
       </c>
-      <c r="K45" s="83">
+      <c r="K45" s="99">
         <f>J45/365</f>
         <v>33.904109589041099</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="B46" s="26">
-        <f>(B44*B45)+([1]Лист1!B27*1000)</f>
+    <row r="46" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A46" s="114" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" s="27">
         <v>23874.631942834287</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C46" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F46" s="83"/>
-      <c r="G46" s="50" t="s">
+      <c r="F46" s="99"/>
+      <c r="G46" s="48" t="s">
         <v>126</v>
       </c>
       <c r="H46" s="27"/>
       <c r="I46" s="27"/>
-      <c r="J46" s="83"/>
-      <c r="K46" s="83"/>
-    </row>
-    <row r="47" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="B47" s="26">
+      <c r="J46" s="99"/>
+      <c r="K46" s="99"/>
+    </row>
+    <row r="47" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A47" s="114" t="s">
+        <v>199</v>
+      </c>
+      <c r="B47" s="27">
         <f>B46/1000</f>
         <v>23.874631942834288</v>
       </c>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="F47" s="83" t="s">
+      <c r="F47" s="99" t="s">
         <v>156</v>
       </c>
-      <c r="G47" s="50" t="s">
+      <c r="G47" s="48" t="s">
         <v>125</v>
       </c>
       <c r="H47" s="27"/>
@@ -5408,30 +5118,30 @@
         <f>B19*P25*24*365</f>
         <v>376.68</v>
       </c>
-      <c r="J47" s="83">
+      <c r="J47" s="99">
         <f t="shared" ref="J47" si="7">SUM(H47:I47)</f>
         <v>376.68</v>
       </c>
-      <c r="K47" s="83">
+      <c r="K47" s="99">
         <f>J47/365</f>
         <v>1.032</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F48" s="83"/>
-      <c r="G48" s="50" t="s">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F48" s="99"/>
+      <c r="G48" s="48" t="s">
         <v>126</v>
       </c>
       <c r="H48" s="27"/>
       <c r="I48" s="27"/>
-      <c r="J48" s="83"/>
-      <c r="K48" s="83"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F49" s="83" t="s">
+      <c r="J48" s="99"/>
+      <c r="K48" s="99"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F49" s="99" t="s">
         <v>157</v>
       </c>
-      <c r="G49" s="50" t="s">
+      <c r="G49" s="48" t="s">
         <v>125</v>
       </c>
       <c r="H49" s="27"/>
@@ -5439,664 +5149,690 @@
         <f>B19*O25*24*365</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="J49" s="83">
+      <c r="J49" s="99">
         <f t="shared" ref="J49" si="8">SUM(H49:I49)</f>
         <v>1.5767999999999999E-3</v>
       </c>
-      <c r="K49" s="83">
+      <c r="K49" s="99">
         <f>J49/365</f>
         <v>4.3200000000000001E-6</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F50" s="83"/>
-      <c r="G50" s="50" t="s">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F50" s="99"/>
+      <c r="G50" s="48" t="s">
         <v>126</v>
       </c>
       <c r="H50" s="27"/>
       <c r="I50" s="27"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="83"/>
-    </row>
-    <row r="51" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="28" t="s">
+      <c r="J50" s="99"/>
+      <c r="K50" s="99"/>
+    </row>
+    <row r="51" spans="1:13" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A51" s="114" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" s="27">
+        <v>1.4469473904748054</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="114" t="s">
         <v>202</v>
       </c>
-      <c r="B51" s="26">
-        <f>(B47/[1]Лист1!Q1)/10000</f>
-        <v>1.4469473904748054</v>
-      </c>
-      <c r="C51" s="26" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B52" s="26">
+      <c r="B52" s="27">
         <f>B51*1.25</f>
         <v>1.8086842380935066</v>
       </c>
-      <c r="C52" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="G52" s="30" t="s">
+      <c r="C52" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="G52" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="H52" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="H52" s="32" t="s">
+      <c r="I52" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="I52" s="37" t="s">
+      <c r="J52" s="57"/>
+    </row>
+    <row r="53" spans="1:13" ht="53.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G53" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="J52" s="59"/>
-    </row>
-    <row r="53" spans="1:11" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G53" s="31" t="s">
+      <c r="H53" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="H53" s="33" t="s">
+      <c r="I53" s="53" t="s">
         <v>232</v>
       </c>
-      <c r="I53" s="55" t="s">
-        <v>233</v>
-      </c>
-      <c r="J53" s="63" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="B54" s="26">
+      <c r="J53" s="61" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="30" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="114" t="s">
+        <v>203</v>
+      </c>
+      <c r="B54" s="27">
         <f>SUM(I16:I21)</f>
         <v>15</v>
       </c>
-      <c r="C54" s="26" t="s">
+      <c r="C54" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="G54" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="H54" s="39">
+        <f>K33/$D$25</f>
+        <v>2.0489318982387474</v>
+      </c>
+      <c r="I54" s="54">
+        <f>K33/J71</f>
+        <v>2390.4205479452053</v>
+      </c>
+      <c r="J54" s="60">
+        <f>H54/J71</f>
+        <v>0.68297729941291585</v>
+      </c>
+      <c r="L54" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="M54" s="121" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G55" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="H55" s="50">
+        <f>K35/$D$25</f>
+        <v>8.2295107632093939E-3</v>
+      </c>
+      <c r="I55" s="55">
+        <f>K35/J78</f>
+        <v>576.0657534246576</v>
+      </c>
+      <c r="J55" s="58">
+        <f>H55/J78</f>
+        <v>0.16459021526418788</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="G56" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="H56" s="50">
+        <f>K37/$D$25</f>
+        <v>9.8788884540117416E-2</v>
+      </c>
+      <c r="I56" s="55">
+        <f>K37/J68</f>
+        <v>8644.0273972602736</v>
+      </c>
+      <c r="J56" s="58">
+        <f>H56/J68</f>
+        <v>2.4697221135029355</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G57" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="H57" s="50">
+        <f>K39/$D$25</f>
+        <v>3.6304109589041099E-3</v>
+      </c>
+      <c r="I57" s="55">
+        <f>K39/J70</f>
+        <v>42354.794520547955</v>
+      </c>
+      <c r="J57" s="58">
+        <f>H57/J70</f>
+        <v>12.101369863013701</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G58" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="H58" s="50">
+        <f>K41*1000/$D$25</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="55">
+        <f>K41/J84</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="58">
+        <f>H58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G59" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="H59" s="50">
+        <f>K43/$D$25</f>
+        <v>0.18044853228962818</v>
+      </c>
+      <c r="I59" s="55">
+        <f>K43/J74</f>
+        <v>126313.97260273973</v>
+      </c>
+      <c r="J59" s="58">
+        <f>H59/J74</f>
+        <v>36.089706457925637</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G60" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="H60" s="50">
+        <f>K45/$D$25</f>
+        <v>9.6868884540117425E-3</v>
+      </c>
+      <c r="I60" s="55">
+        <f>K45/J69</f>
+        <v>678.08219178082197</v>
+      </c>
+      <c r="J60" s="58">
+        <f>H60/J69</f>
+        <v>0.19373776908023485</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G61" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="H61" s="50">
+        <f>K47/$D$25</f>
+        <v>2.9485714285714288E-4</v>
+      </c>
+      <c r="I61" s="55">
+        <f>K47/J85</f>
+        <v>17.200000000000003</v>
+      </c>
+      <c r="J61" s="58">
+        <f>H61/J85</f>
+        <v>4.9142857142857148E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G62" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="H62" s="51">
+        <f>K49/$D$25</f>
+        <v>1.2342857142857144E-9</v>
+      </c>
+      <c r="I62" s="56">
+        <f>K49/J81</f>
+        <v>4.32</v>
+      </c>
+      <c r="J62" s="59">
+        <f>H62/J81</f>
+        <v>1.2342857142857145E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G64" s="83" t="s">
+        <v>153</v>
+      </c>
+      <c r="H64" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="I64" s="106" t="s">
+        <v>234</v>
+      </c>
+      <c r="J64" s="107"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G65" s="84"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="108"/>
+      <c r="J65" s="109"/>
+    </row>
+    <row r="66" spans="1:10" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G66" s="84"/>
+      <c r="H66" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="I66" s="110" t="s">
+        <v>236</v>
+      </c>
+      <c r="J66" s="111"/>
+    </row>
+    <row r="67" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G67" s="85"/>
+      <c r="H67" s="52"/>
+      <c r="I67" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="J67" s="32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G68" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="H68" s="32">
+        <v>2</v>
+      </c>
+      <c r="I68" s="32">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="J68" s="32">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="114" t="s">
         <v>205</v>
       </c>
-      <c r="G54" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="H54" s="41">
+      <c r="B69" s="27">
+        <v>0.4</v>
+      </c>
+      <c r="C69" s="27"/>
+      <c r="G69" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="H69" s="32">
+        <v>3</v>
+      </c>
+      <c r="I69" s="32">
+        <v>0.15</v>
+      </c>
+      <c r="J69" s="32">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="31.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="114" t="s">
+        <v>206</v>
+      </c>
+      <c r="B70" s="27">
+        <v>1</v>
+      </c>
+      <c r="C70" s="27"/>
+      <c r="G70" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="H70" s="32">
+        <v>1</v>
+      </c>
+      <c r="I70" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="J70" s="32">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A71" s="114" t="s">
+        <v>237</v>
+      </c>
+      <c r="B71" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="C71" s="27"/>
+      <c r="G71" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="H71" s="83">
+        <v>3</v>
+      </c>
+      <c r="I71" s="83">
+        <v>5</v>
+      </c>
+      <c r="J71" s="83">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A72" s="114" t="s">
+        <v>207</v>
+      </c>
+      <c r="B72" s="27">
+        <v>1</v>
+      </c>
+      <c r="C72" s="27"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="84"/>
+      <c r="I72" s="84"/>
+      <c r="J72" s="84"/>
+    </row>
+    <row r="73" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="114" t="s">
+        <v>208</v>
+      </c>
+      <c r="B73" s="27">
+        <v>1</v>
+      </c>
+      <c r="C73" s="27"/>
+      <c r="G73" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="H73" s="85"/>
+      <c r="I73" s="85"/>
+      <c r="J73" s="85"/>
+    </row>
+    <row r="74" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="27"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="27"/>
+      <c r="G74" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="H74" s="83">
+        <v>4</v>
+      </c>
+      <c r="I74" s="83">
+        <v>0.03</v>
+      </c>
+      <c r="J74" s="83">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A75" s="114" t="s">
+        <v>238</v>
+      </c>
+      <c r="B75" s="27">
+        <f>SUM(J99:J102)</f>
+        <v>5</v>
+      </c>
+      <c r="C75" s="27"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="84"/>
+      <c r="I75" s="84"/>
+      <c r="J75" s="84"/>
+    </row>
+    <row r="76" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="27"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="27"/>
+      <c r="G76" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="H76" s="85"/>
+      <c r="I76" s="85"/>
+      <c r="J76" s="85"/>
+    </row>
+    <row r="77" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A77" s="119" t="s">
+        <v>239</v>
+      </c>
+      <c r="B77" s="27">
+        <f>(0.5+0.01*B54*B75)*B69*B70*B71*B72*B73</f>
+        <v>0.75</v>
+      </c>
+      <c r="C77" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="G77" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="H77" s="32">
+        <v>3</v>
+      </c>
+      <c r="I77" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="J77" s="32">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G78" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="H78" s="83">
+        <v>2</v>
+      </c>
+      <c r="I78" s="83">
+        <v>0.5</v>
+      </c>
+      <c r="J78" s="83">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G79" s="49"/>
+      <c r="H79" s="84"/>
+      <c r="I79" s="84"/>
+      <c r="J79" s="84"/>
+    </row>
+    <row r="80" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G80" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="H80" s="85"/>
+      <c r="I80" s="85"/>
+      <c r="J80" s="85"/>
+    </row>
+    <row r="81" spans="7:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G81" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="H81" s="83">
+        <v>1</v>
+      </c>
+      <c r="I81" s="100"/>
+      <c r="J81" s="103">
+        <f>10^-6</f>
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="82" spans="7:12" x14ac:dyDescent="0.3">
+      <c r="G82" s="49"/>
+      <c r="H82" s="84"/>
+      <c r="I82" s="101"/>
+      <c r="J82" s="104"/>
+    </row>
+    <row r="83" spans="7:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G83" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="H83" s="85"/>
+      <c r="I83" s="102"/>
+      <c r="J83" s="105"/>
+    </row>
+    <row r="84" spans="7:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G84" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="H84" s="32">
+        <v>3</v>
+      </c>
+      <c r="I84" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="J84" s="32">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="85" spans="7:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G85" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="H85" s="32">
+        <v>2</v>
+      </c>
+      <c r="I85" s="32">
+        <v>0.4</v>
+      </c>
+      <c r="J85" s="32">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="86" spans="7:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="87" spans="7:12" ht="45.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G87" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="H87" s="69" t="s">
+        <v>183</v>
+      </c>
+      <c r="I87" s="69" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="88" spans="7:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G88" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="H88" s="66">
         <f>K33*1000/$D$25</f>
         <v>2048.9318982387476</v>
       </c>
-      <c r="I54" s="56">
+      <c r="I88" s="66">
         <f>K33/J71</f>
         <v>2390.4205479452053</v>
       </c>
-      <c r="J54" s="62">
-        <f>H54/J71</f>
-        <v>682.97729941291584</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G55" s="30" t="s">
+    </row>
+    <row r="89" spans="7:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="G89" s="63" t="s">
         <v>111</v>
       </c>
-      <c r="H55" s="52">
+      <c r="H89" s="64">
         <f>K35*1000/$D$25</f>
         <v>8.2295107632093938</v>
       </c>
-      <c r="I55" s="57">
+      <c r="I89" s="64">
         <f>K35/J78</f>
         <v>576.0657534246576</v>
       </c>
-      <c r="J55" s="60">
-        <f>H55/J78</f>
-        <v>164.59021526418786</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G56" s="30" t="s">
+    </row>
+    <row r="90" spans="7:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="G90" s="63" t="s">
         <v>112</v>
       </c>
-      <c r="H56" s="52">
+      <c r="H90" s="64">
         <f>K37*1000/$D$25</f>
         <v>98.788884540117408</v>
       </c>
-      <c r="I56" s="57">
+      <c r="I90" s="64">
         <f>K37/J68</f>
         <v>8644.0273972602736</v>
       </c>
-      <c r="J56" s="60">
-        <f>H56/J68</f>
-        <v>2469.7221135029354</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G57" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="H57" s="52">
+      <c r="K90" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="L90" s="112" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="91" spans="7:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G91" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="H91" s="64">
         <f>K39*1000/$D$25</f>
         <v>3.6304109589041103</v>
       </c>
-      <c r="I57" s="57">
+      <c r="I91" s="64">
         <f>K39/J70</f>
         <v>42354.794520547955</v>
       </c>
-      <c r="J57" s="60">
-        <f>H57/J70</f>
-        <v>12101.369863013702</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G58" s="30" t="s">
+    </row>
+    <row r="92" spans="7:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="G92" s="63" t="s">
         <v>128</v>
       </c>
-      <c r="H58" s="52">
+      <c r="H92" s="64">
         <f>K41*1000/$D$25</f>
         <v>0</v>
       </c>
-      <c r="I58" s="57">
+      <c r="I92" s="64">
         <f>K41/J84</f>
         <v>0</v>
       </c>
-      <c r="J58" s="60">
-        <f>H58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G59" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="H59" s="52">
+    </row>
+    <row r="93" spans="7:12" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="G93" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="H93" s="64">
         <f>K43*1000/$D$25</f>
         <v>180.44853228962816</v>
       </c>
-      <c r="I59" s="57">
+      <c r="I93" s="64">
         <f>K43/J74</f>
         <v>126313.97260273973</v>
       </c>
-      <c r="J59" s="60">
-        <f>H59/J74</f>
-        <v>36089.706457925633</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G60" s="30" t="s">
+    </row>
+    <row r="94" spans="7:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G94" s="63" t="s">
         <v>129</v>
       </c>
-      <c r="H60" s="52">
+      <c r="H94" s="64">
         <f>K45*1000/$D$25</f>
         <v>9.6868884540117435</v>
       </c>
-      <c r="I60" s="57">
+      <c r="I94" s="64">
         <f>K45/J69</f>
         <v>678.08219178082197</v>
       </c>
-      <c r="J60" s="60">
-        <f>H60/J69</f>
-        <v>193.73776908023487</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G61" s="30" t="s">
+    </row>
+    <row r="95" spans="7:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G95" s="63" t="s">
         <v>130</v>
       </c>
-      <c r="H61" s="52">
+      <c r="H95" s="64">
         <f>K47*1000/$D$25</f>
         <v>0.29485714285714287</v>
       </c>
-      <c r="I61" s="57">
+      <c r="I95" s="64">
         <f>K47/J85</f>
         <v>17.200000000000003</v>
       </c>
-      <c r="J61" s="60">
-        <f>H61/J85</f>
-        <v>4.9142857142857146</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G62" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="H62" s="53">
+    </row>
+    <row r="96" spans="7:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G96" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="H96" s="67">
         <f>K49*1000/$D$25</f>
         <v>1.2342857142857142E-6</v>
       </c>
-      <c r="I62" s="58">
+      <c r="I96" s="67">
         <f>K49/J81</f>
         <v>4.32</v>
       </c>
-      <c r="J62" s="61">
-        <f>H62/J81</f>
-        <v>1.2342857142857142</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G64" s="84" t="s">
-        <v>153</v>
-      </c>
-      <c r="H64" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="I64" s="87" t="s">
-        <v>235</v>
-      </c>
-      <c r="J64" s="88"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G65" s="85"/>
-      <c r="H65" s="40"/>
-      <c r="I65" s="89"/>
-      <c r="J65" s="90"/>
-    </row>
-    <row r="66" spans="1:10" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G66" s="85"/>
-      <c r="H66" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="I66" s="91" t="s">
-        <v>237</v>
-      </c>
-      <c r="J66" s="92"/>
-    </row>
-    <row r="67" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="86"/>
-      <c r="H67" s="54"/>
-      <c r="I67" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="J67" s="33" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G68" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="H68" s="33">
-        <v>2</v>
-      </c>
-      <c r="I68" s="33">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="J68" s="33">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="B69" s="26">
-        <v>0.4</v>
-      </c>
-      <c r="G69" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="H69" s="33">
-        <v>3</v>
-      </c>
-      <c r="I69" s="33">
-        <v>0.15</v>
-      </c>
-      <c r="J69" s="33">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="B70" s="26">
-        <v>1</v>
-      </c>
-      <c r="G70" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H70" s="33">
-        <v>1</v>
-      </c>
-      <c r="I70" s="33">
-        <v>1E-3</v>
-      </c>
-      <c r="J70" s="33">
-        <v>2.9999999999999997E-4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A71" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="B71" s="26">
-        <v>1.5</v>
-      </c>
-      <c r="G71" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="H71" s="84">
-        <v>3</v>
-      </c>
-      <c r="I71" s="84">
-        <v>5</v>
-      </c>
-      <c r="J71" s="84">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A72" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="B72" s="26">
-        <v>1</v>
-      </c>
-      <c r="G72" s="51"/>
-      <c r="H72" s="85"/>
-      <c r="I72" s="85"/>
-      <c r="J72" s="85"/>
-    </row>
-    <row r="73" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="28" t="s">
+    </row>
+    <row r="98" spans="7:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G98" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="B73" s="26">
-        <v>1</v>
-      </c>
-      <c r="G73" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="H73" s="86"/>
-      <c r="I73" s="86"/>
-      <c r="J73" s="86"/>
-    </row>
-    <row r="74" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G74" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="H74" s="84">
-        <v>4</v>
-      </c>
-      <c r="I74" s="84">
-        <v>0.03</v>
-      </c>
-      <c r="J74" s="84">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A75" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="B75" s="26">
-        <f>SUM(J99:J102)</f>
-        <v>5</v>
-      </c>
-      <c r="G75" s="51"/>
-      <c r="H75" s="85"/>
-      <c r="I75" s="85"/>
-      <c r="J75" s="85"/>
-    </row>
-    <row r="76" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G76" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="H76" s="86"/>
-      <c r="I76" s="86"/>
-      <c r="J76" s="86"/>
-    </row>
-    <row r="77" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="80" t="s">
-        <v>240</v>
-      </c>
-      <c r="B77" s="26">
-        <f>(0.5+0.01*B54*B75)*B69*B70*B71*B72*B73</f>
-        <v>0.75</v>
-      </c>
-      <c r="C77" s="26" t="s">
+      <c r="H98" s="75" t="s">
         <v>241</v>
       </c>
-      <c r="G77" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="H77" s="33">
-        <v>3</v>
-      </c>
-      <c r="I77" s="33">
-        <v>0.5</v>
-      </c>
-      <c r="J77" s="33">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G78" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="H78" s="84">
-        <v>2</v>
-      </c>
-      <c r="I78" s="84">
-        <v>0.5</v>
-      </c>
-      <c r="J78" s="84">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G79" s="51"/>
-      <c r="H79" s="85"/>
-      <c r="I79" s="85"/>
-      <c r="J79" s="85"/>
-    </row>
-    <row r="80" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G80" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="H80" s="86"/>
-      <c r="I80" s="86"/>
-      <c r="J80" s="86"/>
-    </row>
-    <row r="81" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G81" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="H81" s="84">
-        <v>1</v>
-      </c>
-      <c r="I81" s="93"/>
-      <c r="J81" s="96">
-        <f>10^-6</f>
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="82" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G82" s="51"/>
-      <c r="H82" s="85"/>
-      <c r="I82" s="94"/>
-      <c r="J82" s="97"/>
-    </row>
-    <row r="83" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G83" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="H83" s="86"/>
-      <c r="I83" s="95"/>
-      <c r="J83" s="98"/>
-    </row>
-    <row r="84" spans="7:10" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G84" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="H84" s="33">
-        <v>3</v>
-      </c>
-      <c r="I84" s="33">
-        <v>0.5</v>
-      </c>
-      <c r="J84" s="33">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="85" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G85" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="H85" s="33">
-        <v>2</v>
-      </c>
-      <c r="I85" s="33">
-        <v>0.4</v>
-      </c>
-      <c r="J85" s="33">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="86" spans="7:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="7:10" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G87" s="70" t="s">
-        <v>153</v>
-      </c>
-      <c r="H87" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="I87" s="71" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="88" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G88" s="64" t="s">
-        <v>135</v>
-      </c>
-      <c r="H88" s="68">
-        <f>K33*1000/$D$25</f>
-        <v>2048.9318982387476</v>
-      </c>
-      <c r="I88" s="68">
-        <f>K33/J71</f>
-        <v>2390.4205479452053</v>
-      </c>
-    </row>
-    <row r="89" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G89" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="H89" s="66">
-        <f>K35*1000/$D$25</f>
-        <v>8.2295107632093938</v>
-      </c>
-      <c r="I89" s="66">
-        <f>K35/J78</f>
-        <v>576.0657534246576</v>
-      </c>
-    </row>
-    <row r="90" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G90" s="65" t="s">
-        <v>112</v>
-      </c>
-      <c r="H90" s="66">
-        <f>K37*1000/$D$25</f>
-        <v>98.788884540117408</v>
-      </c>
-      <c r="I90" s="66">
-        <f>K37/J68</f>
-        <v>8644.0273972602736</v>
-      </c>
-    </row>
-    <row r="91" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G91" s="65" t="s">
-        <v>113</v>
-      </c>
-      <c r="H91" s="66">
-        <f>K39*1000/$D$25</f>
-        <v>3.6304109589041103</v>
-      </c>
-      <c r="I91" s="66">
-        <f>K39/J70</f>
-        <v>42354.794520547955</v>
-      </c>
-    </row>
-    <row r="92" spans="7:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G92" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="H92" s="66">
-        <f>K41*1000/$D$25</f>
-        <v>0</v>
-      </c>
-      <c r="I92" s="66">
-        <f>K41/J84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="7:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="G93" s="66" t="s">
-        <v>186</v>
-      </c>
-      <c r="H93" s="66">
-        <f>K43*1000/$D$25</f>
-        <v>180.44853228962816</v>
-      </c>
-      <c r="I93" s="66">
-        <f>K43/J74</f>
-        <v>126313.97260273973</v>
-      </c>
-    </row>
-    <row r="94" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G94" s="65" t="s">
-        <v>129</v>
-      </c>
-      <c r="H94" s="66">
-        <f>K45*1000/$D$25</f>
-        <v>9.6868884540117435</v>
-      </c>
-      <c r="I94" s="66">
-        <f>K45/J69</f>
-        <v>678.08219178082197</v>
-      </c>
-    </row>
-    <row r="95" spans="7:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G95" s="65" t="s">
-        <v>130</v>
-      </c>
-      <c r="H95" s="66">
-        <f>K47*1000/$D$25</f>
-        <v>0.29485714285714287</v>
-      </c>
-      <c r="I95" s="66">
-        <f>K47/J85</f>
-        <v>17.200000000000003</v>
-      </c>
-    </row>
-    <row r="96" spans="7:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G96" s="67" t="s">
-        <v>187</v>
-      </c>
-      <c r="H96" s="69">
-        <f>K49*1000/$D$25</f>
-        <v>1.2342857142857142E-6</v>
-      </c>
-      <c r="I96" s="69">
-        <f>K49/J81</f>
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="98" spans="7:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G98" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="H98" s="78" t="s">
+      <c r="I98" s="75" t="s">
         <v>242</v>
       </c>
-      <c r="I98" s="78" t="s">
+      <c r="J98" s="75" t="s">
         <v>243</v>
       </c>
-      <c r="J98" s="78" t="s">
+      <c r="K98" s="76"/>
+    </row>
+    <row r="99" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G99" s="27" t="s">
         <v>244</v>
-      </c>
-      <c r="K98" s="79"/>
-    </row>
-    <row r="99" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G99" s="27" t="s">
-        <v>245</v>
       </c>
       <c r="H99" s="27">
         <v>2.2999999999999998</v>
@@ -6110,9 +5846,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="7:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G100" s="27" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H100" s="27">
         <v>0.2</v>
@@ -6126,9 +5862,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="7:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G101" s="27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H101" s="27">
         <v>1</v>
@@ -6141,9 +5877,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="7:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G102" s="27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H102" s="27">
         <v>3.7</v>
@@ -6157,216 +5893,271 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="104" spans="7:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G104" s="75" t="s">
+    <row r="103" spans="7:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="104" spans="7:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G104" s="72" t="s">
+        <v>227</v>
+      </c>
+      <c r="H104" s="80" t="s">
+        <v>248</v>
+      </c>
+      <c r="I104" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="H104" s="101" t="s">
+      <c r="J104" s="83" t="s">
         <v>249</v>
       </c>
-      <c r="I104" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="J104" s="84" t="s">
+      <c r="K104" s="86" t="s">
         <v>250</v>
       </c>
-      <c r="K104" s="104" t="s">
+    </row>
+    <row r="105" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G105" s="73"/>
+      <c r="H105" s="81"/>
+      <c r="I105" s="38"/>
+      <c r="J105" s="84"/>
+      <c r="K105" s="87"/>
+    </row>
+    <row r="106" spans="7:11" ht="36" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G106" s="74" t="s">
+        <v>230</v>
+      </c>
+      <c r="H106" s="82"/>
+      <c r="I106" s="32" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="105" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G105" s="76"/>
-      <c r="H105" s="102"/>
-      <c r="I105" s="40"/>
-      <c r="J105" s="85"/>
-      <c r="K105" s="105"/>
-    </row>
-    <row r="106" spans="7:11" ht="54" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G106" s="77" t="s">
-        <v>231</v>
-      </c>
-      <c r="H106" s="103"/>
-      <c r="I106" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="J106" s="86"/>
-      <c r="K106" s="106"/>
-    </row>
-    <row r="107" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G107" s="75" t="s">
+      <c r="J106" s="85"/>
+      <c r="K106" s="88"/>
+    </row>
+    <row r="107" spans="7:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G107" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="H107" s="30">
+      <c r="H107" s="29">
         <f>H25</f>
         <v>19.8</v>
       </c>
-      <c r="I107" s="52">
+      <c r="I107" s="50">
+        <f>H88</f>
         <v>2048.9318982387476</v>
       </c>
-      <c r="J107" s="32">
+      <c r="J107" s="31">
         <f>(H107*$B$77)/$J$54</f>
-        <v>2.1743035987821256E-2</v>
-      </c>
-      <c r="K107" s="81">
+        <v>21.743035987821255</v>
+      </c>
+      <c r="K107" s="77">
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G108" s="75" t="s">
+    <row r="108" spans="7:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G108" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="H108" s="30">
+      <c r="H108" s="29">
         <f>L25</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I108" s="52">
+      <c r="I108" s="50">
+        <f t="shared" ref="I108:I115" si="10">H89</f>
         <v>8.2295107632093938</v>
       </c>
-      <c r="J108" s="32">
-        <f t="shared" ref="J108:J115" si="10">(H108*$B$77)/$J$54</f>
-        <v>7.6869319148863016E-5</v>
-      </c>
-      <c r="K108" s="81">
+      <c r="J108" s="31">
+        <f t="shared" ref="J108:J115" si="11">(H108*$B$77)/$J$54</f>
+        <v>7.6869319148863025E-2</v>
+      </c>
+      <c r="K108" s="77">
         <v>0.05</v>
       </c>
     </row>
-    <row r="109" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G109" s="75" t="s">
+    <row r="109" spans="7:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G109" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="H109" s="30">
+      <c r="H109" s="29">
         <f>J25</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="I109" s="52">
+      <c r="I109" s="50">
+        <f t="shared" si="10"/>
         <v>98.788884540117408</v>
       </c>
-      <c r="J109" s="32">
-        <f t="shared" si="10"/>
-        <v>3.0747727659545207E-4</v>
-      </c>
-      <c r="K109" s="81">
+      <c r="J109" s="31">
+        <f t="shared" si="11"/>
+        <v>0.3074772765954521</v>
+      </c>
+      <c r="K109" s="77">
         <v>0.04</v>
       </c>
     </row>
-    <row r="110" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G110" s="75" t="s">
+    <row r="110" spans="7:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G110" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="H110" s="30">
+      <c r="H110" s="29">
         <f>M25</f>
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I110" s="52">
+      <c r="I110" s="50">
+        <f t="shared" si="10"/>
         <v>3.6304109589041103</v>
       </c>
-      <c r="J110" s="32">
-        <f t="shared" si="10"/>
-        <v>3.8434659574431508E-5</v>
-      </c>
-      <c r="K110" s="81">
+      <c r="J110" s="31">
+        <f t="shared" si="11"/>
+        <v>3.8434659574431512E-2</v>
+      </c>
+      <c r="K110" s="77">
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
-    <row r="111" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G111" s="75" t="s">
+    <row r="111" spans="7:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G111" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="H111" s="30">
+      <c r="H111" s="29">
         <f>N25</f>
         <v>0</v>
       </c>
-      <c r="I111" s="52">
-        <v>0</v>
-      </c>
-      <c r="J111" s="32">
+      <c r="I111" s="50">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K111" s="81">
+      <c r="J111" s="31">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K111" s="77">
         <v>0.15</v>
       </c>
     </row>
-    <row r="112" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G112" s="75" t="s">
+    <row r="112" spans="7:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G112" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="H112" s="30">
+      <c r="H112" s="29">
         <f>I25</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="I112" s="52">
+      <c r="I112" s="50">
+        <f t="shared" si="10"/>
         <v>180.44853228962816</v>
       </c>
-      <c r="J112" s="32">
-        <f t="shared" si="10"/>
-        <v>2.5257062006054988E-3</v>
-      </c>
-      <c r="K112" s="81">
+      <c r="J112" s="31">
+        <f t="shared" si="11"/>
+        <v>2.5257062006054989</v>
+      </c>
+      <c r="K112" s="77">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="113" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G113" s="75" t="s">
-        <v>253</v>
-      </c>
-      <c r="H113" s="30" t="str">
+    <row r="113" spans="7:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G113" s="72" t="s">
+        <v>252</v>
+      </c>
+      <c r="H113" s="29" t="str">
         <f>K25</f>
         <v>-</v>
       </c>
-      <c r="I113" s="52">
+      <c r="I113" s="50">
+        <f t="shared" si="10"/>
         <v>9.6868884540117435</v>
       </c>
-      <c r="J113" s="32" t="e">
-        <f t="shared" si="10"/>
+      <c r="J113" s="31" t="e">
+        <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
-      <c r="K113" s="81">
+      <c r="K113" s="77">
         <v>0.05</v>
       </c>
     </row>
-    <row r="114" spans="7:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G114" s="75" t="s">
+    <row r="114" spans="7:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G114" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="H114" s="30">
+      <c r="H114" s="29">
         <f>P25</f>
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="I114" s="52">
+      <c r="I114" s="50">
+        <f t="shared" si="10"/>
         <v>0.29485714285714287</v>
       </c>
-      <c r="J114" s="32">
-        <f t="shared" si="10"/>
-        <v>4.7219724620015856E-5</v>
-      </c>
-      <c r="K114" s="81">
+      <c r="J114" s="31">
+        <f t="shared" si="11"/>
+        <v>4.7219724620015856E-2</v>
+      </c>
+      <c r="K114" s="77">
         <v>0.06</v>
       </c>
     </row>
-    <row r="115" spans="7:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G115" s="74" t="s">
+    <row r="115" spans="7:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G115" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="H115" s="48">
+      <c r="H115" s="46">
         <f>O25</f>
         <v>1.8E-7</v>
       </c>
-      <c r="I115" s="58">
+      <c r="I115" s="50">
+        <f t="shared" si="10"/>
         <v>1.2342857142857142E-6</v>
       </c>
-      <c r="J115" s="70">
-        <f t="shared" si="10"/>
-        <v>1.9766396352564775E-10</v>
-      </c>
-      <c r="K115" s="82">
+      <c r="J115" s="68">
+        <f t="shared" si="11"/>
+        <v>1.9766396352564775E-7</v>
+      </c>
+      <c r="K115" s="78">
         <f>1/10^6</f>
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="G64:G67"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="J71:J73"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="J74:J76"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="I78:I80"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="I81:I83"/>
+    <mergeCell ref="J81:J83"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="K37:K38"/>
     <mergeCell ref="H104:H106"/>
     <mergeCell ref="J104:J106"/>
     <mergeCell ref="K104:K106"/>
@@ -6383,100 +6174,54 @@
     <mergeCell ref="O26:O27"/>
     <mergeCell ref="P26:P27"/>
     <mergeCell ref="F31:G32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="I78:I80"/>
-    <mergeCell ref="J78:J80"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="I81:I83"/>
-    <mergeCell ref="J81:J83"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="J71:J73"/>
-    <mergeCell ref="H74:H76"/>
-    <mergeCell ref="I74:I76"/>
-    <mergeCell ref="J74:J76"/>
-    <mergeCell ref="G64:G67"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="K41:K42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24692D00-5DB8-4A31-A496-F2C39E600400}">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="11.6640625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="D1" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>217</v>
-      </c>
       <c r="H1" s="25"/>
     </row>
-    <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>110</v>
       </c>
       <c r="B2" s="15">
-        <f>Лист2!J33</f>
-        <v>2617510.5</v>
+        <f>Лист2!J33/1000000</f>
+        <v>2.6175104999999999</v>
       </c>
       <c r="C2" s="15">
         <f>Лист2!J71</f>
@@ -6491,17 +6236,17 @@
       </c>
       <c r="F2" s="15">
         <f>B2*E2*D2</f>
-        <v>436251.75</v>
+        <v>0.43625174999999994</v>
       </c>
       <c r="G2" s="16"/>
     </row>
-    <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B3" s="15">
-        <f>Лист2!J35</f>
-        <v>10513.2</v>
+        <f>Лист2!J35/1000000</f>
+        <v>1.05132E-2</v>
       </c>
       <c r="C3" s="15">
         <f>Лист2!J78</f>
@@ -6516,16 +6261,16 @@
       </c>
       <c r="F3" s="15">
         <f t="shared" ref="F3:F10" si="1">B3*E3*D3</f>
-        <v>210264</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.21026400000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B4" s="15">
-        <f>Лист2!J37</f>
-        <v>126202.8</v>
+        <f>Лист2!J37/1000000</f>
+        <v>0.1262028</v>
       </c>
       <c r="C4" s="15">
         <f>Лист2!J68</f>
@@ -6540,17 +6285,17 @@
       </c>
       <c r="F4" s="15">
         <f t="shared" si="1"/>
-        <v>3155070</v>
+        <v>3.1550700000000003</v>
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>127</v>
       </c>
       <c r="B5" s="15">
-        <f>Лист2!J39</f>
-        <v>4637.8500000000004</v>
+        <f>Лист2!J39/1000000</f>
+        <v>4.6378500000000007E-3</v>
       </c>
       <c r="C5" s="15">
         <f>Лист2!J70</f>
@@ -6565,12 +6310,12 @@
       </c>
       <c r="F5" s="15">
         <f t="shared" si="1"/>
-        <v>61838000.000000007</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>61.838000000000008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B6" s="15">
         <f>Лист2!J41</f>
@@ -6592,13 +6337,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B7" s="15">
-        <f>Лист2!J43</f>
-        <v>230523</v>
+        <f>Лист2!J43/1000000</f>
+        <v>0.23052300000000001</v>
       </c>
       <c r="C7" s="15">
         <f>Лист2!J74</f>
@@ -6613,16 +6358,16 @@
       </c>
       <c r="F7" s="15">
         <f t="shared" si="1"/>
-        <v>115261500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>115.2615</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>129</v>
       </c>
       <c r="B8" s="15">
-        <f>Лист2!J45</f>
-        <v>12375</v>
+        <f>Лист2!J45/1000000</f>
+        <v>1.2375000000000001E-2</v>
       </c>
       <c r="C8" s="15">
         <f>Лист2!J69</f>
@@ -6637,16 +6382,16 @@
       </c>
       <c r="F8" s="15">
         <f t="shared" si="1"/>
-        <v>618750</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.61875000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>130</v>
       </c>
       <c r="B9" s="15">
-        <f>Лист2!J47</f>
-        <v>376.68</v>
+        <f>Лист2!J47/1000000</f>
+        <v>3.7668000000000001E-4</v>
       </c>
       <c r="C9" s="15">
         <f>Лист2!J85</f>
@@ -6661,16 +6406,16 @@
       </c>
       <c r="F9" s="15">
         <f t="shared" si="1"/>
-        <v>6278.0000000000009</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>6.2780000000000006E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B10" s="18">
-        <f>Лист2!J49</f>
-        <v>1.5767999999999999E-3</v>
+        <f>Лист2!J49/1000000</f>
+        <v>1.5768E-9</v>
       </c>
       <c r="C10" s="19">
         <f>Лист2!J81</f>
@@ -6685,12 +6430,12 @@
       </c>
       <c r="F10" s="15">
         <f t="shared" si="1"/>
-        <v>3942</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3.9420000000000002E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -6698,38 +6443,44 @@
       <c r="E11" s="23"/>
       <c r="F11" s="24">
         <f>SUM(F2:F10)</f>
-        <v>181530055.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+        <v>181.53005575</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B13" s="13">
         <v>2.4</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
         <v>226</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>227</v>
       </c>
       <c r="B14" s="13">
         <v>1.68</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="A15" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B15" s="13">
         <f>B13*B14*F11</f>
-        <v>731929184.78400004</v>
+        <v>731.92918478399997</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="120" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
